--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R169e798de3044b9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rbd1db940ee6940b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R21c8f14c8b2d4eb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rf8a3c076b5dc4ae5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R163dc8d01e3c40bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R9756c9f130b44eaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rc2df67eb4d524995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rb5a015032af14469"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R8e2d095c7c174910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R2c8142cd65604ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R9d8ab9c736f24cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R33822aa14428450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rcc3120f052ce46b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R5b30526eccf9400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R7497c7323e954a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Re84f2b5dd37040f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R65f371ab6ac1401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R5d35c608a4074cd9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2434,7 +2434,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R27e9f47c2d4a4c9d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8381b92cc2ae49c8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2464,7 +2464,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re5611a0c17fc46b1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb41ed0392ad04517"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2494,7 +2494,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rac3379090ba9463b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ae53af4d394496f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2524,7 +2524,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf811a531b28c46c0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd7330c4e8be94def"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2554,7 +2554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re88809e682f1483e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd62869d5a9e14c06"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2589,7 +2589,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfde6208bfb584ec2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff3a8b1f393b433a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2619,7 +2619,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6c0af748429a4fd4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fbf386ca2054025"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2649,7 +2649,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5c7a23e1fd0949df"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2f2825a87b44af8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2679,7 +2679,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbbd394770d3d499b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcd39169486154457"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2709,7 +2709,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R614ebbb0e3e24e1a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfac561fb113c4285"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2744,7 +2744,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb24ea1c984bb4afc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67a6e3c3a8104faa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2774,7 +2774,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcc5073fe49464121"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re703e0137a1349cb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2804,7 +2804,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re824426f17104faf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc373637150b34625"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2834,7 +2834,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf43b313c950a4490"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2aeb4306b7a44abe"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3797,7 +3797,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5845d532675544f0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87be8e0b82134b57"/>
 </x:worksheet>
 </file>
 
@@ -4531,7 +4531,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd246bea7412468b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra551d673a4d04b18"/>
 </x:worksheet>
 </file>
 
@@ -10521,7 +10521,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e1c8d983fd9420a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36aa0df483b345ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14898,7 +14898,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R457566594e4b4e71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R573e19f94fe44ea7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21105,7 +21105,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48fb47ed283a44e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R063877adf1e34b9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24826,7 +24826,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf965729fc094afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f2661e6683349fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26756,7 +26756,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc940f9c387a746b4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae9a672ebb3d4863"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R2c8142cd65604ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R9d8ab9c736f24cf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R33822aa14428450e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Rcc3120f052ce46b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R5b30526eccf9400a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R7497c7323e954a49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Re84f2b5dd37040f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R65f371ab6ac1401e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R5d35c608a4074cd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Re87528e56a36462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Ra379386546114bb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R5f74e0a1d39c4cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R296337b48e8e4cd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Re93f5d3b0154472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R80e815531c144522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rbef1f4f447074f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rdeff005d91a04d7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R7c8db6c9138a4ccf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -598,7 +598,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>四大基金合計｜$298.8 bn USD</a:t>
+              <a:t>四大基金合計｜$298.8B</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1940,7 +1940,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>新制基金｜$181.4 bn USD</a:t>
+              <a:t>新制基金｜$181.4B</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2060,7 +2060,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>舊制基金｜$36.4 bn USD</a:t>
+              <a:t>舊制基金｜$36.4B</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2180,7 +2180,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>勞工保險基金｜$52.7 bn USD</a:t>
+              <a:t>勞工保險基金｜$52.7B</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2300,7 +2300,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>國民年金保險基金｜$28.3 bn USD</a:t>
+              <a:t>國民年金保險基金｜$28.3B</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2434,7 +2434,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8381b92cc2ae49c8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra165c5aaee68413b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2464,7 +2464,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb41ed0392ad04517"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcb2e7cdce6614c73"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2494,7 +2494,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ae53af4d394496f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f6a283226d9416a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2524,7 +2524,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd7330c4e8be94def"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8cfaf89a012f430b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2554,7 +2554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd62869d5a9e14c06"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5d77060cd4cb476d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2589,7 +2589,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rff3a8b1f393b433a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf6d9b1780a914709"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2619,7 +2619,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fbf386ca2054025"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9de1220e0fe4090"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2649,7 +2649,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2f2825a87b44af8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re627f86af3d847f6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2679,7 +2679,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcd39169486154457"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R17d6bef0e3de4335"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2709,7 +2709,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfac561fb113c4285"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R410a26c28fa14145"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2744,7 +2744,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67a6e3c3a8104faa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb4dedc3b6dcf4f44"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2774,7 +2774,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re703e0137a1349cb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R66ac9d1d7f1e440a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2804,7 +2804,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc373637150b34625"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8bf1758ab4b24786"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2834,7 +2834,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2aeb4306b7a44abe"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6643bb1acfbb43e6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3797,7 +3797,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87be8e0b82134b57"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcb8b7b460574715"/>
 </x:worksheet>
 </file>
 
@@ -3853,7 +3853,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="53" t="str">
-        <x:v>資料範圍：115 年 1–6 月；勞保、國保為 115 年 6 月；金額單位：USD 十億（以臺銀 USD/TWD 即期賣出匯率換算；匯率資訊位於本頁下方）</x:v>
+        <x:v>資料範圍：115 年 1–6 月；勞保、國保為 115 年 6 月；金額單位：美元($B)（以臺銀 USD/TWD 即期賣出匯率換算；匯率資訊位於本頁下方）</x:v>
       </x:c>
       <x:c r="B3" s="53"/>
       <x:c r="C3" s="53"/>
@@ -3947,7 +3947,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="15" t="str">
-        <x:v>資產配置（最新月份，USD（十億美元））</x:v>
+        <x:v>資產配置（最新月份，美元($B)）</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
         <x:v>新制</x:v>
@@ -4531,7 +4531,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra551d673a4d04b18"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0271ae0687c4e3d"/>
 </x:worksheet>
 </file>
 
@@ -10521,7 +10521,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36aa0df483b345ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1874c35804c04598"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14898,7 +14898,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R573e19f94fe44ea7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdc830a4a3de4613"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21105,7 +21105,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R063877adf1e34b9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bcc5a7be51f4a7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24826,7 +24826,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f2661e6683349fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1e24e89e4a74a27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26756,7 +26756,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae9a672ebb3d4863"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9ded2b0d3c5422c"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rc3760eb465814bee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R4ab0f97ddfb54e1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R0bb90f0bbce44153"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R708dcdbd86a54718"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R57e4dc2ca3164fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R1d7c0b45cf3649bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R9c8e0791b2c040fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rd5911ddbf4ca4ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Rb9d5cf87635c44da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R487bcf520f79471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rada8bb51beac4a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rc3ccb376be50460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="Refe6e8cec1564d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R63d269e5b1c34a11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R76cbc8231bd04780"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R41bf344536ff42e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R3929023ff7bb474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Ra89fba7ef0b94723"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2434,7 +2434,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdc7dcf749fba405c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c51ed7c97944b93"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2464,7 +2464,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab8034949bd046ef"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re604e5ece7fd4839"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2494,7 +2494,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf0a26b5521554d0d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8dc43c2b4dc8439a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2524,7 +2524,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf36f868abd104642"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb73e27fb668b491b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2554,7 +2554,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Racd7148820ba4efe"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf66f8289aa8a4337"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2589,7 +2589,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5f910c967b174b24"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ec5370df38d4275"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2619,7 +2619,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8a9d62993d544b45"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re9dfbb084c3b4aef"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2649,7 +2649,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78c6fa0081954898"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R565bc2fdc06d48dc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2679,7 +2679,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R45afe5d18266442d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R44ddc595310f4f7a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2709,7 +2709,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R753f5b4564184411"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R763cd43bf82146f0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2744,7 +2744,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R805b8c4a01bc4c6e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R396bdd0b110b48a7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2774,7 +2774,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd80b3a2fa2ff4fbe"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcd4b4459311e4b27"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2804,7 +2804,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R488c5ef50a8549ab"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Red77b596403c49d0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2834,7 +2834,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf29366bcee104e53"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5d3b0e7c90a6430a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2860,8 +2860,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblDomestic" displayName="tblDomestic" ref="A3:L112" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="12">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblDomestic" displayName="tblDomestic" ref="A3:M112" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
     <x:tableColumn id="1" name="日期"/>
     <x:tableColumn id="2" name="期間"/>
     <x:tableColumn id="3" name="基金"/>
@@ -2870,18 +2870,19 @@
     <x:tableColumn id="6" name="業者"/>
     <x:tableColumn id="7" name="委託金額"/>
     <x:tableColumn id="8" name="目前淨資產"/>
-    <x:tableColumn id="9" name="委任至今投資報酬率"/>
-    <x:tableColumn id="10" name="委任至今目標／指標報酬率"/>
-    <x:tableColumn id="11" name="單位"/>
-    <x:tableColumn id="12" name="來源檔案"/>
+    <x:tableColumn id="9" name="委外帳戶當期加/減"/>
+    <x:tableColumn id="10" name="單位"/>
+    <x:tableColumn id="11" name="委任至今投資報酬率"/>
+    <x:tableColumn id="12" name="委任至今目標／指標報酬率"/>
+    <x:tableColumn id="13" name="來源檔案"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblOverseas" displayName="tblOverseas" ref="A3:L162" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="12">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblOverseas" displayName="tblOverseas" ref="A3:M162" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
     <x:tableColumn id="1" name="日期"/>
     <x:tableColumn id="2" name="期間"/>
     <x:tableColumn id="3" name="基金"/>
@@ -2890,10 +2891,11 @@
     <x:tableColumn id="6" name="業者"/>
     <x:tableColumn id="7" name="委託金額"/>
     <x:tableColumn id="8" name="目前淨資產"/>
-    <x:tableColumn id="9" name="委任至今投資報酬率"/>
-    <x:tableColumn id="10" name="委任至今目標／指標報酬率"/>
-    <x:tableColumn id="11" name="單位"/>
-    <x:tableColumn id="12" name="來源檔案"/>
+    <x:tableColumn id="9" name="委外帳戶當期加/減"/>
+    <x:tableColumn id="10" name="單位"/>
+    <x:tableColumn id="11" name="委任至今投資報酬率"/>
+    <x:tableColumn id="12" name="委任至今目標／指標報酬率"/>
+    <x:tableColumn id="13" name="來源檔案"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -3797,7 +3799,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R045987c6d2e545a3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19e1a1d19bb647c8"/>
 </x:worksheet>
 </file>
 
@@ -4531,7 +4533,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb210442aee34db9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re369268823c1431d"/>
 </x:worksheet>
 </file>
 
@@ -11353,7 +11355,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70d9d42b366849fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R080317631f6b4903"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11370,10 +11372,11 @@
     <x:col min="6" max="6" width="14.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="11.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22.219999313354492" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="7" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="7" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -11391,6 +11394,7 @@
       <x:c r="J1" s="4"/>
       <x:c r="K1" s="4"/>
       <x:c r="L1" s="4"/>
+      <x:c r="M1" s="4"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="15" t="str">
@@ -11418,15 +11422,18 @@
         <x:v>目前淨資產</x:v>
       </x:c>
       <x:c r="I3" s="16" t="str">
+        <x:v>委外帳戶當期加/減</x:v>
+      </x:c>
+      <x:c r="J3" s="16" t="str">
+        <x:v>單位</x:v>
+      </x:c>
+      <x:c r="K3" s="16" t="str">
         <x:v>委任至今投資報酬率</x:v>
       </x:c>
-      <x:c r="J3" s="16" t="str">
+      <x:c r="L3" s="16" t="str">
         <x:v>委任至今目標／指標報酬率</x:v>
       </x:c>
-      <x:c r="K3" s="16" t="str">
-        <x:v>單位</x:v>
-      </x:c>
-      <x:c r="L3" s="17" t="str">
+      <x:c r="M3" s="17" t="str">
         <x:v>來源檔案</x:v>
       </x:c>
     </x:row>
@@ -11455,16 +11462,19 @@
       <x:c r="H4" s="39" t="n">
         <x:v>103171495458</x:v>
       </x:c>
-      <x:c r="I4" s="42" t="n">
+      <x:c r="I4" s="39" t="n">
+        <x:v>-14044944939</x:v>
+      </x:c>
+      <x:c r="J4" s="28" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K4" s="42" t="n">
         <x:v>0.9453</x:v>
       </x:c>
-      <x:c r="J4" s="42" t="n">
+      <x:c r="L4" s="42" t="n">
         <x:v>0.0527</x:v>
       </x:c>
-      <x:c r="K4" s="28" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L4" s="29" t="str">
+      <x:c r="M4" s="29" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11493,16 +11503,19 @@
       <x:c r="H5" s="40" t="n">
         <x:v>23175252518</x:v>
       </x:c>
-      <x:c r="I5" s="43" t="n">
+      <x:c r="I5" s="40" t="n">
+        <x:v>-3769084120</x:v>
+      </x:c>
+      <x:c r="J5" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K5" s="43" t="n">
         <x:v>2.3936</x:v>
       </x:c>
-      <x:c r="J5" s="43" t="n">
+      <x:c r="L5" s="43" t="n">
         <x:v>0.2113</x:v>
       </x:c>
-      <x:c r="K5" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L5" s="32" t="str">
+      <x:c r="M5" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11531,16 +11544,19 @@
       <x:c r="H6" s="40" t="n">
         <x:v>58059587887</x:v>
       </x:c>
-      <x:c r="I6" s="43" t="n">
+      <x:c r="I6" s="40" t="n">
+        <x:v>-8430853510</x:v>
+      </x:c>
+      <x:c r="J6" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K6" s="43" t="n">
         <x:v>1.2808000000000002</x:v>
       </x:c>
-      <x:c r="J6" s="43" t="n">
+      <x:c r="L6" s="43" t="n">
         <x:v>0.1198</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L6" s="32" t="str">
+      <x:c r="M6" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11569,16 +11585,19 @@
       <x:c r="H7" s="40" t="n">
         <x:v>12830277484</x:v>
       </x:c>
-      <x:c r="I7" s="43" t="n">
+      <x:c r="I7" s="40" t="n">
+        <x:v>-2570992363</x:v>
+      </x:c>
+      <x:c r="J7" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K7" s="43" t="n">
         <x:v>0.7268000000000001</x:v>
       </x:c>
-      <x:c r="J7" s="43" t="n">
+      <x:c r="L7" s="43" t="n">
         <x:v>0.1198</x:v>
       </x:c>
-      <x:c r="K7" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L7" s="32" t="str">
+      <x:c r="M7" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11607,16 +11626,19 @@
       <x:c r="H8" s="40" t="n">
         <x:v>26081939969</x:v>
       </x:c>
-      <x:c r="I8" s="43" t="n">
+      <x:c r="I8" s="40" t="n">
+        <x:v>-3170801195</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K8" s="43" t="n">
         <x:v>1.4969999999999999</x:v>
       </x:c>
-      <x:c r="J8" s="43" t="n">
+      <x:c r="L8" s="43" t="n">
         <x:v>0.22089999999999999</x:v>
       </x:c>
-      <x:c r="K8" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L8" s="32" t="str">
+      <x:c r="M8" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11645,16 +11667,19 @@
       <x:c r="H9" s="40" t="n">
         <x:v>79596508766</x:v>
       </x:c>
-      <x:c r="I9" s="43" t="n">
+      <x:c r="I9" s="40" t="n">
+        <x:v>-9961655016</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K9" s="43" t="n">
         <x:v>1.7350999999999999</x:v>
       </x:c>
-      <x:c r="J9" s="43" t="n">
+      <x:c r="L9" s="43" t="n">
         <x:v>1.6263999999999998</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L9" s="32" t="str">
+      <x:c r="M9" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11683,16 +11708,19 @@
       <x:c r="H10" s="40" t="n">
         <x:v>40396399644</x:v>
       </x:c>
-      <x:c r="I10" s="43" t="n">
+      <x:c r="I10" s="40" t="n">
+        <x:v>-6265873016</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K10" s="43" t="n">
         <x:v>1.6579</x:v>
       </x:c>
-      <x:c r="J10" s="43" t="n">
+      <x:c r="L10" s="43" t="n">
         <x:v>0.1191</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L10" s="32" t="str">
+      <x:c r="M10" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11721,16 +11749,19 @@
       <x:c r="H11" s="40" t="n">
         <x:v>38985680063</x:v>
       </x:c>
-      <x:c r="I11" s="43" t="n">
+      <x:c r="I11" s="40" t="n">
+        <x:v>-7022091552</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K11" s="43" t="n">
         <x:v>0.8642</x:v>
       </x:c>
-      <x:c r="J11" s="43" t="n">
+      <x:c r="L11" s="43" t="n">
         <x:v>0.1191</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L11" s="32" t="str">
+      <x:c r="M11" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11759,16 +11790,19 @@
       <x:c r="H12" s="40" t="n">
         <x:v>56336151382</x:v>
       </x:c>
-      <x:c r="I12" s="43" t="n">
+      <x:c r="I12" s="40" t="n">
+        <x:v>-4431675502</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K12" s="43" t="n">
         <x:v>0.5015999999999999</x:v>
       </x:c>
-      <x:c r="J12" s="43" t="n">
+      <x:c r="L12" s="43" t="n">
         <x:v>0.36619999999999997</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L12" s="32" t="str">
+      <x:c r="M12" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11797,16 +11831,19 @@
       <x:c r="H13" s="40" t="n">
         <x:v>55897686273</x:v>
       </x:c>
-      <x:c r="I13" s="43" t="n">
+      <x:c r="I13" s="40" t="n">
+        <x:v>-4817199812</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K13" s="43" t="n">
         <x:v>0.4313</x:v>
       </x:c>
-      <x:c r="J13" s="43" t="n">
+      <x:c r="L13" s="43" t="n">
         <x:v>0.36619999999999997</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L13" s="32" t="str">
+      <x:c r="M13" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11835,16 +11872,19 @@
       <x:c r="H14" s="40" t="n">
         <x:v>41322318010</x:v>
       </x:c>
-      <x:c r="I14" s="43" t="n">
+      <x:c r="I14" s="40" t="n">
+        <x:v>-3888439594</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K14" s="43" t="n">
         <x:v>1.6085</x:v>
       </x:c>
-      <x:c r="J14" s="43" t="n">
+      <x:c r="L14" s="43" t="n">
         <x:v>0.2302</x:v>
       </x:c>
-      <x:c r="K14" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L14" s="32" t="str">
+      <x:c r="M14" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11873,16 +11913,19 @@
       <x:c r="H15" s="40" t="n">
         <x:v>40415302192</x:v>
       </x:c>
-      <x:c r="I15" s="43" t="n">
+      <x:c r="I15" s="40" t="n">
+        <x:v>-132920971</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K15" s="43" t="n">
         <x:v>0.7082999999999999</x:v>
       </x:c>
-      <x:c r="J15" s="43" t="n">
+      <x:c r="L15" s="43" t="n">
         <x:v>0.6726000000000001</x:v>
       </x:c>
-      <x:c r="K15" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L15" s="32" t="str">
+      <x:c r="M15" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11911,16 +11954,19 @@
       <x:c r="H16" s="40" t="n">
         <x:v>34144349128</x:v>
       </x:c>
-      <x:c r="I16" s="43" t="n">
+      <x:c r="I16" s="40" t="n">
+        <x:v>-35804097</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K16" s="43" t="n">
         <x:v>0.6894</x:v>
       </x:c>
-      <x:c r="J16" s="43" t="n">
+      <x:c r="L16" s="43" t="n">
         <x:v>0.6726000000000001</x:v>
       </x:c>
-      <x:c r="K16" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L16" s="32" t="str">
+      <x:c r="M16" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11949,16 +11995,19 @@
       <x:c r="H17" s="40" t="n">
         <x:v>33339520716</x:v>
       </x:c>
-      <x:c r="I17" s="43" t="n">
+      <x:c r="I17" s="40" t="n">
+        <x:v>-150450416</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K17" s="43" t="n">
         <x:v>0.7049</x:v>
       </x:c>
-      <x:c r="J17" s="43" t="n">
+      <x:c r="L17" s="43" t="n">
         <x:v>0.6726000000000001</x:v>
       </x:c>
-      <x:c r="K17" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L17" s="32" t="str">
+      <x:c r="M17" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -11987,16 +12036,19 @@
       <x:c r="H18" s="40" t="n">
         <x:v>28296630865</x:v>
       </x:c>
-      <x:c r="I18" s="43" t="n">
+      <x:c r="I18" s="40" t="n">
+        <x:v>-194181980</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K18" s="43" t="n">
         <x:v>0.6829999999999999</x:v>
       </x:c>
-      <x:c r="J18" s="43" t="n">
+      <x:c r="L18" s="43" t="n">
         <x:v>0.6726000000000001</x:v>
       </x:c>
-      <x:c r="K18" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L18" s="32" t="str">
+      <x:c r="M18" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12025,16 +12077,19 @@
       <x:c r="H19" s="40" t="n">
         <x:v>41223752467</x:v>
       </x:c>
-      <x:c r="I19" s="43" t="n">
+      <x:c r="I19" s="40" t="n">
+        <x:v>-219117658</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K19" s="43" t="n">
         <x:v>0.7106999999999999</x:v>
       </x:c>
-      <x:c r="J19" s="43" t="n">
+      <x:c r="L19" s="43" t="n">
         <x:v>0.6726000000000001</x:v>
       </x:c>
-      <x:c r="K19" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L19" s="32" t="str">
+      <x:c r="M19" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12063,16 +12118,19 @@
       <x:c r="H20" s="40" t="n">
         <x:v>12929826184</x:v>
       </x:c>
-      <x:c r="I20" s="43" t="n">
+      <x:c r="I20" s="40" t="n">
+        <x:v>-2713341437</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K20" s="43" t="n">
         <x:v>1.6942</x:v>
       </x:c>
-      <x:c r="J20" s="43" t="n">
+      <x:c r="L20" s="43" t="n">
         <x:v>0.1998</x:v>
       </x:c>
-      <x:c r="K20" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L20" s="32" t="str">
+      <x:c r="M20" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12101,16 +12159,19 @@
       <x:c r="H21" s="40" t="n">
         <x:v>7926139191</x:v>
       </x:c>
-      <x:c r="I21" s="43" t="n">
+      <x:c r="I21" s="40" t="n">
+        <x:v>-929727263</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K21" s="43" t="n">
         <x:v>1.2009</x:v>
       </x:c>
-      <x:c r="J21" s="43" t="n">
+      <x:c r="L21" s="43" t="n">
         <x:v>0.1998</x:v>
       </x:c>
-      <x:c r="K21" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L21" s="32" t="str">
+      <x:c r="M21" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12139,16 +12200,19 @@
       <x:c r="H22" s="40" t="n">
         <x:v>44447329187</x:v>
       </x:c>
-      <x:c r="I22" s="43" t="n">
+      <x:c r="I22" s="40" t="n">
+        <x:v>-6906662932</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K22" s="43" t="n">
         <x:v>2.0039</x:v>
       </x:c>
-      <x:c r="J22" s="43" t="n">
+      <x:c r="L22" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K22" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L22" s="32" t="str">
+      <x:c r="M22" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12177,16 +12241,19 @@
       <x:c r="H23" s="40" t="n">
         <x:v>12530478206</x:v>
       </x:c>
-      <x:c r="I23" s="43" t="n">
+      <x:c r="I23" s="40" t="n">
+        <x:v>-2176158615</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K23" s="43" t="n">
         <x:v>1.3041999999999998</x:v>
       </x:c>
-      <x:c r="J23" s="43" t="n">
+      <x:c r="L23" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K23" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L23" s="32" t="str">
+      <x:c r="M23" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12215,16 +12282,19 @@
       <x:c r="H24" s="40" t="n">
         <x:v>13603740058</x:v>
       </x:c>
-      <x:c r="I24" s="43" t="n">
+      <x:c r="I24" s="40" t="n">
+        <x:v>-2277975695</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K24" s="43" t="n">
         <x:v>1.1314</x:v>
       </x:c>
-      <x:c r="J24" s="43" t="n">
+      <x:c r="L24" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K24" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L24" s="32" t="str">
+      <x:c r="M24" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12253,16 +12323,19 @@
       <x:c r="H25" s="40" t="n">
         <x:v>17348896195</x:v>
       </x:c>
-      <x:c r="I25" s="43" t="n">
+      <x:c r="I25" s="40" t="n">
+        <x:v>-1941207021</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K25" s="43" t="n">
         <x:v>1.4447</x:v>
       </x:c>
-      <x:c r="J25" s="43" t="n">
+      <x:c r="L25" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K25" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L25" s="32" t="str">
+      <x:c r="M25" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12291,16 +12364,19 @@
       <x:c r="H26" s="40" t="n">
         <x:v>25518246126</x:v>
       </x:c>
-      <x:c r="I26" s="43" t="n">
+      <x:c r="I26" s="40" t="n">
+        <x:v>-2042873014</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K26" s="43" t="n">
         <x:v>2.0913999999999997</x:v>
       </x:c>
-      <x:c r="J26" s="43" t="n">
+      <x:c r="L26" s="43" t="n">
         <x:v>2.0934</x:v>
       </x:c>
-      <x:c r="K26" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L26" s="32" t="str">
+      <x:c r="M26" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12329,16 +12405,19 @@
       <x:c r="H27" s="40" t="n">
         <x:v>40249195792</x:v>
       </x:c>
-      <x:c r="I27" s="43" t="n">
+      <x:c r="I27" s="40" t="n">
+        <x:v>-3720168503</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K27" s="43" t="n">
         <x:v>2.1505</x:v>
       </x:c>
-      <x:c r="J27" s="43" t="n">
+      <x:c r="L27" s="43" t="n">
         <x:v>2.0934</x:v>
       </x:c>
-      <x:c r="K27" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L27" s="32" t="str">
+      <x:c r="M27" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12367,16 +12446,19 @@
       <x:c r="H28" s="40" t="n">
         <x:v>29896625207</x:v>
       </x:c>
-      <x:c r="I28" s="43" t="n">
+      <x:c r="I28" s="40" t="n">
+        <x:v>-2561695490</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K28" s="43" t="n">
         <x:v>2.1793</x:v>
       </x:c>
-      <x:c r="J28" s="43" t="n">
+      <x:c r="L28" s="43" t="n">
         <x:v>2.0934</x:v>
       </x:c>
-      <x:c r="K28" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L28" s="32" t="str">
+      <x:c r="M28" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12405,16 +12487,19 @@
       <x:c r="H29" s="40" t="n">
         <x:v>39498492066</x:v>
       </x:c>
-      <x:c r="I29" s="43" t="n">
+      <x:c r="I29" s="40" t="n">
+        <x:v>-3193640300</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K29" s="43" t="n">
         <x:v>2.126</x:v>
       </x:c>
-      <x:c r="J29" s="43" t="n">
+      <x:c r="L29" s="43" t="n">
         <x:v>2.0934</x:v>
       </x:c>
-      <x:c r="K29" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L29" s="32" t="str">
+      <x:c r="M29" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12443,16 +12528,19 @@
       <x:c r="H30" s="40" t="n">
         <x:v>33972525542</x:v>
       </x:c>
-      <x:c r="I30" s="43" t="n">
+      <x:c r="I30" s="40" t="n">
+        <x:v>-2547162188</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K30" s="43" t="n">
         <x:v>2.2522</x:v>
       </x:c>
-      <x:c r="J30" s="43" t="n">
+      <x:c r="L30" s="43" t="n">
         <x:v>2.0934</x:v>
       </x:c>
-      <x:c r="K30" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L30" s="32" t="str">
+      <x:c r="M30" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12481,16 +12569,19 @@
       <x:c r="H31" s="40" t="n">
         <x:v>22662104792</x:v>
       </x:c>
-      <x:c r="I31" s="43" t="n">
+      <x:c r="I31" s="40" t="n">
+        <x:v>-1941110779</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K31" s="43" t="n">
         <x:v>2.1319999999999997</x:v>
       </x:c>
-      <x:c r="J31" s="43" t="n">
+      <x:c r="L31" s="43" t="n">
         <x:v>2.0934</x:v>
       </x:c>
-      <x:c r="K31" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L31" s="32" t="str">
+      <x:c r="M31" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12519,16 +12610,19 @@
       <x:c r="H32" s="40" t="n">
         <x:v>14479782645</x:v>
       </x:c>
-      <x:c r="I32" s="43" t="n">
+      <x:c r="I32" s="40" t="n">
+        <x:v>-1187939432</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K32" s="43" t="n">
         <x:v>2.2617</x:v>
       </x:c>
-      <x:c r="J32" s="43" t="n">
+      <x:c r="L32" s="43" t="n">
         <x:v>2.0934</x:v>
       </x:c>
-      <x:c r="K32" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L32" s="32" t="str">
+      <x:c r="M32" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12557,16 +12651,19 @@
       <x:c r="H33" s="40" t="n">
         <x:v>30231598199</x:v>
       </x:c>
-      <x:c r="I33" s="43" t="n">
+      <x:c r="I33" s="40" t="n">
+        <x:v>-4727899740</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K33" s="43" t="n">
         <x:v>1.2308</x:v>
       </x:c>
-      <x:c r="J33" s="43" t="n">
+      <x:c r="L33" s="43" t="n">
         <x:v>0.1286</x:v>
       </x:c>
-      <x:c r="K33" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L33" s="32" t="str">
+      <x:c r="M33" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12595,16 +12692,19 @@
       <x:c r="H34" s="40" t="n">
         <x:v>30148968555</x:v>
       </x:c>
-      <x:c r="I34" s="43" t="n">
+      <x:c r="I34" s="40" t="n">
+        <x:v>-4683153126</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K34" s="43" t="n">
         <x:v>1.6446</x:v>
       </x:c>
-      <x:c r="J34" s="43" t="n">
+      <x:c r="L34" s="43" t="n">
         <x:v>0.1286</x:v>
       </x:c>
-      <x:c r="K34" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L34" s="32" t="str">
+      <x:c r="M34" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12633,16 +12733,19 @@
       <x:c r="H35" s="40" t="n">
         <x:v>28605010963</x:v>
       </x:c>
-      <x:c r="I35" s="43" t="n">
+      <x:c r="I35" s="40" t="n">
+        <x:v>-5936009054</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K35" s="43" t="n">
         <x:v>1.1039</x:v>
       </x:c>
-      <x:c r="J35" s="43" t="n">
+      <x:c r="L35" s="43" t="n">
         <x:v>0.1286</x:v>
       </x:c>
-      <x:c r="K35" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L35" s="32" t="str">
+      <x:c r="M35" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12671,16 +12774,19 @@
       <x:c r="H36" s="40" t="n">
         <x:v>56940962295</x:v>
       </x:c>
-      <x:c r="I36" s="43" t="n">
+      <x:c r="I36" s="40" t="n">
+        <x:v>-8643495963</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K36" s="43" t="n">
         <x:v>1.7790000000000001</x:v>
       </x:c>
-      <x:c r="J36" s="43" t="n">
+      <x:c r="L36" s="43" t="n">
         <x:v>0.1286</x:v>
       </x:c>
-      <x:c r="K36" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L36" s="32" t="str">
+      <x:c r="M36" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12709,16 +12815,19 @@
       <x:c r="H37" s="40" t="n">
         <x:v>42021514983</x:v>
       </x:c>
-      <x:c r="I37" s="43" t="n">
+      <x:c r="I37" s="40" t="n">
+        <x:v>-4491313504</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K37" s="43" t="n">
         <x:v>1.1596</x:v>
       </x:c>
-      <x:c r="J37" s="43" t="n">
+      <x:c r="L37" s="43" t="n">
         <x:v>0.1286</x:v>
       </x:c>
-      <x:c r="K37" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L37" s="32" t="str">
+      <x:c r="M37" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12747,16 +12856,19 @@
       <x:c r="H38" s="40" t="n">
         <x:v>21096859167</x:v>
       </x:c>
-      <x:c r="I38" s="43" t="n">
+      <x:c r="I38" s="40" t="n">
+        <x:v>-4447073144</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K38" s="43" t="n">
         <x:v>1.1694</x:v>
       </x:c>
-      <x:c r="J38" s="43" t="n">
+      <x:c r="L38" s="43" t="n">
         <x:v>0.1286</x:v>
       </x:c>
-      <x:c r="K38" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L38" s="32" t="str">
+      <x:c r="M38" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12785,16 +12897,19 @@
       <x:c r="H39" s="40" t="n">
         <x:v>16416991185</x:v>
       </x:c>
-      <x:c r="I39" s="43" t="n">
+      <x:c r="I39" s="40" t="n">
+        <x:v>-1858941707</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K39" s="43" t="n">
         <x:v>-0.0748</x:v>
       </x:c>
-      <x:c r="J39" s="43" t="n">
+      <x:c r="L39" s="43" t="n">
         <x:v>0.013600000000000001</x:v>
       </x:c>
-      <x:c r="K39" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L39" s="32" t="str">
+      <x:c r="M39" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12823,16 +12938,19 @@
       <x:c r="H40" s="40" t="n">
         <x:v>22752979420</x:v>
       </x:c>
-      <x:c r="I40" s="43" t="n">
+      <x:c r="I40" s="40" t="n">
+        <x:v>-3714805833</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K40" s="43" t="n">
         <x:v>-0.0942</x:v>
       </x:c>
-      <x:c r="J40" s="43" t="n">
+      <x:c r="L40" s="43" t="n">
         <x:v>0.013600000000000001</x:v>
       </x:c>
-      <x:c r="K40" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L40" s="32" t="str">
+      <x:c r="M40" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12861,16 +12979,19 @@
       <x:c r="H41" s="40" t="n">
         <x:v>16064777486</x:v>
       </x:c>
-      <x:c r="I41" s="43" t="n">
+      <x:c r="I41" s="40" t="n">
+        <x:v>-3367153763</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K41" s="43" t="n">
         <x:v>-0.1412</x:v>
       </x:c>
-      <x:c r="J41" s="43" t="n">
+      <x:c r="L41" s="43" t="n">
         <x:v>0.013600000000000001</x:v>
       </x:c>
-      <x:c r="K41" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L41" s="32" t="str">
+      <x:c r="M41" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12899,16 +13020,19 @@
       <x:c r="H42" s="40" t="n">
         <x:v>21117075101</x:v>
       </x:c>
-      <x:c r="I42" s="43" t="n">
+      <x:c r="I42" s="40" t="n">
+        <x:v>-3106908113</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K42" s="43" t="n">
         <x:v>-0.0882</x:v>
       </x:c>
-      <x:c r="J42" s="43" t="n">
+      <x:c r="L42" s="43" t="n">
         <x:v>0.013600000000000001</x:v>
       </x:c>
-      <x:c r="K42" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L42" s="32" t="str">
+      <x:c r="M42" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12937,16 +13061,19 @@
       <x:c r="H43" s="40" t="n">
         <x:v>30727399354</x:v>
       </x:c>
-      <x:c r="I43" s="43" t="n">
+      <x:c r="I43" s="40" t="n">
+        <x:v>-4182581585</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K43" s="43" t="n">
         <x:v>-0.11710000000000001</x:v>
       </x:c>
-      <x:c r="J43" s="43" t="n">
+      <x:c r="L43" s="43" t="n">
         <x:v>0.013600000000000001</x:v>
       </x:c>
-      <x:c r="K43" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L43" s="32" t="str">
+      <x:c r="M43" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -12975,16 +13102,19 @@
       <x:c r="H44" s="40" t="n">
         <x:v>7088003475</x:v>
       </x:c>
-      <x:c r="I44" s="43" t="n">
+      <x:c r="I44" s="40" t="n">
+        <x:v>-1031036926</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K44" s="43" t="n">
         <x:v>1.2791</x:v>
       </x:c>
-      <x:c r="J44" s="43" t="n">
+      <x:c r="L44" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K44" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L44" s="32" t="str">
+      <x:c r="M44" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13013,16 +13143,19 @@
       <x:c r="H45" s="40" t="n">
         <x:v>7046409838</x:v>
       </x:c>
-      <x:c r="I45" s="43" t="n">
+      <x:c r="I45" s="40" t="n">
+        <x:v>-960398939</x:v>
+      </x:c>
+      <x:c r="J45" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K45" s="43" t="n">
         <x:v>1.2836</x:v>
       </x:c>
-      <x:c r="J45" s="43" t="n">
+      <x:c r="L45" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K45" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L45" s="32" t="str">
+      <x:c r="M45" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13051,16 +13184,19 @@
       <x:c r="H46" s="40" t="n">
         <x:v>7058698601</x:v>
       </x:c>
-      <x:c r="I46" s="43" t="n">
+      <x:c r="I46" s="40" t="n">
+        <x:v>-1084168934</x:v>
+      </x:c>
+      <x:c r="J46" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K46" s="43" t="n">
         <x:v>1.2375</x:v>
       </x:c>
-      <x:c r="J46" s="43" t="n">
+      <x:c r="L46" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K46" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L46" s="32" t="str">
+      <x:c r="M46" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13089,16 +13225,19 @@
       <x:c r="H47" s="40" t="n">
         <x:v>7299682641</x:v>
       </x:c>
-      <x:c r="I47" s="43" t="n">
+      <x:c r="I47" s="40" t="n">
+        <x:v>-1048120932</x:v>
+      </x:c>
+      <x:c r="J47" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K47" s="43" t="n">
         <x:v>1.3363999999999998</x:v>
       </x:c>
-      <x:c r="J47" s="43" t="n">
+      <x:c r="L47" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K47" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L47" s="32" t="str">
+      <x:c r="M47" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13127,16 +13266,19 @@
       <x:c r="H48" s="40" t="n">
         <x:v>6973552798</x:v>
       </x:c>
-      <x:c r="I48" s="43" t="n">
+      <x:c r="I48" s="40" t="n">
+        <x:v>-1133900852</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K48" s="43" t="n">
         <x:v>1.2166</x:v>
       </x:c>
-      <x:c r="J48" s="43" t="n">
+      <x:c r="L48" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K48" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L48" s="32" t="str">
+      <x:c r="M48" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13165,16 +13307,19 @@
       <x:c r="H49" s="40" t="n">
         <x:v>21201075224</x:v>
       </x:c>
-      <x:c r="I49" s="43" t="n">
+      <x:c r="I49" s="40" t="n">
+        <x:v>-3302151519</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K49" s="43" t="n">
         <x:v>1.729</x:v>
       </x:c>
-      <x:c r="J49" s="43" t="n">
+      <x:c r="L49" s="43" t="n">
         <x:v>0.2808</x:v>
       </x:c>
-      <x:c r="K49" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L49" s="32" t="str">
+      <x:c r="M49" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13203,16 +13348,19 @@
       <x:c r="H50" s="40" t="n">
         <x:v>16562402836</x:v>
       </x:c>
-      <x:c r="I50" s="43" t="n">
+      <x:c r="I50" s="40" t="n">
+        <x:v>-3285455291</x:v>
+      </x:c>
+      <x:c r="J50" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K50" s="43" t="n">
         <x:v>1.111</x:v>
       </x:c>
-      <x:c r="J50" s="43" t="n">
+      <x:c r="L50" s="43" t="n">
         <x:v>0.2808</x:v>
       </x:c>
-      <x:c r="K50" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L50" s="32" t="str">
+      <x:c r="M50" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13241,16 +13389,19 @@
       <x:c r="H51" s="40" t="n">
         <x:v>20580006389</x:v>
       </x:c>
-      <x:c r="I51" s="43" t="n">
+      <x:c r="I51" s="40" t="n">
+        <x:v>-2300995758</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K51" s="43" t="n">
         <x:v>1.6996</x:v>
       </x:c>
-      <x:c r="J51" s="43" t="n">
+      <x:c r="L51" s="43" t="n">
         <x:v>0.2808</x:v>
       </x:c>
-      <x:c r="K51" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L51" s="32" t="str">
+      <x:c r="M51" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13279,16 +13430,19 @@
       <x:c r="H52" s="40" t="n">
         <x:v>17031604335</x:v>
       </x:c>
-      <x:c r="I52" s="43" t="n">
+      <x:c r="I52" s="40" t="n">
+        <x:v>-4051602044</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K52" s="43" t="n">
         <x:v>1.1247</x:v>
       </x:c>
-      <x:c r="J52" s="43" t="n">
+      <x:c r="L52" s="43" t="n">
         <x:v>0.2808</x:v>
       </x:c>
-      <x:c r="K52" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L52" s="32" t="str">
+      <x:c r="M52" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13317,16 +13471,19 @@
       <x:c r="H53" s="40" t="n">
         <x:v>24613117899</x:v>
       </x:c>
-      <x:c r="I53" s="43" t="n">
+      <x:c r="I53" s="40" t="n">
+        <x:v>-3391873397</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K53" s="43" t="n">
         <x:v>2.1054</x:v>
       </x:c>
-      <x:c r="J53" s="43" t="n">
+      <x:c r="L53" s="43" t="n">
         <x:v>0.2808</x:v>
       </x:c>
-      <x:c r="K53" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L53" s="32" t="str">
+      <x:c r="M53" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13355,16 +13512,19 @@
       <x:c r="H54" s="40" t="n">
         <x:v>21079896694</x:v>
       </x:c>
-      <x:c r="I54" s="43" t="n">
+      <x:c r="I54" s="40" t="n">
+        <x:v>-3866696231</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K54" s="43" t="n">
         <x:v>1.6864</x:v>
       </x:c>
-      <x:c r="J54" s="43" t="n">
+      <x:c r="L54" s="43" t="n">
         <x:v>0.2808</x:v>
       </x:c>
-      <x:c r="K54" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L54" s="32" t="str">
+      <x:c r="M54" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13393,16 +13553,19 @@
       <x:c r="H55" s="40" t="n">
         <x:v>12706419190</x:v>
       </x:c>
-      <x:c r="I55" s="43" t="n">
+      <x:c r="I55" s="40" t="n">
+        <x:v>-1482204945</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K55" s="43" t="n">
         <x:v>1.0719</x:v>
       </x:c>
-      <x:c r="J55" s="43" t="n">
+      <x:c r="L55" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K55" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L55" s="32" t="str">
+      <x:c r="M55" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13431,16 +13594,19 @@
       <x:c r="H56" s="40" t="n">
         <x:v>18530231676</x:v>
       </x:c>
-      <x:c r="I56" s="43" t="n">
+      <x:c r="I56" s="40" t="n">
+        <x:v>-2892118189</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K56" s="43" t="n">
         <x:v>2.0507</x:v>
       </x:c>
-      <x:c r="J56" s="43" t="n">
+      <x:c r="L56" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K56" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L56" s="32" t="str">
+      <x:c r="M56" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13469,16 +13635,19 @@
       <x:c r="H57" s="40" t="n">
         <x:v>15293632896</x:v>
       </x:c>
-      <x:c r="I57" s="43" t="n">
+      <x:c r="I57" s="40" t="n">
+        <x:v>-3134839058</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K57" s="43" t="n">
         <x:v>1.6005</x:v>
       </x:c>
-      <x:c r="J57" s="43" t="n">
+      <x:c r="L57" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K57" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L57" s="32" t="str">
+      <x:c r="M57" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13507,16 +13676,19 @@
       <x:c r="H58" s="40" t="n">
         <x:v>15089595873</x:v>
       </x:c>
-      <x:c r="I58" s="43" t="n">
+      <x:c r="I58" s="40" t="n">
+        <x:v>-3597316692</x:v>
+      </x:c>
+      <x:c r="J58" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K58" s="43" t="n">
         <x:v>1.1255</x:v>
       </x:c>
-      <x:c r="J58" s="43" t="n">
+      <x:c r="L58" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K58" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L58" s="32" t="str">
+      <x:c r="M58" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13545,16 +13717,19 @@
       <x:c r="H59" s="40" t="n">
         <x:v>19452951069</x:v>
       </x:c>
-      <x:c r="I59" s="43" t="n">
+      <x:c r="I59" s="40" t="n">
+        <x:v>-2986864821</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K59" s="43" t="n">
         <x:v>2.1375</x:v>
       </x:c>
-      <x:c r="J59" s="43" t="n">
+      <x:c r="L59" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K59" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L59" s="32" t="str">
+      <x:c r="M59" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13583,16 +13758,19 @@
       <x:c r="H60" s="40" t="n">
         <x:v>9121413882</x:v>
       </x:c>
-      <x:c r="I60" s="43" t="n">
+      <x:c r="I60" s="40" t="n">
+        <x:v>-3054589966</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K60" s="43" t="n">
         <x:v>0.40130000000000005</x:v>
       </x:c>
-      <x:c r="J60" s="43" t="n">
+      <x:c r="L60" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K60" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L60" s="32" t="str">
+      <x:c r="M60" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13621,16 +13799,19 @@
       <x:c r="H61" s="40" t="n">
         <x:v>14552780847</x:v>
       </x:c>
-      <x:c r="I61" s="43" t="n">
+      <x:c r="I61" s="40" t="n">
+        <x:v>-1793710777</x:v>
+      </x:c>
+      <x:c r="J61" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K61" s="43" t="n">
         <x:v>1.3118</x:v>
       </x:c>
-      <x:c r="J61" s="43" t="n">
+      <x:c r="L61" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K61" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L61" s="32" t="str">
+      <x:c r="M61" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13659,16 +13840,19 @@
       <x:c r="H62" s="40" t="n">
         <x:v>13507194558</x:v>
       </x:c>
-      <x:c r="I62" s="43" t="n">
+      <x:c r="I62" s="40" t="n">
+        <x:v>2841307175</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K62" s="43" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="J62" s="43" t="n">
+      <x:c r="L62" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K62" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L62" s="32" t="str">
+      <x:c r="M62" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13697,16 +13881,19 @@
       <x:c r="H63" s="40" t="n">
         <x:v>12874751853</x:v>
       </x:c>
-      <x:c r="I63" s="43" t="n">
+      <x:c r="I63" s="40" t="n">
+        <x:v>3138260899</x:v>
+      </x:c>
+      <x:c r="J63" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K63" s="43" t="n">
         <x:v>1.2703</x:v>
       </x:c>
-      <x:c r="J63" s="43" t="n">
+      <x:c r="L63" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K63" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L63" s="32" t="str">
+      <x:c r="M63" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13735,16 +13922,19 @@
       <x:c r="H64" s="40" t="n">
         <x:v>13017408018</x:v>
       </x:c>
-      <x:c r="I64" s="43" t="n">
+      <x:c r="I64" s="40" t="n">
+        <x:v>2815123461</x:v>
+      </x:c>
+      <x:c r="J64" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K64" s="43" t="n">
         <x:v>1.2777</x:v>
       </x:c>
-      <x:c r="J64" s="43" t="n">
+      <x:c r="L64" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K64" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L64" s="32" t="str">
+      <x:c r="M64" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13773,16 +13963,19 @@
       <x:c r="H65" s="40" t="n">
         <x:v>12735007874</x:v>
       </x:c>
-      <x:c r="I65" s="43" t="n">
+      <x:c r="I65" s="40" t="n">
+        <x:v>2937317022</x:v>
+      </x:c>
+      <x:c r="J65" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K65" s="43" t="n">
         <x:v>1.1823000000000001</x:v>
       </x:c>
-      <x:c r="J65" s="43" t="n">
+      <x:c r="L65" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K65" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L65" s="32" t="str">
+      <x:c r="M65" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13811,16 +14004,19 @@
       <x:c r="H66" s="40" t="n">
         <x:v>12823234724</x:v>
       </x:c>
-      <x:c r="I66" s="43" t="n">
+      <x:c r="I66" s="40" t="n">
+        <x:v>3025246858</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K66" s="43" t="n">
         <x:v>1.2054</x:v>
       </x:c>
-      <x:c r="J66" s="43" t="n">
+      <x:c r="L66" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K66" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L66" s="32" t="str">
+      <x:c r="M66" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13849,16 +14045,19 @@
       <x:c r="H67" s="40" t="n">
         <x:v>12903392256</x:v>
       </x:c>
-      <x:c r="I67" s="43" t="n">
+      <x:c r="I67" s="40" t="n">
+        <x:v>2886045448</x:v>
+      </x:c>
+      <x:c r="J67" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K67" s="43" t="n">
         <x:v>1.2443</x:v>
       </x:c>
-      <x:c r="J67" s="43" t="n">
+      <x:c r="L67" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K67" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L67" s="32" t="str">
+      <x:c r="M67" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13887,16 +14086,19 @@
       <x:c r="H68" s="40" t="n">
         <x:v>12279463586</x:v>
       </x:c>
-      <x:c r="I68" s="43" t="n">
+      <x:c r="I68" s="40" t="n">
+        <x:v>-1996133443</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K68" s="43" t="n">
         <x:v>0.46659999999999996</x:v>
       </x:c>
-      <x:c r="J68" s="43" t="n">
+      <x:c r="L68" s="43" t="n">
         <x:v>0.0444</x:v>
       </x:c>
-      <x:c r="K68" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L68" s="32" t="str">
+      <x:c r="M68" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13925,16 +14127,19 @@
       <x:c r="H69" s="40" t="n">
         <x:v>13053425511</x:v>
       </x:c>
-      <x:c r="I69" s="43" t="n">
+      <x:c r="I69" s="40" t="n">
+        <x:v>-1809935991</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K69" s="43" t="n">
         <x:v>0.5784</x:v>
       </x:c>
-      <x:c r="J69" s="43" t="n">
+      <x:c r="L69" s="43" t="n">
         <x:v>0.0444</x:v>
       </x:c>
-      <x:c r="K69" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L69" s="32" t="str">
+      <x:c r="M69" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -13963,16 +14168,19 @@
       <x:c r="H70" s="40" t="n">
         <x:v>13497748336</x:v>
       </x:c>
-      <x:c r="I70" s="43" t="n">
+      <x:c r="I70" s="40" t="n">
+        <x:v>-2075471315</x:v>
+      </x:c>
+      <x:c r="J70" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K70" s="43" t="n">
         <x:v>0.6163000000000001</x:v>
       </x:c>
-      <x:c r="J70" s="43" t="n">
+      <x:c r="L70" s="43" t="n">
         <x:v>0.0444</x:v>
       </x:c>
-      <x:c r="K70" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L70" s="32" t="str">
+      <x:c r="M70" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14001,16 +14209,19 @@
       <x:c r="H71" s="40" t="n">
         <x:v>12623775612</x:v>
       </x:c>
-      <x:c r="I71" s="43" t="n">
+      <x:c r="I71" s="40" t="n">
+        <x:v>-2086726212</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K71" s="43" t="n">
         <x:v>0.5424</x:v>
       </x:c>
-      <x:c r="J71" s="43" t="n">
+      <x:c r="L71" s="43" t="n">
         <x:v>0.0444</x:v>
       </x:c>
-      <x:c r="K71" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L71" s="32" t="str">
+      <x:c r="M71" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14039,16 +14250,19 @@
       <x:c r="H72" s="40" t="n">
         <x:v>13042654095</x:v>
       </x:c>
-      <x:c r="I72" s="43" t="n">
+      <x:c r="I72" s="40" t="n">
+        <x:v>-1703940444</x:v>
+      </x:c>
+      <x:c r="J72" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K72" s="43" t="n">
         <x:v>0.5698</x:v>
       </x:c>
-      <x:c r="J72" s="43" t="n">
+      <x:c r="L72" s="43" t="n">
         <x:v>0.0444</x:v>
       </x:c>
-      <x:c r="K72" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L72" s="32" t="str">
+      <x:c r="M72" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14077,14 +14291,17 @@
       <x:c r="H73" s="40" t="n">
         <x:v>4902240425</x:v>
       </x:c>
-      <x:c r="I73" s="43" t="n">
+      <x:c r="I73" s="40" t="n">
+        <x:v>3357707657</x:v>
+      </x:c>
+      <x:c r="J73" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K73" s="43" t="n">
         <x:v>-0.0526</x:v>
       </x:c>
-      <x:c r="J73" s="43"/>
-      <x:c r="K73" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L73" s="32" t="str">
+      <x:c r="L73" s="43"/>
+      <x:c r="M73" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14113,16 +14330,19 @@
       <x:c r="H74" s="40" t="n">
         <x:v>32320138788</x:v>
       </x:c>
-      <x:c r="I74" s="43" t="n">
+      <x:c r="I74" s="40" t="n">
+        <x:v>-6039242500</x:v>
+      </x:c>
+      <x:c r="J74" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K74" s="43" t="n">
         <x:v>1.0713</x:v>
       </x:c>
-      <x:c r="J74" s="43" t="n">
+      <x:c r="L74" s="43" t="n">
         <x:v>0.0947</x:v>
       </x:c>
-      <x:c r="K74" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L74" s="32" t="str">
+      <x:c r="M74" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14151,16 +14371,19 @@
       <x:c r="H75" s="40" t="n">
         <x:v>26790911817</x:v>
       </x:c>
-      <x:c r="I75" s="43" t="n">
+      <x:c r="I75" s="40" t="n">
+        <x:v>-5561557655</x:v>
+      </x:c>
+      <x:c r="J75" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K75" s="43" t="n">
         <x:v>0.9856</x:v>
       </x:c>
-      <x:c r="J75" s="43" t="n">
+      <x:c r="L75" s="43" t="n">
         <x:v>0.0947</x:v>
       </x:c>
-      <x:c r="K75" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L75" s="32" t="str">
+      <x:c r="M75" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14189,16 +14412,19 @@
       <x:c r="H76" s="40" t="n">
         <x:v>13425179562</x:v>
       </x:c>
-      <x:c r="I76" s="43" t="n">
+      <x:c r="I76" s="40" t="n">
+        <x:v>-918698815</x:v>
+      </x:c>
+      <x:c r="J76" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K76" s="43" t="n">
         <x:v>1.0556999999999999</x:v>
       </x:c>
-      <x:c r="J76" s="43" t="n">
+      <x:c r="L76" s="43" t="n">
         <x:v>0.9778</x:v>
       </x:c>
-      <x:c r="K76" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L76" s="32" t="str">
+      <x:c r="M76" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14227,16 +14453,19 @@
       <x:c r="H77" s="40" t="n">
         <x:v>78465559204</x:v>
       </x:c>
-      <x:c r="I77" s="43" t="n">
+      <x:c r="I77" s="40" t="n">
+        <x:v>-11765906915</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K77" s="43" t="n">
         <x:v>1.8681999999999999</x:v>
       </x:c>
-      <x:c r="J77" s="43" t="n">
+      <x:c r="L77" s="43" t="n">
         <x:v>0.132</x:v>
       </x:c>
-      <x:c r="K77" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L77" s="32" t="str">
+      <x:c r="M77" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14265,16 +14494,19 @@
       <x:c r="H78" s="40" t="n">
         <x:v>12931832350</x:v>
       </x:c>
-      <x:c r="I78" s="43" t="n">
+      <x:c r="I78" s="40" t="n">
+        <x:v>-2713291289</x:v>
+      </x:c>
+      <x:c r="J78" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K78" s="43" t="n">
         <x:v>1.6941</x:v>
       </x:c>
-      <x:c r="J78" s="43" t="n">
+      <x:c r="L78" s="43" t="n">
         <x:v>0.1998</x:v>
       </x:c>
-      <x:c r="K78" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L78" s="32" t="str">
+      <x:c r="M78" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14303,16 +14535,19 @@
       <x:c r="H79" s="40" t="n">
         <x:v>6928377916</x:v>
       </x:c>
-      <x:c r="I79" s="43" t="n">
+      <x:c r="I79" s="40" t="n">
+        <x:v>-898102998</x:v>
+      </x:c>
+      <x:c r="J79" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K79" s="43" t="n">
         <x:v>1.1693</x:v>
       </x:c>
-      <x:c r="J79" s="43" t="n">
+      <x:c r="L79" s="43" t="n">
         <x:v>0.1998</x:v>
       </x:c>
-      <x:c r="K79" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L79" s="32" t="str">
+      <x:c r="M79" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14341,16 +14576,19 @@
       <x:c r="H80" s="40" t="n">
         <x:v>44451751213</x:v>
       </x:c>
-      <x:c r="I80" s="43" t="n">
+      <x:c r="I80" s="40" t="n">
+        <x:v>-6906493455</x:v>
+      </x:c>
+      <x:c r="J80" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K80" s="43" t="n">
         <x:v>2.0039</x:v>
       </x:c>
-      <x:c r="J80" s="43" t="n">
+      <x:c r="L80" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K80" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L80" s="32" t="str">
+      <x:c r="M80" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14379,16 +14617,19 @@
       <x:c r="H81" s="40" t="n">
         <x:v>10627945460</x:v>
       </x:c>
-      <x:c r="I81" s="43" t="n">
+      <x:c r="I81" s="40" t="n">
+        <x:v>-1827363987</x:v>
+      </x:c>
+      <x:c r="J81" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K81" s="43" t="n">
         <x:v>1.2893000000000001</x:v>
       </x:c>
-      <x:c r="J81" s="43" t="n">
+      <x:c r="L81" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K81" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L81" s="32" t="str">
+      <x:c r="M81" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14417,16 +14658,19 @@
       <x:c r="H82" s="40" t="n">
         <x:v>11811294891</x:v>
       </x:c>
-      <x:c r="I82" s="43" t="n">
+      <x:c r="I82" s="40" t="n">
+        <x:v>-1980272675</x:v>
+      </x:c>
+      <x:c r="J82" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K82" s="43" t="n">
         <x:v>1.1309</x:v>
       </x:c>
-      <x:c r="J82" s="43" t="n">
+      <x:c r="L82" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K82" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L82" s="32" t="str">
+      <x:c r="M82" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14455,16 +14699,19 @@
       <x:c r="H83" s="40" t="n">
         <x:v>15904763483</x:v>
       </x:c>
-      <x:c r="I83" s="43" t="n">
+      <x:c r="I83" s="40" t="n">
+        <x:v>-1781367234</x:v>
+      </x:c>
+      <x:c r="J83" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K83" s="43" t="n">
         <x:v>1.4385</x:v>
       </x:c>
-      <x:c r="J83" s="43" t="n">
+      <x:c r="L83" s="43" t="n">
         <x:v>0.21</x:v>
       </x:c>
-      <x:c r="K83" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L83" s="32" t="str">
+      <x:c r="M83" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14493,16 +14740,19 @@
       <x:c r="H84" s="40" t="n">
         <x:v>2330215349</x:v>
       </x:c>
-      <x:c r="I84" s="43" t="n">
+      <x:c r="I84" s="40" t="n">
+        <x:v>-376471490</x:v>
+      </x:c>
+      <x:c r="J84" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K84" s="43" t="n">
         <x:v>1.2483</x:v>
       </x:c>
-      <x:c r="J84" s="43" t="n">
+      <x:c r="L84" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K84" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L84" s="32" t="str">
+      <x:c r="M84" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14531,16 +14781,19 @@
       <x:c r="H85" s="40" t="n">
         <x:v>2302140221</x:v>
       </x:c>
-      <x:c r="I85" s="43" t="n">
+      <x:c r="I85" s="40" t="n">
+        <x:v>-367060392</x:v>
+      </x:c>
+      <x:c r="J85" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K85" s="43" t="n">
         <x:v>1.2382</x:v>
       </x:c>
-      <x:c r="J85" s="43" t="n">
+      <x:c r="L85" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K85" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L85" s="32" t="str">
+      <x:c r="M85" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14569,16 +14822,19 @@
       <x:c r="H86" s="40" t="n">
         <x:v>2297488877</x:v>
       </x:c>
-      <x:c r="I86" s="43" t="n">
+      <x:c r="I86" s="40" t="n">
+        <x:v>-417079026</x:v>
+      </x:c>
+      <x:c r="J86" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K86" s="43" t="n">
         <x:v>1.1848</x:v>
       </x:c>
-      <x:c r="J86" s="43" t="n">
+      <x:c r="L86" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K86" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L86" s="32" t="str">
+      <x:c r="M86" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14607,16 +14863,19 @@
       <x:c r="H87" s="40" t="n">
         <x:v>2374031106</x:v>
       </x:c>
-      <x:c r="I87" s="43" t="n">
+      <x:c r="I87" s="40" t="n">
+        <x:v>-408884808</x:v>
+      </x:c>
+      <x:c r="J87" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K87" s="43" t="n">
         <x:v>1.2799</x:v>
       </x:c>
-      <x:c r="J87" s="43" t="n">
+      <x:c r="L87" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K87" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L87" s="32" t="str">
+      <x:c r="M87" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14645,16 +14904,19 @@
       <x:c r="H88" s="40" t="n">
         <x:v>2293703108</x:v>
       </x:c>
-      <x:c r="I88" s="43" t="n">
+      <x:c r="I88" s="40" t="n">
+        <x:v>-409648800</x:v>
+      </x:c>
+      <x:c r="J88" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K88" s="43" t="n">
         <x:v>1.1886</x:v>
       </x:c>
-      <x:c r="J88" s="43" t="n">
+      <x:c r="L88" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K88" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L88" s="32" t="str">
+      <x:c r="M88" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14683,16 +14945,19 @@
       <x:c r="H89" s="40" t="n">
         <x:v>5395348747</x:v>
       </x:c>
-      <x:c r="I89" s="43" t="n">
+      <x:c r="I89" s="40" t="n">
+        <x:v>-655239852</x:v>
+      </x:c>
+      <x:c r="J89" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K89" s="43" t="n">
         <x:v>1.0949</x:v>
       </x:c>
-      <x:c r="J89" s="43" t="n">
+      <x:c r="L89" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K89" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L89" s="32" t="str">
+      <x:c r="M89" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14721,16 +14986,19 @@
       <x:c r="H90" s="40" t="n">
         <x:v>7802702228</x:v>
       </x:c>
-      <x:c r="I90" s="43" t="n">
+      <x:c r="I90" s="40" t="n">
+        <x:v>-1217848671</x:v>
+      </x:c>
+      <x:c r="J90" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K90" s="43" t="n">
         <x:v>2.0665</x:v>
       </x:c>
-      <x:c r="J90" s="43" t="n">
+      <x:c r="L90" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K90" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L90" s="32" t="str">
+      <x:c r="M90" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14759,16 +15027,19 @@
       <x:c r="H91" s="40" t="n">
         <x:v>6513458038</x:v>
       </x:c>
-      <x:c r="I91" s="43" t="n">
+      <x:c r="I91" s="40" t="n">
+        <x:v>-1331100520</x:v>
+      </x:c>
+      <x:c r="J91" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K91" s="43" t="n">
         <x:v>1.6488999999999998</x:v>
       </x:c>
-      <x:c r="J91" s="43" t="n">
+      <x:c r="L91" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K91" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L91" s="32" t="str">
+      <x:c r="M91" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14797,16 +15068,19 @@
       <x:c r="H92" s="40" t="n">
         <x:v>6612291633</x:v>
       </x:c>
-      <x:c r="I92" s="43" t="n">
+      <x:c r="I92" s="40" t="n">
+        <x:v>-1576257862</x:v>
+      </x:c>
+      <x:c r="J92" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K92" s="43" t="n">
         <x:v>1.1372</x:v>
       </x:c>
-      <x:c r="J92" s="43" t="n">
+      <x:c r="L92" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K92" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L92" s="32" t="str">
+      <x:c r="M92" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14835,16 +15109,19 @@
       <x:c r="H93" s="40" t="n">
         <x:v>8185169896</x:v>
       </x:c>
-      <x:c r="I93" s="43" t="n">
+      <x:c r="I93" s="40" t="n">
+        <x:v>-1256946817</x:v>
+      </x:c>
+      <x:c r="J93" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K93" s="43" t="n">
         <x:v>2.1261</x:v>
       </x:c>
-      <x:c r="J93" s="43" t="n">
+      <x:c r="L93" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K93" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L93" s="32" t="str">
+      <x:c r="M93" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14873,16 +15150,19 @@
       <x:c r="H94" s="40" t="n">
         <x:v>3966553054</x:v>
       </x:c>
-      <x:c r="I94" s="43" t="n">
+      <x:c r="I94" s="40" t="n">
+        <x:v>-1328383087</x:v>
+      </x:c>
+      <x:c r="J94" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K94" s="43" t="n">
         <x:v>0.43560000000000004</x:v>
       </x:c>
-      <x:c r="J94" s="43" t="n">
+      <x:c r="L94" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K94" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L94" s="32" t="str">
+      <x:c r="M94" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14911,16 +15191,19 @@
       <x:c r="H95" s="40" t="n">
         <x:v>6160765344</x:v>
       </x:c>
-      <x:c r="I95" s="43" t="n">
+      <x:c r="I95" s="40" t="n">
+        <x:v>-759365736</x:v>
+      </x:c>
+      <x:c r="J95" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K95" s="43" t="n">
         <x:v>1.3285</x:v>
       </x:c>
-      <x:c r="J95" s="43" t="n">
+      <x:c r="L95" s="43" t="n">
         <x:v>0.1681</x:v>
       </x:c>
-      <x:c r="K95" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L95" s="32" t="str">
+      <x:c r="M95" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14949,16 +15232,19 @@
       <x:c r="H96" s="40" t="n">
         <x:v>15506059249</x:v>
       </x:c>
-      <x:c r="I96" s="43" t="n">
+      <x:c r="I96" s="40" t="n">
+        <x:v>-1911360124</x:v>
+      </x:c>
+      <x:c r="J96" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K96" s="43" t="n">
         <x:v>1.5816</x:v>
       </x:c>
-      <x:c r="J96" s="43" t="n">
+      <x:c r="L96" s="43" t="n">
         <x:v>0.1689</x:v>
       </x:c>
-      <x:c r="K96" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L96" s="32" t="str">
+      <x:c r="M96" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -14987,16 +15273,19 @@
       <x:c r="H97" s="40" t="n">
         <x:v>25210400997</x:v>
       </x:c>
-      <x:c r="I97" s="43" t="n">
+      <x:c r="I97" s="40" t="n">
+        <x:v>-3467042417</x:v>
+      </x:c>
+      <x:c r="J97" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K97" s="43" t="n">
         <x:v>1.4922</x:v>
       </x:c>
-      <x:c r="J97" s="43" t="n">
+      <x:c r="L97" s="43" t="n">
         <x:v>0.12210000000000001</x:v>
       </x:c>
-      <x:c r="K97" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L97" s="32" t="str">
+      <x:c r="M97" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15025,16 +15314,19 @@
       <x:c r="H98" s="40" t="n">
         <x:v>3818517195</x:v>
       </x:c>
-      <x:c r="I98" s="43" t="n">
+      <x:c r="I98" s="40" t="n">
+        <x:v>-808647247</x:v>
+      </x:c>
+      <x:c r="J98" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K98" s="43" t="n">
         <x:v>1.5265</x:v>
       </x:c>
-      <x:c r="J98" s="43" t="n">
+      <x:c r="L98" s="43" t="n">
         <x:v>0.1675</x:v>
       </x:c>
-      <x:c r="K98" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L98" s="32" t="str">
+      <x:c r="M98" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15063,16 +15355,19 @@
       <x:c r="H99" s="40" t="n">
         <x:v>6954213572</x:v>
       </x:c>
-      <x:c r="I99" s="43" t="n">
+      <x:c r="I99" s="40" t="n">
+        <x:v>-1093007069</x:v>
+      </x:c>
+      <x:c r="J99" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K99" s="43" t="n">
         <x:v>1.6194</x:v>
       </x:c>
-      <x:c r="J99" s="43" t="n">
+      <x:c r="L99" s="43" t="n">
         <x:v>0.1675</x:v>
       </x:c>
-      <x:c r="K99" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L99" s="32" t="str">
+      <x:c r="M99" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15101,16 +15396,19 @@
       <x:c r="H100" s="40" t="n">
         <x:v>3603308455</x:v>
       </x:c>
-      <x:c r="I100" s="43" t="n">
+      <x:c r="I100" s="40" t="n">
+        <x:v>-432746327</x:v>
+      </x:c>
+      <x:c r="J100" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K100" s="43" t="n">
         <x:v>1.63</x:v>
       </x:c>
-      <x:c r="J100" s="43" t="n">
+      <x:c r="L100" s="43" t="n">
         <x:v>0.1675</x:v>
       </x:c>
-      <x:c r="K100" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L100" s="32" t="str">
+      <x:c r="M100" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15139,16 +15437,19 @@
       <x:c r="H101" s="40" t="n">
         <x:v>2468400903</x:v>
       </x:c>
-      <x:c r="I101" s="43" t="n">
+      <x:c r="I101" s="40" t="n">
+        <x:v>-433264662</x:v>
+      </x:c>
+      <x:c r="J101" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K101" s="43" t="n">
         <x:v>1.1815</x:v>
       </x:c>
-      <x:c r="J101" s="43" t="n">
+      <x:c r="L101" s="43" t="n">
         <x:v>0.1675</x:v>
       </x:c>
-      <x:c r="K101" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L101" s="32" t="str">
+      <x:c r="M101" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15177,16 +15478,19 @@
       <x:c r="H102" s="40" t="n">
         <x:v>2792913358</x:v>
       </x:c>
-      <x:c r="I102" s="43" t="n">
+      <x:c r="I102" s="40" t="n">
+        <x:v>-467485995</x:v>
+      </x:c>
+      <x:c r="J102" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K102" s="43" t="n">
         <x:v>0.8889</x:v>
       </x:c>
-      <x:c r="J102" s="43" t="n">
+      <x:c r="L102" s="43" t="n">
         <x:v>0.1675</x:v>
       </x:c>
-      <x:c r="K102" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L102" s="32" t="str">
+      <x:c r="M102" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15215,16 +15519,19 @@
       <x:c r="H103" s="40" t="n">
         <x:v>3454968458</x:v>
       </x:c>
-      <x:c r="I103" s="43" t="n">
+      <x:c r="I103" s="40" t="n">
+        <x:v>-387037767</x:v>
+      </x:c>
+      <x:c r="J103" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K103" s="43" t="n">
         <x:v>1.3153</x:v>
       </x:c>
-      <x:c r="J103" s="43" t="n">
+      <x:c r="L103" s="43" t="n">
         <x:v>0.1675</x:v>
       </x:c>
-      <x:c r="K103" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L103" s="32" t="str">
+      <x:c r="M103" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15253,16 +15560,19 @@
       <x:c r="H104" s="40" t="n">
         <x:v>1165423958</x:v>
       </x:c>
-      <x:c r="I104" s="43" t="n">
+      <x:c r="I104" s="40" t="n">
+        <x:v>1165423958</x:v>
+      </x:c>
+      <x:c r="J104" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K104" s="43" t="n">
         <x:v>1.2519</x:v>
       </x:c>
-      <x:c r="J104" s="43" t="n">
+      <x:c r="L104" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K104" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L104" s="32" t="str">
+      <x:c r="M104" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15291,16 +15601,19 @@
       <x:c r="H105" s="40" t="n">
         <x:v>1151125436</x:v>
       </x:c>
-      <x:c r="I105" s="43" t="n">
+      <x:c r="I105" s="40" t="n">
+        <x:v>1151125436</x:v>
+      </x:c>
+      <x:c r="J105" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K105" s="43" t="n">
         <x:v>1.2381</x:v>
       </x:c>
-      <x:c r="J105" s="43" t="n">
+      <x:c r="L105" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K105" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L105" s="32" t="str">
+      <x:c r="M105" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15329,16 +15642,19 @@
       <x:c r="H106" s="40" t="n">
         <x:v>1148829895</x:v>
       </x:c>
-      <x:c r="I106" s="43" t="n">
+      <x:c r="I106" s="40" t="n">
+        <x:v>1148829895</x:v>
+      </x:c>
+      <x:c r="J106" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K106" s="43" t="n">
         <x:v>1.185</x:v>
       </x:c>
-      <x:c r="J106" s="43" t="n">
+      <x:c r="L106" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K106" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L106" s="32" t="str">
+      <x:c r="M106" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15367,16 +15683,19 @@
       <x:c r="H107" s="40" t="n">
         <x:v>1186966069</x:v>
       </x:c>
-      <x:c r="I107" s="43" t="n">
+      <x:c r="I107" s="40" t="n">
+        <x:v>1186966069</x:v>
+      </x:c>
+      <x:c r="J107" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K107" s="43" t="n">
         <x:v>1.2793</x:v>
       </x:c>
-      <x:c r="J107" s="43" t="n">
+      <x:c r="L107" s="43" t="n">
         <x:v>1.2554</x:v>
       </x:c>
-      <x:c r="K107" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L107" s="32" t="str">
+      <x:c r="M107" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15405,16 +15724,19 @@
       <x:c r="H108" s="40" t="n">
         <x:v>3958912304</x:v>
       </x:c>
-      <x:c r="I108" s="43" t="n">
+      <x:c r="I108" s="40" t="n">
+        <x:v>1380163332</x:v>
+      </x:c>
+      <x:c r="J108" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K108" s="43" t="n">
         <x:v>1.1781</x:v>
       </x:c>
-      <x:c r="J108" s="43" t="n">
+      <x:c r="L108" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K108" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L108" s="32" t="str">
+      <x:c r="M108" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15443,16 +15765,19 @@
       <x:c r="H109" s="40" t="n">
         <x:v>3975895368</x:v>
       </x:c>
-      <x:c r="I109" s="43" t="n">
+      <x:c r="I109" s="40" t="n">
+        <x:v>1397858568</x:v>
+      </x:c>
+      <x:c r="J109" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K109" s="43" t="n">
         <x:v>1.198</x:v>
       </x:c>
-      <x:c r="J109" s="43" t="n">
+      <x:c r="L109" s="43" t="n">
         <x:v>1.1673</x:v>
       </x:c>
-      <x:c r="K109" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L109" s="32" t="str">
+      <x:c r="M109" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15481,16 +15806,19 @@
       <x:c r="H110" s="40" t="n">
         <x:v>381187393</x:v>
       </x:c>
-      <x:c r="I110" s="43" t="n">
+      <x:c r="I110" s="40" t="n">
+        <x:v>-30591888</x:v>
+      </x:c>
+      <x:c r="J110" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K110" s="43" t="n">
         <x:v>-0.047</x:v>
       </x:c>
-      <x:c r="J110" s="43" t="n">
+      <x:c r="L110" s="43" t="n">
         <x:v>0.009000000000000001</x:v>
       </x:c>
-      <x:c r="K110" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L110" s="32" t="str">
+      <x:c r="M110" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15519,16 +15847,19 @@
       <x:c r="H111" s="40" t="n">
         <x:v>333326095</x:v>
       </x:c>
-      <x:c r="I111" s="43" t="n">
+      <x:c r="I111" s="40" t="n">
+        <x:v>-59815011</x:v>
+      </x:c>
+      <x:c r="J111" s="31" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K111" s="43" t="n">
         <x:v>-0.16670000000000001</x:v>
       </x:c>
-      <x:c r="J111" s="43" t="n">
+      <x:c r="L111" s="43" t="n">
         <x:v>0.009000000000000001</x:v>
       </x:c>
-      <x:c r="K111" s="31" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L111" s="32" t="str">
+      <x:c r="M111" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15557,26 +15888,29 @@
       <x:c r="H112" s="41" t="n">
         <x:v>341538111</x:v>
       </x:c>
-      <x:c r="I112" s="44" t="n">
+      <x:c r="I112" s="41" t="n">
+        <x:v>-55332604</x:v>
+      </x:c>
+      <x:c r="J112" s="34" t="str">
+        <x:v>新臺幣元</x:v>
+      </x:c>
+      <x:c r="K112" s="44" t="n">
         <x:v>-0.1462</x:v>
       </x:c>
-      <x:c r="J112" s="44" t="n">
+      <x:c r="L112" s="44" t="n">
         <x:v>0.009000000000000001</x:v>
       </x:c>
-      <x:c r="K112" s="34" t="str">
-        <x:v>新臺幣元</x:v>
-      </x:c>
-      <x:c r="L112" s="35" t="str">
+      <x:c r="M112" s="35" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b058e572abc4751"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R704faca334eb4284"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15593,10 +15927,11 @@
     <x:col min="6" max="6" width="14.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.890000343322754" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="10.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22.219999313354492" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="6" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="6" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -15614,6 +15949,7 @@
       <x:c r="J1" s="4"/>
       <x:c r="K1" s="4"/>
       <x:c r="L1" s="4"/>
+      <x:c r="M1" s="4"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="15" t="str">
@@ -15641,15 +15977,18 @@
         <x:v>目前淨資產</x:v>
       </x:c>
       <x:c r="I3" s="16" t="str">
+        <x:v>委外帳戶當期加/減</x:v>
+      </x:c>
+      <x:c r="J3" s="16" t="str">
+        <x:v>單位</x:v>
+      </x:c>
+      <x:c r="K3" s="16" t="str">
         <x:v>委任至今投資報酬率</x:v>
       </x:c>
-      <x:c r="J3" s="16" t="str">
+      <x:c r="L3" s="16" t="str">
         <x:v>委任至今目標／指標報酬率</x:v>
       </x:c>
-      <x:c r="K3" s="16" t="str">
-        <x:v>單位</x:v>
-      </x:c>
-      <x:c r="L3" s="17" t="str">
+      <x:c r="M3" s="17" t="str">
         <x:v>來源檔案</x:v>
       </x:c>
     </x:row>
@@ -15678,16 +16017,19 @@
       <x:c r="H4" s="39" t="n">
         <x:v>897752897</x:v>
       </x:c>
-      <x:c r="I4" s="42" t="n">
+      <x:c r="I4" s="39" t="n">
+        <x:v>-6520966</x:v>
+      </x:c>
+      <x:c r="J4" s="28" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K4" s="42" t="n">
         <x:v>-0.003</x:v>
       </x:c>
-      <x:c r="J4" s="42" t="n">
+      <x:c r="L4" s="42" t="n">
         <x:v>-0.0048</x:v>
       </x:c>
-      <x:c r="K4" s="28" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L4" s="29" t="str">
+      <x:c r="M4" s="29" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15716,16 +16058,19 @@
       <x:c r="H5" s="40" t="n">
         <x:v>1334569313</x:v>
       </x:c>
-      <x:c r="I5" s="43" t="n">
+      <x:c r="I5" s="40" t="n">
+        <x:v>-7251097</x:v>
+      </x:c>
+      <x:c r="J5" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K5" s="43" t="n">
         <x:v>-0.0031</x:v>
       </x:c>
-      <x:c r="J5" s="43" t="n">
+      <x:c r="L5" s="43" t="n">
         <x:v>-0.0048</x:v>
       </x:c>
-      <x:c r="K5" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L5" s="32" t="str">
+      <x:c r="M5" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15754,16 +16099,19 @@
       <x:c r="H6" s="40" t="n">
         <x:v>2364612047</x:v>
       </x:c>
-      <x:c r="I6" s="43" t="n">
+      <x:c r="I6" s="40" t="n">
+        <x:v>-22907566</x:v>
+      </x:c>
+      <x:c r="J6" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K6" s="43" t="n">
         <x:v>-0.0496</x:v>
       </x:c>
-      <x:c r="J6" s="43" t="n">
+      <x:c r="L6" s="43" t="n">
         <x:v>-0.07490000000000001</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L6" s="32" t="str">
+      <x:c r="M6" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15792,16 +16140,19 @@
       <x:c r="H7" s="40" t="n">
         <x:v>3608745347</x:v>
       </x:c>
-      <x:c r="I7" s="43" t="n">
+      <x:c r="I7" s="40" t="n">
+        <x:v>232055969</x:v>
+      </x:c>
+      <x:c r="J7" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K7" s="43" t="n">
         <x:v>0.8793000000000001</x:v>
       </x:c>
-      <x:c r="J7" s="43" t="n">
+      <x:c r="L7" s="43" t="n">
         <x:v>0.6754000000000001</x:v>
       </x:c>
-      <x:c r="K7" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L7" s="32" t="str">
+      <x:c r="M7" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15830,16 +16181,19 @@
       <x:c r="H8" s="40" t="n">
         <x:v>2656287171</x:v>
       </x:c>
-      <x:c r="I8" s="43" t="n">
+      <x:c r="I8" s="40" t="n">
+        <x:v>6278013</x:v>
+      </x:c>
+      <x:c r="J8" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K8" s="43" t="n">
         <x:v>0.6968000000000001</x:v>
       </x:c>
-      <x:c r="J8" s="43" t="n">
+      <x:c r="L8" s="43" t="n">
         <x:v>0.6754000000000001</x:v>
       </x:c>
-      <x:c r="K8" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L8" s="32" t="str">
+      <x:c r="M8" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15868,16 +16222,19 @@
       <x:c r="H9" s="40" t="n">
         <x:v>1304933202</x:v>
       </x:c>
-      <x:c r="I9" s="43" t="n">
+      <x:c r="I9" s="40" t="n">
+        <x:v>11196846</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K9" s="43" t="n">
         <x:v>0.9876999999999999</x:v>
       </x:c>
-      <x:c r="J9" s="43" t="n">
+      <x:c r="L9" s="43" t="n">
         <x:v>0.882</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L9" s="32" t="str">
+      <x:c r="M9" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15906,16 +16263,19 @@
       <x:c r="H10" s="40" t="n">
         <x:v>2348868079</x:v>
       </x:c>
-      <x:c r="I10" s="43" t="n">
+      <x:c r="I10" s="40" t="n">
+        <x:v>-5498903</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K10" s="43" t="n">
         <x:v>0.8826999999999999</x:v>
       </x:c>
-      <x:c r="J10" s="43" t="n">
+      <x:c r="L10" s="43" t="n">
         <x:v>0.8704999999999999</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L10" s="32" t="str">
+      <x:c r="M10" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15944,16 +16304,19 @@
       <x:c r="H11" s="40" t="n">
         <x:v>3175972208</x:v>
       </x:c>
-      <x:c r="I11" s="43" t="n">
+      <x:c r="I11" s="40" t="n">
+        <x:v>6605173</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K11" s="43" t="n">
         <x:v>0.8973</x:v>
       </x:c>
-      <x:c r="J11" s="43" t="n">
+      <x:c r="L11" s="43" t="n">
         <x:v>0.8704999999999999</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L11" s="32" t="str">
+      <x:c r="M11" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -15982,16 +16345,19 @@
       <x:c r="H12" s="40" t="n">
         <x:v>1714089252</x:v>
       </x:c>
-      <x:c r="I12" s="43" t="n">
+      <x:c r="I12" s="40" t="n">
+        <x:v>1714089252</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K12" s="43" t="n">
         <x:v>0.0183</x:v>
       </x:c>
-      <x:c r="J12" s="43" t="n">
+      <x:c r="L12" s="43" t="n">
         <x:v>0.0174</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L12" s="32" t="str">
+      <x:c r="M12" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16020,16 +16386,19 @@
       <x:c r="H13" s="40" t="n">
         <x:v>1711777799</x:v>
       </x:c>
-      <x:c r="I13" s="43" t="n">
+      <x:c r="I13" s="40" t="n">
+        <x:v>1711777799</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K13" s="43" t="n">
         <x:v>0.0146</x:v>
       </x:c>
-      <x:c r="J13" s="43" t="n">
+      <x:c r="L13" s="43" t="n">
         <x:v>0.0174</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L13" s="32" t="str">
+      <x:c r="M13" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16058,14 +16427,17 @@
       <x:c r="H14" s="40" t="n">
         <x:v>2941839542</x:v>
       </x:c>
-      <x:c r="I14" s="43" t="n">
+      <x:c r="I14" s="40" t="n">
+        <x:v>79438726</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K14" s="43" t="n">
         <x:v>0.1306</x:v>
       </x:c>
-      <x:c r="J14" s="43"/>
-      <x:c r="K14" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L14" s="32" t="str">
+      <x:c r="L14" s="43"/>
+      <x:c r="M14" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16094,14 +16466,17 @@
       <x:c r="H15" s="40" t="n">
         <x:v>1552479450</x:v>
       </x:c>
-      <x:c r="I15" s="43" t="n">
+      <x:c r="I15" s="40" t="n">
+        <x:v>43035694</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K15" s="43" t="n">
         <x:v>0.08070000000000001</x:v>
       </x:c>
-      <x:c r="J15" s="43"/>
-      <x:c r="K15" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L15" s="32" t="str">
+      <x:c r="L15" s="43"/>
+      <x:c r="M15" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16130,16 +16505,19 @@
       <x:c r="H16" s="40" t="n">
         <x:v>769778438</x:v>
       </x:c>
-      <x:c r="I16" s="43" t="n">
+      <x:c r="I16" s="40" t="n">
+        <x:v>-7734260</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K16" s="43" t="n">
         <x:v>0.24969999999999998</x:v>
       </x:c>
-      <x:c r="J16" s="43" t="n">
+      <x:c r="L16" s="43" t="n">
         <x:v>0.2728</x:v>
       </x:c>
-      <x:c r="K16" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L16" s="32" t="str">
+      <x:c r="M16" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16168,16 +16546,19 @@
       <x:c r="H17" s="40" t="n">
         <x:v>1666508211</x:v>
       </x:c>
-      <x:c r="I17" s="43" t="n">
+      <x:c r="I17" s="40" t="n">
+        <x:v>45958505</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K17" s="43" t="n">
         <x:v>0.345</x:v>
       </x:c>
-      <x:c r="J17" s="43" t="n">
+      <x:c r="L17" s="43" t="n">
         <x:v>0.3337</x:v>
       </x:c>
-      <x:c r="K17" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L17" s="32" t="str">
+      <x:c r="M17" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16206,16 +16587,19 @@
       <x:c r="H18" s="40" t="n">
         <x:v>1781352129</x:v>
       </x:c>
-      <x:c r="I18" s="43" t="n">
+      <x:c r="I18" s="40" t="n">
+        <x:v>49415079</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K18" s="43" t="n">
         <x:v>0.3471</x:v>
       </x:c>
-      <x:c r="J18" s="43" t="n">
+      <x:c r="L18" s="43" t="n">
         <x:v>0.3337</x:v>
       </x:c>
-      <x:c r="K18" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L18" s="32" t="str">
+      <x:c r="M18" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16244,16 +16628,19 @@
       <x:c r="H19" s="40" t="n">
         <x:v>2098200969</x:v>
       </x:c>
-      <x:c r="I19" s="43" t="n">
+      <x:c r="I19" s="40" t="n">
+        <x:v>-4941952</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K19" s="43" t="n">
         <x:v>0.1744</x:v>
       </x:c>
-      <x:c r="J19" s="43" t="n">
+      <x:c r="L19" s="43" t="n">
         <x:v>0.5083</x:v>
       </x:c>
-      <x:c r="K19" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L19" s="32" t="str">
+      <x:c r="M19" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16282,16 +16669,19 @@
       <x:c r="H20" s="40" t="n">
         <x:v>1785160367</x:v>
       </x:c>
-      <x:c r="I20" s="43" t="n">
+      <x:c r="I20" s="40" t="n">
+        <x:v>66873759</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K20" s="43" t="n">
         <x:v>0.5401</x:v>
       </x:c>
-      <x:c r="J20" s="43" t="n">
+      <x:c r="L20" s="43" t="n">
         <x:v>0.5083</x:v>
       </x:c>
-      <x:c r="K20" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L20" s="32" t="str">
+      <x:c r="M20" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16320,16 +16710,19 @@
       <x:c r="H21" s="40" t="n">
         <x:v>2290978822</x:v>
       </x:c>
-      <x:c r="I21" s="43" t="n">
+      <x:c r="I21" s="40" t="n">
+        <x:v>76464879</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K21" s="43" t="n">
         <x:v>0.5279</x:v>
       </x:c>
-      <x:c r="J21" s="43" t="n">
+      <x:c r="L21" s="43" t="n">
         <x:v>0.5083</x:v>
       </x:c>
-      <x:c r="K21" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L21" s="32" t="str">
+      <x:c r="M21" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16358,16 +16751,19 @@
       <x:c r="H22" s="40" t="n">
         <x:v>1352096519</x:v>
       </x:c>
-      <x:c r="I22" s="43" t="n">
+      <x:c r="I22" s="40" t="n">
+        <x:v>-15992016</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K22" s="43" t="n">
         <x:v>0.1457</x:v>
       </x:c>
-      <x:c r="J22" s="43" t="n">
+      <x:c r="L22" s="43" t="n">
         <x:v>0.1376</x:v>
       </x:c>
-      <x:c r="K22" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L22" s="32" t="str">
+      <x:c r="M22" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16396,16 +16792,19 @@
       <x:c r="H23" s="40" t="n">
         <x:v>760653316</x:v>
       </x:c>
-      <x:c r="I23" s="43" t="n">
+      <x:c r="I23" s="40" t="n">
+        <x:v>-8033409</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K23" s="43" t="n">
         <x:v>0.1346</x:v>
       </x:c>
-      <x:c r="J23" s="43" t="n">
+      <x:c r="L23" s="43" t="n">
         <x:v>0.1376</x:v>
       </x:c>
-      <x:c r="K23" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L23" s="32" t="str">
+      <x:c r="M23" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16434,16 +16833,19 @@
       <x:c r="H24" s="40" t="n">
         <x:v>1065528056</x:v>
       </x:c>
-      <x:c r="I24" s="43" t="n">
+      <x:c r="I24" s="40" t="n">
+        <x:v>-12213749</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K24" s="43" t="n">
         <x:v>0.1351</x:v>
       </x:c>
-      <x:c r="J24" s="43" t="n">
+      <x:c r="L24" s="43" t="n">
         <x:v>0.1376</x:v>
       </x:c>
-      <x:c r="K24" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L24" s="32" t="str">
+      <x:c r="M24" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16472,16 +16874,19 @@
       <x:c r="H25" s="40" t="n">
         <x:v>3904111203</x:v>
       </x:c>
-      <x:c r="I25" s="43" t="n">
+      <x:c r="I25" s="40" t="n">
+        <x:v>-71469561</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K25" s="43" t="n">
         <x:v>0.2121</x:v>
       </x:c>
-      <x:c r="J25" s="43" t="n">
+      <x:c r="L25" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K25" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L25" s="32" t="str">
+      <x:c r="M25" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16510,16 +16915,19 @@
       <x:c r="H26" s="40" t="n">
         <x:v>3866001108</x:v>
       </x:c>
-      <x:c r="I26" s="43" t="n">
+      <x:c r="I26" s="40" t="n">
+        <x:v>3866001108</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K26" s="43" t="n">
         <x:v>0.20559999999999998</x:v>
       </x:c>
-      <x:c r="J26" s="43" t="n">
+      <x:c r="L26" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K26" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L26" s="32" t="str">
+      <x:c r="M26" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16548,16 +16956,19 @@
       <x:c r="H27" s="40" t="n">
         <x:v>3853735625</x:v>
       </x:c>
-      <x:c r="I27" s="43" t="n">
+      <x:c r="I27" s="40" t="n">
+        <x:v>-68827965</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K27" s="43" t="n">
         <x:v>0.209</x:v>
       </x:c>
-      <x:c r="J27" s="43" t="n">
+      <x:c r="L27" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K27" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L27" s="32" t="str">
+      <x:c r="M27" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16586,16 +16997,19 @@
       <x:c r="H28" s="40" t="n">
         <x:v>1318692011</x:v>
       </x:c>
-      <x:c r="I28" s="43" t="n">
+      <x:c r="I28" s="40" t="n">
+        <x:v>1318692011</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K28" s="43" t="n">
         <x:v>0.1375</x:v>
       </x:c>
-      <x:c r="J28" s="43" t="n">
+      <x:c r="L28" s="43" t="n">
         <x:v>0.1247</x:v>
       </x:c>
-      <x:c r="K28" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L28" s="32" t="str">
+      <x:c r="M28" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16624,16 +17038,19 @@
       <x:c r="H29" s="40" t="n">
         <x:v>1836404740</x:v>
       </x:c>
-      <x:c r="I29" s="43" t="n">
+      <x:c r="I29" s="40" t="n">
+        <x:v>1836404740</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K29" s="43" t="n">
         <x:v>0.1007</x:v>
       </x:c>
-      <x:c r="J29" s="43" t="n">
+      <x:c r="L29" s="43" t="n">
         <x:v>0.1247</x:v>
       </x:c>
-      <x:c r="K29" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L29" s="32" t="str">
+      <x:c r="M29" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16662,16 +17079,19 @@
       <x:c r="H30" s="40" t="n">
         <x:v>1656860388</x:v>
       </x:c>
-      <x:c r="I30" s="43" t="n">
+      <x:c r="I30" s="40" t="n">
+        <x:v>-61990147</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K30" s="43" t="n">
         <x:v>0.7456</x:v>
       </x:c>
-      <x:c r="J30" s="43" t="n">
+      <x:c r="L30" s="43" t="n">
         <x:v>0.6866</x:v>
       </x:c>
-      <x:c r="K30" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L30" s="32" t="str">
+      <x:c r="M30" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16700,16 +17120,19 @@
       <x:c r="H31" s="40" t="n">
         <x:v>1179392915</x:v>
       </x:c>
-      <x:c r="I31" s="43" t="n">
+      <x:c r="I31" s="40" t="n">
+        <x:v>-5865687</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K31" s="43" t="n">
         <x:v>0.9170999999999999</x:v>
       </x:c>
-      <x:c r="J31" s="43" t="n">
+      <x:c r="L31" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K31" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L31" s="32" t="str">
+      <x:c r="M31" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16738,16 +17161,19 @@
       <x:c r="H32" s="40" t="n">
         <x:v>1520309377</x:v>
       </x:c>
-      <x:c r="I32" s="43" t="n">
+      <x:c r="I32" s="40" t="n">
+        <x:v>-1531838</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K32" s="43" t="n">
         <x:v>0.9606999999999999</x:v>
       </x:c>
-      <x:c r="J32" s="43" t="n">
+      <x:c r="L32" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K32" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L32" s="32" t="str">
+      <x:c r="M32" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16776,16 +17202,19 @@
       <x:c r="H33" s="40" t="n">
         <x:v>1538613293</x:v>
       </x:c>
-      <x:c r="I33" s="43" t="n">
+      <x:c r="I33" s="40" t="n">
+        <x:v>-2206522</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K33" s="43" t="n">
         <x:v>0.9578</x:v>
       </x:c>
-      <x:c r="J33" s="43" t="n">
+      <x:c r="L33" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K33" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L33" s="32" t="str">
+      <x:c r="M33" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16814,16 +17243,19 @@
       <x:c r="H34" s="40" t="n">
         <x:v>1408516487</x:v>
       </x:c>
-      <x:c r="I34" s="43" t="n">
+      <x:c r="I34" s="40" t="n">
+        <x:v>-3741370</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K34" s="43" t="n">
         <x:v>0.9377</x:v>
       </x:c>
-      <x:c r="J34" s="43" t="n">
+      <x:c r="L34" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K34" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L34" s="32" t="str">
+      <x:c r="M34" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16852,14 +17284,17 @@
       <x:c r="H35" s="40" t="n">
         <x:v>523380643</x:v>
       </x:c>
-      <x:c r="I35" s="43" t="n">
+      <x:c r="I35" s="40" t="n">
+        <x:v>502276</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K35" s="43" t="n">
         <x:v>0.22469999999999998</x:v>
       </x:c>
-      <x:c r="J35" s="43"/>
-      <x:c r="K35" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L35" s="32" t="str">
+      <x:c r="L35" s="43"/>
+      <x:c r="M35" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16888,14 +17323,17 @@
       <x:c r="H36" s="40" t="n">
         <x:v>1164994046</x:v>
       </x:c>
-      <x:c r="I36" s="43" t="n">
+      <x:c r="I36" s="40" t="n">
+        <x:v>2212877</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K36" s="43" t="n">
         <x:v>0.2735</x:v>
       </x:c>
-      <x:c r="J36" s="43"/>
-      <x:c r="K36" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L36" s="32" t="str">
+      <x:c r="L36" s="43"/>
+      <x:c r="M36" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16924,14 +17362,17 @@
       <x:c r="H37" s="40" t="n">
         <x:v>1287714646</x:v>
       </x:c>
-      <x:c r="I37" s="43" t="n">
+      <x:c r="I37" s="40" t="n">
+        <x:v>-360968</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K37" s="43" t="n">
         <x:v>0.2384</x:v>
       </x:c>
-      <x:c r="J37" s="43"/>
-      <x:c r="K37" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L37" s="32" t="str">
+      <x:c r="L37" s="43"/>
+      <x:c r="M37" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16960,16 +17401,19 @@
       <x:c r="H38" s="40" t="n">
         <x:v>1523316004</x:v>
       </x:c>
-      <x:c r="I38" s="43" t="n">
+      <x:c r="I38" s="40" t="n">
+        <x:v>24254831</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K38" s="43" t="n">
         <x:v>0.6008</x:v>
       </x:c>
-      <x:c r="J38" s="43" t="n">
+      <x:c r="L38" s="43" t="n">
         <x:v>0.4412</x:v>
       </x:c>
-      <x:c r="K38" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L38" s="32" t="str">
+      <x:c r="M38" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -16998,16 +17442,19 @@
       <x:c r="H39" s="40" t="n">
         <x:v>1147513598</x:v>
       </x:c>
-      <x:c r="I39" s="43" t="n">
+      <x:c r="I39" s="40" t="n">
+        <x:v>9050732</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K39" s="43" t="n">
         <x:v>0.3544</x:v>
       </x:c>
-      <x:c r="J39" s="43" t="n">
+      <x:c r="L39" s="43" t="n">
         <x:v>0.4412</x:v>
       </x:c>
-      <x:c r="K39" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L39" s="32" t="str">
+      <x:c r="M39" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17036,16 +17483,19 @@
       <x:c r="H40" s="40" t="n">
         <x:v>1316573361</x:v>
       </x:c>
-      <x:c r="I40" s="43" t="n">
+      <x:c r="I40" s="40" t="n">
+        <x:v>10162178</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K40" s="43" t="n">
         <x:v>0.457</x:v>
       </x:c>
-      <x:c r="J40" s="43" t="n">
+      <x:c r="L40" s="43" t="n">
         <x:v>0.4412</x:v>
       </x:c>
-      <x:c r="K40" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L40" s="32" t="str">
+      <x:c r="M40" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17074,16 +17524,19 @@
       <x:c r="H41" s="40" t="n">
         <x:v>1142750317</x:v>
       </x:c>
-      <x:c r="I41" s="43" t="n">
+      <x:c r="I41" s="40" t="n">
+        <x:v>-536251384</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K41" s="43" t="n">
         <x:v>0.4711</x:v>
       </x:c>
-      <x:c r="J41" s="43" t="n">
+      <x:c r="L41" s="43" t="n">
         <x:v>0.4412</x:v>
       </x:c>
-      <x:c r="K41" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L41" s="32" t="str">
+      <x:c r="M41" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17112,16 +17565,19 @@
       <x:c r="H42" s="40" t="n">
         <x:v>792418771</x:v>
       </x:c>
-      <x:c r="I42" s="43" t="n">
+      <x:c r="I42" s="40" t="n">
+        <x:v>37354910</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K42" s="43" t="n">
         <x:v>0.42229999999999995</x:v>
       </x:c>
-      <x:c r="J42" s="43" t="n">
+      <x:c r="L42" s="43" t="n">
         <x:v>0.4412</x:v>
       </x:c>
-      <x:c r="K42" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L42" s="32" t="str">
+      <x:c r="M42" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17150,16 +17606,19 @@
       <x:c r="H43" s="40" t="n">
         <x:v>697308846</x:v>
       </x:c>
-      <x:c r="I43" s="43" t="n">
+      <x:c r="I43" s="40" t="n">
+        <x:v>31087972</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K43" s="43" t="n">
         <x:v>0.3882</x:v>
       </x:c>
-      <x:c r="J43" s="43" t="n">
+      <x:c r="L43" s="43" t="n">
         <x:v>0.4412</x:v>
       </x:c>
-      <x:c r="K43" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L43" s="32" t="str">
+      <x:c r="M43" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17188,16 +17647,19 @@
       <x:c r="H44" s="40" t="n">
         <x:v>621979937</x:v>
       </x:c>
-      <x:c r="I44" s="43" t="n">
+      <x:c r="I44" s="40" t="n">
+        <x:v>-1057021764</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K44" s="43" t="n">
         <x:v>0.40740000000000004</x:v>
       </x:c>
-      <x:c r="J44" s="43" t="n">
+      <x:c r="L44" s="43" t="n">
         <x:v>0.4412</x:v>
       </x:c>
-      <x:c r="K44" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L44" s="32" t="str">
+      <x:c r="M44" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17226,16 +17688,19 @@
       <x:c r="H45" s="40" t="n">
         <x:v>1049063723</x:v>
       </x:c>
-      <x:c r="I45" s="43" t="n">
+      <x:c r="I45" s="40" t="n">
+        <x:v>-17082600</x:v>
+      </x:c>
+      <x:c r="J45" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K45" s="43" t="n">
         <x:v>-0.009000000000000001</x:v>
       </x:c>
-      <x:c r="J45" s="43" t="n">
+      <x:c r="L45" s="43" t="n">
         <x:v>-0.0070999999999999995</x:v>
       </x:c>
-      <x:c r="K45" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L45" s="32" t="str">
+      <x:c r="M45" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17264,16 +17729,19 @@
       <x:c r="H46" s="40" t="n">
         <x:v>554364692</x:v>
       </x:c>
-      <x:c r="I46" s="43" t="n">
+      <x:c r="I46" s="40" t="n">
+        <x:v>-8893677</x:v>
+      </x:c>
+      <x:c r="J46" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K46" s="43" t="n">
         <x:v>-0.0073</x:v>
       </x:c>
-      <x:c r="J46" s="43" t="n">
+      <x:c r="L46" s="43" t="n">
         <x:v>-0.0070999999999999995</x:v>
       </x:c>
-      <x:c r="K46" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L46" s="32" t="str">
+      <x:c r="M46" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17302,16 +17770,19 @@
       <x:c r="H47" s="40" t="n">
         <x:v>668540853</x:v>
       </x:c>
-      <x:c r="I47" s="43" t="n">
+      <x:c r="I47" s="40" t="n">
+        <x:v>-10700769</x:v>
+      </x:c>
+      <x:c r="J47" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K47" s="43" t="n">
         <x:v>-0.0089</x:v>
       </x:c>
-      <x:c r="J47" s="43" t="n">
+      <x:c r="L47" s="43" t="n">
         <x:v>-0.0070999999999999995</x:v>
       </x:c>
-      <x:c r="K47" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L47" s="32" t="str">
+      <x:c r="M47" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17340,16 +17811,19 @@
       <x:c r="H48" s="40" t="n">
         <x:v>578472486</x:v>
       </x:c>
-      <x:c r="I48" s="43" t="n">
+      <x:c r="I48" s="40" t="n">
+        <x:v>-1988798</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K48" s="43" t="n">
         <x:v>0.3861</x:v>
       </x:c>
-      <x:c r="J48" s="43" t="n">
+      <x:c r="L48" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K48" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L48" s="32" t="str">
+      <x:c r="M48" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17378,16 +17852,19 @@
       <x:c r="H49" s="40" t="n">
         <x:v>957679882</x:v>
       </x:c>
-      <x:c r="I49" s="43" t="n">
+      <x:c r="I49" s="40" t="n">
+        <x:v>-1809574</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K49" s="43" t="n">
         <x:v>0.5249</x:v>
       </x:c>
-      <x:c r="J49" s="43" t="n">
+      <x:c r="L49" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K49" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L49" s="32" t="str">
+      <x:c r="M49" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17416,16 +17893,19 @@
       <x:c r="H50" s="40" t="n">
         <x:v>487745804</x:v>
       </x:c>
-      <x:c r="I50" s="43" t="n">
+      <x:c r="I50" s="40" t="n">
+        <x:v>-5749257</x:v>
+      </x:c>
+      <x:c r="J50" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K50" s="43" t="n">
         <x:v>0.3725</x:v>
       </x:c>
-      <x:c r="J50" s="43" t="n">
+      <x:c r="L50" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K50" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L50" s="32" t="str">
+      <x:c r="M50" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17454,16 +17934,19 @@
       <x:c r="H51" s="40" t="n">
         <x:v>583830731</x:v>
       </x:c>
-      <x:c r="I51" s="43" t="n">
+      <x:c r="I51" s="40" t="n">
+        <x:v>6753960</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K51" s="43" t="n">
         <x:v>0.395</x:v>
       </x:c>
-      <x:c r="J51" s="43" t="n">
+      <x:c r="L51" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K51" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L51" s="32" t="str">
+      <x:c r="M51" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17492,14 +17975,17 @@
       <x:c r="H52" s="40" t="n">
         <x:v>515794235</x:v>
       </x:c>
-      <x:c r="I52" s="43" t="n">
+      <x:c r="I52" s="40" t="n">
+        <x:v>-15067728</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K52" s="43" t="n">
         <x:v>0.2842</x:v>
       </x:c>
-      <x:c r="J52" s="43"/>
-      <x:c r="K52" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L52" s="32" t="str">
+      <x:c r="L52" s="43"/>
+      <x:c r="M52" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17528,14 +18014,17 @@
       <x:c r="H53" s="40" t="n">
         <x:v>487389833</x:v>
       </x:c>
-      <x:c r="I53" s="43" t="n">
+      <x:c r="I53" s="40" t="n">
+        <x:v>-3435319</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K53" s="43" t="n">
         <x:v>0.2163</x:v>
       </x:c>
-      <x:c r="J53" s="43"/>
-      <x:c r="K53" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L53" s="32" t="str">
+      <x:c r="L53" s="43"/>
+      <x:c r="M53" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17564,14 +18053,17 @@
       <x:c r="H54" s="40" t="n">
         <x:v>491940624</x:v>
       </x:c>
-      <x:c r="I54" s="43" t="n">
+      <x:c r="I54" s="40" t="n">
+        <x:v>533187</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K54" s="43" t="n">
         <x:v>0.2234</x:v>
       </x:c>
-      <x:c r="J54" s="43"/>
-      <x:c r="K54" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L54" s="32" t="str">
+      <x:c r="L54" s="43"/>
+      <x:c r="M54" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17600,14 +18092,17 @@
       <x:c r="H55" s="40" t="n">
         <x:v>538651033</x:v>
       </x:c>
-      <x:c r="I55" s="43" t="n">
+      <x:c r="I55" s="40" t="n">
+        <x:v>-97334</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K55" s="43" t="n">
         <x:v>0.3411</x:v>
       </x:c>
-      <x:c r="J55" s="43"/>
-      <x:c r="K55" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L55" s="32" t="str">
+      <x:c r="L55" s="43"/>
+      <x:c r="M55" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17636,14 +18131,17 @@
       <x:c r="H56" s="40" t="n">
         <x:v>509014558</x:v>
       </x:c>
-      <x:c r="I56" s="43" t="n">
+      <x:c r="I56" s="40" t="n">
+        <x:v>-3371138</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K56" s="43" t="n">
         <x:v>0.2576</x:v>
       </x:c>
-      <x:c r="J56" s="43"/>
-      <x:c r="K56" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L56" s="32" t="str">
+      <x:c r="L56" s="43"/>
+      <x:c r="M56" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17672,14 +18170,17 @@
       <x:c r="H57" s="40" t="n">
         <x:v>617340295</x:v>
       </x:c>
-      <x:c r="I57" s="43" t="n">
+      <x:c r="I57" s="40" t="n">
+        <x:v>-8554071</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K57" s="43" t="n">
         <x:v>0.8184999999999999</x:v>
       </x:c>
-      <x:c r="J57" s="43"/>
-      <x:c r="K57" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L57" s="32" t="str">
+      <x:c r="L57" s="43"/>
+      <x:c r="M57" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17708,14 +18209,17 @@
       <x:c r="H58" s="40" t="n">
         <x:v>593041556</x:v>
       </x:c>
-      <x:c r="I58" s="43" t="n">
+      <x:c r="I58" s="40" t="n">
+        <x:v>-6506126</x:v>
+      </x:c>
+      <x:c r="J58" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K58" s="43" t="n">
         <x:v>0.7273000000000001</x:v>
       </x:c>
-      <x:c r="J58" s="43"/>
-      <x:c r="K58" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L58" s="32" t="str">
+      <x:c r="L58" s="43"/>
+      <x:c r="M58" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17744,14 +18248,17 @@
       <x:c r="H59" s="40" t="n">
         <x:v>603262281</x:v>
       </x:c>
-      <x:c r="I59" s="43" t="n">
+      <x:c r="I59" s="40" t="n">
+        <x:v>-3239957</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K59" s="43" t="n">
         <x:v>0.7391</x:v>
       </x:c>
-      <x:c r="J59" s="43"/>
-      <x:c r="K59" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L59" s="32" t="str">
+      <x:c r="L59" s="43"/>
+      <x:c r="M59" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17780,14 +18287,17 @@
       <x:c r="H60" s="40" t="n">
         <x:v>580538915</x:v>
       </x:c>
-      <x:c r="I60" s="43" t="n">
+      <x:c r="I60" s="40" t="n">
+        <x:v>1682150</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K60" s="43" t="n">
         <x:v>0.7005</x:v>
       </x:c>
-      <x:c r="J60" s="43"/>
-      <x:c r="K60" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L60" s="32" t="str">
+      <x:c r="L60" s="43"/>
+      <x:c r="M60" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17816,14 +18326,17 @@
       <x:c r="H61" s="40" t="n">
         <x:v>616317921</x:v>
       </x:c>
-      <x:c r="I61" s="43" t="n">
+      <x:c r="I61" s="40" t="n">
+        <x:v>-5482958</x:v>
+      </x:c>
+      <x:c r="J61" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K61" s="43" t="n">
         <x:v>0.8192</x:v>
       </x:c>
-      <x:c r="J61" s="43"/>
-      <x:c r="K61" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L61" s="32" t="str">
+      <x:c r="L61" s="43"/>
+      <x:c r="M61" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17852,14 +18365,17 @@
       <x:c r="H62" s="40" t="n">
         <x:v>687485218</x:v>
       </x:c>
-      <x:c r="I62" s="43" t="n">
+      <x:c r="I62" s="40" t="n">
+        <x:v>-1989098</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K62" s="43" t="n">
         <x:v>0.20929999999999999</x:v>
       </x:c>
-      <x:c r="J62" s="43"/>
-      <x:c r="K62" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L62" s="32" t="str">
+      <x:c r="L62" s="43"/>
+      <x:c r="M62" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17888,14 +18404,17 @@
       <x:c r="H63" s="40" t="n">
         <x:v>585326949</x:v>
       </x:c>
-      <x:c r="I63" s="43" t="n">
+      <x:c r="I63" s="40" t="n">
+        <x:v>-1842144</x:v>
+      </x:c>
+      <x:c r="J63" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K63" s="43" t="n">
         <x:v>0.19640000000000002</x:v>
       </x:c>
-      <x:c r="J63" s="43"/>
-      <x:c r="K63" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L63" s="32" t="str">
+      <x:c r="L63" s="43"/>
+      <x:c r="M63" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17924,14 +18443,17 @@
       <x:c r="H64" s="40" t="n">
         <x:v>592402750</x:v>
       </x:c>
-      <x:c r="I64" s="43" t="n">
+      <x:c r="I64" s="40" t="n">
+        <x:v>-1333136</x:v>
+      </x:c>
+      <x:c r="J64" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K64" s="43" t="n">
         <x:v>0.2073</x:v>
       </x:c>
-      <x:c r="J64" s="43"/>
-      <x:c r="K64" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L64" s="32" t="str">
+      <x:c r="L64" s="43"/>
+      <x:c r="M64" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17960,14 +18482,17 @@
       <x:c r="H65" s="40" t="n">
         <x:v>688857784</x:v>
       </x:c>
-      <x:c r="I65" s="43" t="n">
+      <x:c r="I65" s="40" t="n">
+        <x:v>2896439</x:v>
+      </x:c>
+      <x:c r="J65" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K65" s="43" t="n">
         <x:v>0.21350000000000002</x:v>
       </x:c>
-      <x:c r="J65" s="43"/>
-      <x:c r="K65" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L65" s="32" t="str">
+      <x:c r="L65" s="43"/>
+      <x:c r="M65" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -17996,14 +18521,17 @@
       <x:c r="H66" s="40" t="n">
         <x:v>557844230</x:v>
       </x:c>
-      <x:c r="I66" s="43" t="n">
+      <x:c r="I66" s="40" t="n">
+        <x:v>112413</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K66" s="43" t="n">
         <x:v>0.126</x:v>
       </x:c>
-      <x:c r="J66" s="43"/>
-      <x:c r="K66" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L66" s="32" t="str">
+      <x:c r="L66" s="43"/>
+      <x:c r="M66" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18032,14 +18560,17 @@
       <x:c r="H67" s="40" t="n">
         <x:v>574633525</x:v>
       </x:c>
-      <x:c r="I67" s="43" t="n">
+      <x:c r="I67" s="40" t="n">
+        <x:v>1135897</x:v>
+      </x:c>
+      <x:c r="J67" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K67" s="43" t="n">
         <x:v>0.177</x:v>
       </x:c>
-      <x:c r="J67" s="43"/>
-      <x:c r="K67" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L67" s="32" t="str">
+      <x:c r="L67" s="43"/>
+      <x:c r="M67" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18068,16 +18599,19 @@
       <x:c r="H68" s="40" t="n">
         <x:v>532527714</x:v>
       </x:c>
-      <x:c r="I68" s="43" t="n">
+      <x:c r="I68" s="40" t="n">
+        <x:v>-508444</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K68" s="43" t="n">
         <x:v>0.38880000000000003</x:v>
       </x:c>
-      <x:c r="J68" s="43" t="n">
+      <x:c r="L68" s="43" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K68" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L68" s="32" t="str">
+      <x:c r="M68" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18106,16 +18640,19 @@
       <x:c r="H69" s="40" t="n">
         <x:v>544159304</x:v>
       </x:c>
-      <x:c r="I69" s="43" t="n">
+      <x:c r="I69" s="40" t="n">
+        <x:v>544159304</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K69" s="43" t="n">
         <x:v>0.433</x:v>
       </x:c>
-      <x:c r="J69" s="43" t="n">
+      <x:c r="L69" s="43" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K69" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L69" s="32" t="str">
+      <x:c r="M69" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18144,16 +18681,19 @@
       <x:c r="H70" s="40" t="n">
         <x:v>546139746</x:v>
       </x:c>
-      <x:c r="I70" s="43" t="n">
+      <x:c r="I70" s="40" t="n">
+        <x:v>1244569</x:v>
+      </x:c>
+      <x:c r="J70" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K70" s="43" t="n">
         <x:v>0.44060000000000005</x:v>
       </x:c>
-      <x:c r="J70" s="43" t="n">
+      <x:c r="L70" s="43" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K70" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L70" s="32" t="str">
+      <x:c r="M70" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18182,16 +18722,19 @@
       <x:c r="H71" s="40" t="n">
         <x:v>546102748</x:v>
       </x:c>
-      <x:c r="I71" s="43" t="n">
+      <x:c r="I71" s="40" t="n">
+        <x:v>671977</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K71" s="43" t="n">
         <x:v>0.4384</x:v>
       </x:c>
-      <x:c r="J71" s="43" t="n">
+      <x:c r="L71" s="43" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K71" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L71" s="32" t="str">
+      <x:c r="M71" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18220,16 +18763,19 @@
       <x:c r="H72" s="40" t="n">
         <x:v>450426531</x:v>
       </x:c>
-      <x:c r="I72" s="43" t="n">
+      <x:c r="I72" s="40" t="n">
+        <x:v>12569454</x:v>
+      </x:c>
+      <x:c r="J72" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K72" s="43" t="n">
         <x:v>0.15439999999999998</x:v>
       </x:c>
-      <x:c r="J72" s="43" t="n">
+      <x:c r="L72" s="43" t="n">
         <x:v>0.1201</x:v>
       </x:c>
-      <x:c r="K72" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L72" s="32" t="str">
+      <x:c r="M72" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18258,16 +18804,19 @@
       <x:c r="H73" s="40" t="n">
         <x:v>458409894</x:v>
       </x:c>
-      <x:c r="I73" s="43" t="n">
+      <x:c r="I73" s="40" t="n">
+        <x:v>12336919</x:v>
+      </x:c>
+      <x:c r="J73" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K73" s="43" t="n">
         <x:v>0.1727</x:v>
       </x:c>
-      <x:c r="J73" s="43" t="n">
+      <x:c r="L73" s="43" t="n">
         <x:v>0.1201</x:v>
       </x:c>
-      <x:c r="K73" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L73" s="32" t="str">
+      <x:c r="M73" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18296,16 +18845,19 @@
       <x:c r="H74" s="40" t="n">
         <x:v>454110042</x:v>
       </x:c>
-      <x:c r="I74" s="43" t="n">
+      <x:c r="I74" s="40" t="n">
+        <x:v>10557301</x:v>
+      </x:c>
+      <x:c r="J74" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K74" s="43" t="n">
         <x:v>0.1631</x:v>
       </x:c>
-      <x:c r="J74" s="43" t="n">
+      <x:c r="L74" s="43" t="n">
         <x:v>0.1201</x:v>
       </x:c>
-      <x:c r="K74" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L74" s="32" t="str">
+      <x:c r="M74" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18334,16 +18886,19 @@
       <x:c r="H75" s="40" t="n">
         <x:v>453176548</x:v>
       </x:c>
-      <x:c r="I75" s="43" t="n">
+      <x:c r="I75" s="40" t="n">
+        <x:v>10798921</x:v>
+      </x:c>
+      <x:c r="J75" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K75" s="43" t="n">
         <x:v>0.15960000000000002</x:v>
       </x:c>
-      <x:c r="J75" s="43" t="n">
+      <x:c r="L75" s="43" t="n">
         <x:v>0.1201</x:v>
       </x:c>
-      <x:c r="K75" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L75" s="32" t="str">
+      <x:c r="M75" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18372,16 +18927,19 @@
       <x:c r="H76" s="40" t="n">
         <x:v>423356755</x:v>
       </x:c>
-      <x:c r="I76" s="43" t="n">
+      <x:c r="I76" s="40" t="n">
+        <x:v>3142782</x:v>
+      </x:c>
+      <x:c r="J76" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K76" s="43" t="n">
         <x:v>0.1117</x:v>
       </x:c>
-      <x:c r="J76" s="43" t="n">
+      <x:c r="L76" s="43" t="n">
         <x:v>0.1043</x:v>
       </x:c>
-      <x:c r="K76" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L76" s="32" t="str">
+      <x:c r="M76" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18410,16 +18968,19 @@
       <x:c r="H77" s="40" t="n">
         <x:v>421747465</x:v>
       </x:c>
-      <x:c r="I77" s="43" t="n">
+      <x:c r="I77" s="40" t="n">
+        <x:v>2810705</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K77" s="43" t="n">
         <x:v>0.1032</x:v>
       </x:c>
-      <x:c r="J77" s="43" t="n">
+      <x:c r="L77" s="43" t="n">
         <x:v>0.1043</x:v>
       </x:c>
-      <x:c r="K77" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L77" s="32" t="str">
+      <x:c r="M77" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18448,16 +19009,19 @@
       <x:c r="H78" s="40" t="n">
         <x:v>421814640</x:v>
       </x:c>
-      <x:c r="I78" s="43" t="n">
+      <x:c r="I78" s="40" t="n">
+        <x:v>2766191</x:v>
+      </x:c>
+      <x:c r="J78" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K78" s="43" t="n">
         <x:v>0.1047</x:v>
       </x:c>
-      <x:c r="J78" s="43" t="n">
+      <x:c r="L78" s="43" t="n">
         <x:v>0.1043</x:v>
       </x:c>
-      <x:c r="K78" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L78" s="32" t="str">
+      <x:c r="M78" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18486,16 +19050,19 @@
       <x:c r="H79" s="40" t="n">
         <x:v>422040147</x:v>
       </x:c>
-      <x:c r="I79" s="43" t="n">
+      <x:c r="I79" s="40" t="n">
+        <x:v>2839858</x:v>
+      </x:c>
+      <x:c r="J79" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K79" s="43" t="n">
         <x:v>0.1054</x:v>
       </x:c>
-      <x:c r="J79" s="43" t="n">
+      <x:c r="L79" s="43" t="n">
         <x:v>0.1043</x:v>
       </x:c>
-      <x:c r="K79" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L79" s="32" t="str">
+      <x:c r="M79" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18524,16 +19091,19 @@
       <x:c r="H80" s="40" t="n">
         <x:v>1000473186</x:v>
       </x:c>
-      <x:c r="I80" s="43" t="n">
+      <x:c r="I80" s="40" t="n">
+        <x:v>-15737222</x:v>
+      </x:c>
+      <x:c r="J80" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K80" s="43" t="n">
         <x:v>0.3284</x:v>
       </x:c>
-      <x:c r="J80" s="43" t="n">
+      <x:c r="L80" s="43" t="n">
         <x:v>0.2753</x:v>
       </x:c>
-      <x:c r="K80" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L80" s="32" t="str">
+      <x:c r="M80" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18562,16 +19132,19 @@
       <x:c r="H81" s="40" t="n">
         <x:v>955925026</x:v>
       </x:c>
-      <x:c r="I81" s="43" t="n">
+      <x:c r="I81" s="40" t="n">
+        <x:v>-9211812</x:v>
+      </x:c>
+      <x:c r="J81" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K81" s="43" t="n">
         <x:v>-0.047599999999999996</x:v>
       </x:c>
-      <x:c r="J81" s="43" t="n">
+      <x:c r="L81" s="43" t="n">
         <x:v>-0.07490000000000001</x:v>
       </x:c>
-      <x:c r="K81" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L81" s="32" t="str">
+      <x:c r="M81" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18600,16 +19173,19 @@
       <x:c r="H82" s="40" t="n">
         <x:v>951725548</x:v>
       </x:c>
-      <x:c r="I82" s="43" t="n">
+      <x:c r="I82" s="40" t="n">
+        <x:v>-7643783</x:v>
+      </x:c>
+      <x:c r="J82" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K82" s="43" t="n">
         <x:v>-0.07769999999999999</x:v>
       </x:c>
-      <x:c r="J82" s="43" t="n">
+      <x:c r="L82" s="43" t="n">
         <x:v>-0.07490000000000001</x:v>
       </x:c>
-      <x:c r="K82" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L82" s="32" t="str">
+      <x:c r="M82" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18638,16 +19214,19 @@
       <x:c r="H83" s="40" t="n">
         <x:v>1504388734</x:v>
       </x:c>
-      <x:c r="I83" s="43" t="n">
+      <x:c r="I83" s="40" t="n">
+        <x:v>-492790883</x:v>
+      </x:c>
+      <x:c r="J83" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K83" s="43" t="n">
         <x:v>0.8691</x:v>
       </x:c>
-      <x:c r="J83" s="43" t="n">
+      <x:c r="L83" s="43" t="n">
         <x:v>0.6754000000000001</x:v>
       </x:c>
-      <x:c r="K83" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L83" s="32" t="str">
+      <x:c r="M83" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18676,14 +19255,17 @@
       <x:c r="H84" s="40" t="n">
         <x:v>388876019</x:v>
       </x:c>
-      <x:c r="I84" s="43" t="n">
+      <x:c r="I84" s="40" t="n">
+        <x:v>3292095</x:v>
+      </x:c>
+      <x:c r="J84" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K84" s="43" t="n">
         <x:v>0.9747</x:v>
       </x:c>
-      <x:c r="J84" s="43"/>
-      <x:c r="K84" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L84" s="32" t="str">
+      <x:c r="L84" s="43"/>
+      <x:c r="M84" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18712,16 +19294,19 @@
       <x:c r="H85" s="40" t="n">
         <x:v>308345333</x:v>
       </x:c>
-      <x:c r="I85" s="43" t="n">
+      <x:c r="I85" s="40" t="n">
+        <x:v>308345333</x:v>
+      </x:c>
+      <x:c r="J85" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K85" s="43" t="n">
         <x:v>0.0151</x:v>
       </x:c>
-      <x:c r="J85" s="43" t="n">
+      <x:c r="L85" s="43" t="n">
         <x:v>0.0174</x:v>
       </x:c>
-      <x:c r="K85" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L85" s="32" t="str">
+      <x:c r="M85" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18750,16 +19335,19 @@
       <x:c r="H86" s="40" t="n">
         <x:v>464380516</x:v>
       </x:c>
-      <x:c r="I86" s="43" t="n">
+      <x:c r="I86" s="40" t="n">
+        <x:v>464380516</x:v>
+      </x:c>
+      <x:c r="J86" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K86" s="43" t="n">
         <x:v>0.018000000000000002</x:v>
       </x:c>
-      <x:c r="J86" s="43" t="n">
+      <x:c r="L86" s="43" t="n">
         <x:v>0.0174</x:v>
       </x:c>
-      <x:c r="K86" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L86" s="32" t="str">
+      <x:c r="M86" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18788,16 +19376,19 @@
       <x:c r="H87" s="40" t="n">
         <x:v>367521178</x:v>
       </x:c>
-      <x:c r="I87" s="43" t="n">
+      <x:c r="I87" s="40" t="n">
+        <x:v>367521178</x:v>
+      </x:c>
+      <x:c r="J87" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K87" s="43" t="n">
         <x:v>0.0175</x:v>
       </x:c>
-      <x:c r="J87" s="43" t="n">
+      <x:c r="L87" s="43" t="n">
         <x:v>0.0174</x:v>
       </x:c>
-      <x:c r="K87" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L87" s="32" t="str">
+      <x:c r="M87" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18826,16 +19417,19 @@
       <x:c r="H88" s="40" t="n">
         <x:v>412290581</x:v>
       </x:c>
-      <x:c r="I88" s="43" t="n">
+      <x:c r="I88" s="40" t="n">
+        <x:v>412290581</x:v>
+      </x:c>
+      <x:c r="J88" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K88" s="43" t="n">
         <x:v>0.016</x:v>
       </x:c>
-      <x:c r="J88" s="43" t="n">
+      <x:c r="L88" s="43" t="n">
         <x:v>0.0174</x:v>
       </x:c>
-      <x:c r="K88" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L88" s="32" t="str">
+      <x:c r="M88" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18864,16 +19458,19 @@
       <x:c r="H89" s="40" t="n">
         <x:v>1013212614</x:v>
       </x:c>
-      <x:c r="I89" s="43" t="n">
+      <x:c r="I89" s="40" t="n">
+        <x:v>28070705</x:v>
+      </x:c>
+      <x:c r="J89" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K89" s="43" t="n">
         <x:v>0.34740000000000004</x:v>
       </x:c>
-      <x:c r="J89" s="43" t="n">
+      <x:c r="L89" s="43" t="n">
         <x:v>0.3337</x:v>
       </x:c>
-      <x:c r="K89" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L89" s="32" t="str">
+      <x:c r="M89" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18902,16 +19499,19 @@
       <x:c r="H90" s="40" t="n">
         <x:v>485988414</x:v>
       </x:c>
-      <x:c r="I90" s="43" t="n">
+      <x:c r="I90" s="40" t="n">
+        <x:v>-1144086</x:v>
+      </x:c>
+      <x:c r="J90" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K90" s="43" t="n">
         <x:v>0.17370000000000002</x:v>
       </x:c>
-      <x:c r="J90" s="43" t="n">
+      <x:c r="L90" s="43" t="n">
         <x:v>0.5083</x:v>
       </x:c>
-      <x:c r="K90" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L90" s="32" t="str">
+      <x:c r="M90" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18940,16 +19540,19 @@
       <x:c r="H91" s="40" t="n">
         <x:v>485100246</x:v>
       </x:c>
-      <x:c r="I91" s="43" t="n">
+      <x:c r="I91" s="40" t="n">
+        <x:v>18202137</x:v>
+      </x:c>
+      <x:c r="J91" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K91" s="43" t="n">
         <x:v>0.5386</x:v>
       </x:c>
-      <x:c r="J91" s="43" t="n">
+      <x:c r="L91" s="43" t="n">
         <x:v>0.5083</x:v>
       </x:c>
-      <x:c r="K91" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L91" s="32" t="str">
+      <x:c r="M91" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -18978,16 +19581,19 @@
       <x:c r="H92" s="40" t="n">
         <x:v>1076341328</x:v>
       </x:c>
-      <x:c r="I92" s="43" t="n">
+      <x:c r="I92" s="40" t="n">
+        <x:v>35929266</x:v>
+      </x:c>
+      <x:c r="J92" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K92" s="43" t="n">
         <x:v>0.5278</x:v>
       </x:c>
-      <x:c r="J92" s="43" t="n">
+      <x:c r="L92" s="43" t="n">
         <x:v>0.5083</x:v>
       </x:c>
-      <x:c r="K92" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L92" s="32" t="str">
+      <x:c r="M92" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19016,16 +19622,19 @@
       <x:c r="H93" s="40" t="n">
         <x:v>1388520134</x:v>
       </x:c>
-      <x:c r="I93" s="43" t="n">
+      <x:c r="I93" s="40" t="n">
+        <x:v>-4372508</x:v>
+      </x:c>
+      <x:c r="J93" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K93" s="43" t="n">
         <x:v>0.4548</x:v>
       </x:c>
-      <x:c r="J93" s="43" t="n">
+      <x:c r="L93" s="43" t="n">
         <x:v>0.4003</x:v>
       </x:c>
-      <x:c r="K93" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L93" s="32" t="str">
+      <x:c r="M93" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19054,14 +19663,17 @@
       <x:c r="H94" s="40" t="n">
         <x:v>801020312</x:v>
       </x:c>
-      <x:c r="I94" s="43" t="n">
+      <x:c r="I94" s="40" t="n">
+        <x:v>17805307</x:v>
+      </x:c>
+      <x:c r="J94" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K94" s="43" t="n">
         <x:v>0.13</x:v>
       </x:c>
-      <x:c r="J94" s="43"/>
-      <x:c r="K94" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L94" s="32" t="str">
+      <x:c r="L94" s="43"/>
+      <x:c r="M94" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19090,14 +19702,17 @@
       <x:c r="H95" s="40" t="n">
         <x:v>275639320</x:v>
       </x:c>
-      <x:c r="I95" s="43" t="n">
+      <x:c r="I95" s="40" t="n">
+        <x:v>275639320</x:v>
+      </x:c>
+      <x:c r="J95" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K95" s="43" t="n">
         <x:v>-0.001</x:v>
       </x:c>
-      <x:c r="J95" s="43"/>
-      <x:c r="K95" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L95" s="32" t="str">
+      <x:c r="L95" s="43"/>
+      <x:c r="M95" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19126,14 +19741,17 @@
       <x:c r="H96" s="40" t="n">
         <x:v>442701115</x:v>
       </x:c>
-      <x:c r="I96" s="43" t="n">
+      <x:c r="I96" s="40" t="n">
+        <x:v>442701115</x:v>
+      </x:c>
+      <x:c r="J96" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K96" s="43" t="n">
         <x:v>0.0049</x:v>
       </x:c>
-      <x:c r="J96" s="43"/>
-      <x:c r="K96" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L96" s="32" t="str">
+      <x:c r="L96" s="43"/>
+      <x:c r="M96" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19162,14 +19780,17 @@
       <x:c r="H97" s="40" t="n">
         <x:v>446332480</x:v>
       </x:c>
-      <x:c r="I97" s="43" t="n">
+      <x:c r="I97" s="40" t="n">
+        <x:v>446332480</x:v>
+      </x:c>
+      <x:c r="J97" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K97" s="43" t="n">
         <x:v>0.0070999999999999995</x:v>
       </x:c>
-      <x:c r="J97" s="43"/>
-      <x:c r="K97" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L97" s="32" t="str">
+      <x:c r="L97" s="43"/>
+      <x:c r="M97" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19198,16 +19819,19 @@
       <x:c r="H98" s="40" t="n">
         <x:v>243246878</x:v>
       </x:c>
-      <x:c r="I98" s="43" t="n">
+      <x:c r="I98" s="40" t="n">
+        <x:v>-903402</x:v>
+      </x:c>
+      <x:c r="J98" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K98" s="43" t="n">
         <x:v>0.9107999999999999</x:v>
       </x:c>
-      <x:c r="J98" s="43" t="n">
+      <x:c r="L98" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K98" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L98" s="32" t="str">
+      <x:c r="M98" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19236,16 +19860,19 @@
       <x:c r="H99" s="40" t="n">
         <x:v>288944122</x:v>
       </x:c>
-      <x:c r="I99" s="43" t="n">
+      <x:c r="I99" s="40" t="n">
+        <x:v>-305339</x:v>
+      </x:c>
+      <x:c r="J99" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K99" s="43" t="n">
         <x:v>0.9586</x:v>
       </x:c>
-      <x:c r="J99" s="43" t="n">
+      <x:c r="L99" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K99" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L99" s="32" t="str">
+      <x:c r="M99" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19274,16 +19901,19 @@
       <x:c r="H100" s="40" t="n">
         <x:v>308803058</x:v>
       </x:c>
-      <x:c r="I100" s="43" t="n">
+      <x:c r="I100" s="40" t="n">
+        <x:v>-423848</x:v>
+      </x:c>
+      <x:c r="J100" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K100" s="43" t="n">
         <x:v>0.9547</x:v>
       </x:c>
-      <x:c r="J100" s="43" t="n">
+      <x:c r="L100" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K100" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L100" s="32" t="str">
+      <x:c r="M100" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19312,16 +19942,19 @@
       <x:c r="H101" s="40" t="n">
         <x:v>306792507</x:v>
       </x:c>
-      <x:c r="I101" s="43" t="n">
+      <x:c r="I101" s="40" t="n">
+        <x:v>-754352</x:v>
+      </x:c>
+      <x:c r="J101" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K101" s="43" t="n">
         <x:v>0.9358</x:v>
       </x:c>
-      <x:c r="J101" s="43" t="n">
+      <x:c r="L101" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K101" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L101" s="32" t="str">
+      <x:c r="M101" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19350,14 +19983,17 @@
       <x:c r="H102" s="40" t="n">
         <x:v>391326795</x:v>
       </x:c>
-      <x:c r="I102" s="43" t="n">
+      <x:c r="I102" s="40" t="n">
+        <x:v>381026</x:v>
+      </x:c>
+      <x:c r="J102" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K102" s="43" t="n">
         <x:v>0.2243</x:v>
       </x:c>
-      <x:c r="J102" s="43"/>
-      <x:c r="K102" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L102" s="32" t="str">
+      <x:c r="L102" s="43"/>
+      <x:c r="M102" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19386,14 +20022,17 @@
       <x:c r="H103" s="40" t="n">
         <x:v>361976287</x:v>
       </x:c>
-      <x:c r="I103" s="43" t="n">
+      <x:c r="I103" s="40" t="n">
+        <x:v>695834</x:v>
+      </x:c>
+      <x:c r="J103" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K103" s="43" t="n">
         <x:v>0.2789</x:v>
       </x:c>
-      <x:c r="J103" s="43"/>
-      <x:c r="K103" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L103" s="32" t="str">
+      <x:c r="L103" s="43"/>
+      <x:c r="M103" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19422,14 +20061,17 @@
       <x:c r="H104" s="40" t="n">
         <x:v>409014201</x:v>
       </x:c>
-      <x:c r="I104" s="43" t="n">
+      <x:c r="I104" s="40" t="n">
+        <x:v>147161</x:v>
+      </x:c>
+      <x:c r="J104" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K104" s="43" t="n">
         <x:v>0.247</x:v>
       </x:c>
-      <x:c r="J104" s="43"/>
-      <x:c r="K104" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L104" s="32" t="str">
+      <x:c r="L104" s="43"/>
+      <x:c r="M104" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19458,14 +20100,17 @@
       <x:c r="H105" s="40" t="n">
         <x:v>187362563</x:v>
       </x:c>
-      <x:c r="I105" s="43" t="n">
+      <x:c r="I105" s="40" t="n">
+        <x:v>3027644</x:v>
+      </x:c>
+      <x:c r="J105" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K105" s="43" t="n">
         <x:v>0.6017</x:v>
       </x:c>
-      <x:c r="J105" s="43"/>
-      <x:c r="K105" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L105" s="32" t="str">
+      <x:c r="L105" s="43"/>
+      <x:c r="M105" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19494,14 +20139,17 @@
       <x:c r="H106" s="40" t="n">
         <x:v>145514023</x:v>
       </x:c>
-      <x:c r="I106" s="43" t="n">
+      <x:c r="I106" s="40" t="n">
+        <x:v>1149442</x:v>
+      </x:c>
+      <x:c r="J106" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K106" s="43" t="n">
         <x:v>0.3539</x:v>
       </x:c>
-      <x:c r="J106" s="43"/>
-      <x:c r="K106" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L106" s="32" t="str">
+      <x:c r="L106" s="43"/>
+      <x:c r="M106" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19530,14 +20178,17 @@
       <x:c r="H107" s="40" t="n">
         <x:v>167820235</x:v>
       </x:c>
-      <x:c r="I107" s="43" t="n">
+      <x:c r="I107" s="40" t="n">
+        <x:v>1264593</x:v>
+      </x:c>
+      <x:c r="J107" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K107" s="43" t="n">
         <x:v>0.4579</x:v>
       </x:c>
-      <x:c r="J107" s="43"/>
-      <x:c r="K107" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L107" s="32" t="str">
+      <x:c r="L107" s="43"/>
+      <x:c r="M107" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19566,16 +20217,19 @@
       <x:c r="H108" s="40" t="n">
         <x:v>82391662</x:v>
       </x:c>
-      <x:c r="I108" s="43" t="n">
+      <x:c r="I108" s="40" t="n">
+        <x:v>-283260</x:v>
+      </x:c>
+      <x:c r="J108" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K108" s="43" t="n">
         <x:v>0.3895</x:v>
       </x:c>
-      <x:c r="J108" s="43" t="n">
+      <x:c r="L108" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K108" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L108" s="32" t="str">
+      <x:c r="M108" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19604,16 +20258,19 @@
       <x:c r="H109" s="40" t="n">
         <x:v>90179012</x:v>
       </x:c>
-      <x:c r="I109" s="43" t="n">
+      <x:c r="I109" s="40" t="n">
+        <x:v>-171763</x:v>
+      </x:c>
+      <x:c r="J109" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K109" s="43" t="n">
         <x:v>0.5423</x:v>
       </x:c>
-      <x:c r="J109" s="43" t="n">
+      <x:c r="L109" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K109" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L109" s="32" t="str">
+      <x:c r="M109" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19642,16 +20299,19 @@
       <x:c r="H110" s="40" t="n">
         <x:v>73920654</x:v>
       </x:c>
-      <x:c r="I110" s="43" t="n">
+      <x:c r="I110" s="40" t="n">
+        <x:v>-869016</x:v>
+      </x:c>
+      <x:c r="J110" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K110" s="43" t="n">
         <x:v>0.38189999999999996</x:v>
       </x:c>
-      <x:c r="J110" s="43" t="n">
+      <x:c r="L110" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K110" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L110" s="32" t="str">
+      <x:c r="M110" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19680,16 +20340,19 @@
       <x:c r="H111" s="40" t="n">
         <x:v>83221636</x:v>
       </x:c>
-      <x:c r="I111" s="43" t="n">
+      <x:c r="I111" s="40" t="n">
+        <x:v>996985</x:v>
+      </x:c>
+      <x:c r="J111" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K111" s="43" t="n">
         <x:v>0.40380000000000005</x:v>
       </x:c>
-      <x:c r="J111" s="43" t="n">
+      <x:c r="L111" s="43" t="n">
         <x:v>0.39909999999999995</x:v>
       </x:c>
-      <x:c r="K111" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L111" s="32" t="str">
+      <x:c r="M111" s="32" t="str">
         <x:v>勞工退休基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19718,16 +20381,19 @@
       <x:c r="H112" s="40" t="n">
         <x:v>1255172172</x:v>
       </x:c>
-      <x:c r="I112" s="43" t="n">
+      <x:c r="I112" s="40" t="n">
+        <x:v>86029794</x:v>
+      </x:c>
+      <x:c r="J112" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K112" s="43" t="n">
         <x:v>0.2121</x:v>
       </x:c>
-      <x:c r="J112" s="43" t="n">
+      <x:c r="L112" s="43" t="n">
         <x:v>0.6374</x:v>
       </x:c>
-      <x:c r="K112" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L112" s="32" t="str">
+      <x:c r="M112" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19756,16 +20422,19 @@
       <x:c r="H113" s="40" t="n">
         <x:v>374599171</x:v>
       </x:c>
-      <x:c r="I113" s="43" t="n">
+      <x:c r="I113" s="40" t="n">
+        <x:v>-1221560</x:v>
+      </x:c>
+      <x:c r="J113" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K113" s="43" t="n">
         <x:v>0.3655</x:v>
       </x:c>
-      <x:c r="J113" s="43" t="n">
+      <x:c r="L113" s="43" t="n">
         <x:v>0.36829999999999996</x:v>
       </x:c>
-      <x:c r="K113" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L113" s="32" t="str">
+      <x:c r="M113" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19794,16 +20463,19 @@
       <x:c r="H114" s="40" t="n">
         <x:v>337505230</x:v>
       </x:c>
-      <x:c r="I114" s="43" t="n">
+      <x:c r="I114" s="40" t="n">
+        <x:v>-2653247</x:v>
+      </x:c>
+      <x:c r="J114" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K114" s="43" t="n">
         <x:v>0.0716</x:v>
       </x:c>
-      <x:c r="J114" s="43" t="n">
+      <x:c r="L114" s="43" t="n">
         <x:v>0.0633</x:v>
       </x:c>
-      <x:c r="K114" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L114" s="32" t="str">
+      <x:c r="M114" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19832,16 +20504,19 @@
       <x:c r="H115" s="40" t="n">
         <x:v>1214682638</x:v>
       </x:c>
-      <x:c r="I115" s="43" t="n">
+      <x:c r="I115" s="40" t="n">
+        <x:v>-11725692</x:v>
+      </x:c>
+      <x:c r="J115" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K115" s="43" t="n">
         <x:v>0.0672</x:v>
       </x:c>
-      <x:c r="J115" s="43" t="n">
+      <x:c r="L115" s="43" t="n">
         <x:v>0.0633</x:v>
       </x:c>
-      <x:c r="K115" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L115" s="32" t="str">
+      <x:c r="M115" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19870,16 +20545,19 @@
       <x:c r="H116" s="40" t="n">
         <x:v>997557132</x:v>
       </x:c>
-      <x:c r="I116" s="43" t="n">
+      <x:c r="I116" s="40" t="n">
+        <x:v>-18297135</x:v>
+      </x:c>
+      <x:c r="J116" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K116" s="43" t="n">
         <x:v>0.2119</x:v>
       </x:c>
-      <x:c r="J116" s="43" t="n">
+      <x:c r="L116" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K116" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L116" s="32" t="str">
+      <x:c r="M116" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19908,16 +20586,19 @@
       <x:c r="H117" s="40" t="n">
         <x:v>988168804</x:v>
       </x:c>
-      <x:c r="I117" s="43" t="n">
+      <x:c r="I117" s="40" t="n">
+        <x:v>-15019704</x:v>
+      </x:c>
+      <x:c r="J117" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K117" s="43" t="n">
         <x:v>0.2057</x:v>
       </x:c>
-      <x:c r="J117" s="43" t="n">
+      <x:c r="L117" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K117" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L117" s="32" t="str">
+      <x:c r="M117" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19946,16 +20627,19 @@
       <x:c r="H118" s="40" t="n">
         <x:v>993985391</x:v>
       </x:c>
-      <x:c r="I118" s="43" t="n">
+      <x:c r="I118" s="40" t="n">
+        <x:v>-17743111</x:v>
+      </x:c>
+      <x:c r="J118" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K118" s="43" t="n">
         <x:v>0.20929999999999999</x:v>
       </x:c>
-      <x:c r="J118" s="43" t="n">
+      <x:c r="L118" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K118" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L118" s="32" t="str">
+      <x:c r="M118" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -19984,16 +20668,19 @@
       <x:c r="H119" s="40" t="n">
         <x:v>475239009</x:v>
       </x:c>
-      <x:c r="I119" s="43" t="n">
+      <x:c r="I119" s="40" t="n">
+        <x:v>9432028</x:v>
+      </x:c>
+      <x:c r="J119" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K119" s="43" t="n">
         <x:v>0.11720000000000001</x:v>
       </x:c>
-      <x:c r="J119" s="43" t="n">
+      <x:c r="L119" s="43" t="n">
         <x:v>0.1247</x:v>
       </x:c>
-      <x:c r="K119" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L119" s="32" t="str">
+      <x:c r="M119" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20022,16 +20709,19 @@
       <x:c r="H120" s="40" t="n">
         <x:v>578473784</x:v>
       </x:c>
-      <x:c r="I120" s="43" t="n">
+      <x:c r="I120" s="40" t="n">
+        <x:v>1973545</x:v>
+      </x:c>
+      <x:c r="J120" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K120" s="43" t="n">
         <x:v>0.1374</x:v>
       </x:c>
-      <x:c r="J120" s="43" t="n">
+      <x:c r="L120" s="43" t="n">
         <x:v>0.1247</x:v>
       </x:c>
-      <x:c r="K120" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L120" s="32" t="str">
+      <x:c r="M120" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20060,16 +20750,19 @@
       <x:c r="H121" s="40" t="n">
         <x:v>511250642</x:v>
       </x:c>
-      <x:c r="I121" s="43" t="n">
+      <x:c r="I121" s="40" t="n">
+        <x:v>-186646</x:v>
+      </x:c>
+      <x:c r="J121" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K121" s="43" t="n">
         <x:v>0.1007</x:v>
       </x:c>
-      <x:c r="J121" s="43" t="n">
+      <x:c r="L121" s="43" t="n">
         <x:v>0.1247</x:v>
       </x:c>
-      <x:c r="K121" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L121" s="32" t="str">
+      <x:c r="M121" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20098,16 +20791,19 @@
       <x:c r="H122" s="40" t="n">
         <x:v>714504487</x:v>
       </x:c>
-      <x:c r="I122" s="43" t="n">
+      <x:c r="I122" s="40" t="n">
+        <x:v>18107712</x:v>
+      </x:c>
+      <x:c r="J122" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K122" s="43" t="n">
         <x:v>0.1392</x:v>
       </x:c>
-      <x:c r="J122" s="43" t="n">
+      <x:c r="L122" s="43" t="n">
         <x:v>0.1307</x:v>
       </x:c>
-      <x:c r="K122" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L122" s="32" t="str">
+      <x:c r="M122" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20136,16 +20832,19 @@
       <x:c r="H123" s="40" t="n">
         <x:v>478192278</x:v>
       </x:c>
-      <x:c r="I123" s="43" t="n">
+      <x:c r="I123" s="40" t="n">
+        <x:v>10642444</x:v>
+      </x:c>
+      <x:c r="J123" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K123" s="43" t="n">
         <x:v>0.1249</x:v>
       </x:c>
-      <x:c r="J123" s="43" t="n">
+      <x:c r="L123" s="43" t="n">
         <x:v>0.1307</x:v>
       </x:c>
-      <x:c r="K123" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L123" s="32" t="str">
+      <x:c r="M123" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20174,14 +20873,17 @@
       <x:c r="H124" s="40" t="n">
         <x:v>431428553</x:v>
       </x:c>
-      <x:c r="I124" s="43" t="n">
+      <x:c r="I124" s="40" t="n">
+        <x:v>431428553</x:v>
+      </x:c>
+      <x:c r="J124" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K124" s="43" t="n">
         <x:v>0.0058</x:v>
       </x:c>
-      <x:c r="J124" s="43"/>
-      <x:c r="K124" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L124" s="32" t="str">
+      <x:c r="L124" s="43"/>
+      <x:c r="M124" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20210,14 +20912,17 @@
       <x:c r="H125" s="40" t="n">
         <x:v>466146222</x:v>
       </x:c>
-      <x:c r="I125" s="43" t="n">
+      <x:c r="I125" s="40" t="n">
+        <x:v>466146222</x:v>
+      </x:c>
+      <x:c r="J125" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K125" s="43" t="n">
         <x:v>0.008</x:v>
       </x:c>
-      <x:c r="J125" s="43"/>
-      <x:c r="K125" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L125" s="32" t="str">
+      <x:c r="L125" s="43"/>
+      <x:c r="M125" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20246,16 +20951,19 @@
       <x:c r="H126" s="40" t="n">
         <x:v>266710574</x:v>
       </x:c>
-      <x:c r="I126" s="43" t="n">
+      <x:c r="I126" s="40" t="n">
+        <x:v>-10002997</x:v>
+      </x:c>
+      <x:c r="J126" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K126" s="43" t="n">
         <x:v>0.755</x:v>
       </x:c>
-      <x:c r="J126" s="43" t="n">
+      <x:c r="L126" s="43" t="n">
         <x:v>0.6866</x:v>
       </x:c>
-      <x:c r="K126" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L126" s="32" t="str">
+      <x:c r="M126" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20284,14 +20992,17 @@
       <x:c r="H127" s="40" t="n">
         <x:v>129828838</x:v>
       </x:c>
-      <x:c r="I127" s="43" t="n">
+      <x:c r="I127" s="40" t="n">
+        <x:v>127284</x:v>
+      </x:c>
+      <x:c r="J127" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K127" s="43" t="n">
         <x:v>0.2249</x:v>
       </x:c>
-      <x:c r="J127" s="43"/>
-      <x:c r="K127" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L127" s="32" t="str">
+      <x:c r="L127" s="43"/>
+      <x:c r="M127" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20320,14 +21031,17 @@
       <x:c r="H128" s="40" t="n">
         <x:v>333870078</x:v>
       </x:c>
-      <x:c r="I128" s="43" t="n">
+      <x:c r="I128" s="40" t="n">
+        <x:v>649752</x:v>
+      </x:c>
+      <x:c r="J128" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K128" s="43" t="n">
         <x:v>0.2776</x:v>
       </x:c>
-      <x:c r="J128" s="43"/>
-      <x:c r="K128" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L128" s="32" t="str">
+      <x:c r="L128" s="43"/>
+      <x:c r="M128" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20356,14 +21070,17 @@
       <x:c r="H129" s="40" t="n">
         <x:v>373139760</x:v>
       </x:c>
-      <x:c r="I129" s="43" t="n">
+      <x:c r="I129" s="40" t="n">
+        <x:v>61623</x:v>
+      </x:c>
+      <x:c r="J129" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K129" s="43" t="n">
         <x:v>0.24670000000000003</x:v>
       </x:c>
-      <x:c r="J129" s="43"/>
-      <x:c r="K129" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L129" s="32" t="str">
+      <x:c r="L129" s="43"/>
+      <x:c r="M129" s="32" t="str">
         <x:v>勞工保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20392,16 +21109,19 @@
       <x:c r="H130" s="40" t="n">
         <x:v>619202327</x:v>
       </x:c>
-      <x:c r="I130" s="43" t="n">
+      <x:c r="I130" s="40" t="n">
+        <x:v>-11343656</x:v>
+      </x:c>
+      <x:c r="J130" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K130" s="43" t="n">
         <x:v>0.2122</x:v>
       </x:c>
-      <x:c r="J130" s="43" t="n">
+      <x:c r="L130" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K130" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L130" s="32" t="str">
+      <x:c r="M130" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20430,16 +21150,19 @@
       <x:c r="H131" s="40" t="n">
         <x:v>612836264</x:v>
       </x:c>
-      <x:c r="I131" s="43" t="n">
+      <x:c r="I131" s="40" t="n">
+        <x:v>-9349078</x:v>
+      </x:c>
+      <x:c r="J131" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K131" s="43" t="n">
         <x:v>0.2054</x:v>
       </x:c>
-      <x:c r="J131" s="43" t="n">
+      <x:c r="L131" s="43" t="n">
         <x:v>0.21989999999999998</x:v>
       </x:c>
-      <x:c r="K131" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L131" s="32" t="str">
+      <x:c r="M131" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20468,16 +21191,19 @@
       <x:c r="H132" s="40" t="n">
         <x:v>430909955</x:v>
       </x:c>
-      <x:c r="I132" s="43" t="n">
+      <x:c r="I132" s="40" t="n">
+        <x:v>10920693</x:v>
+      </x:c>
+      <x:c r="J132" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K132" s="43" t="n">
         <x:v>0.1391</x:v>
       </x:c>
-      <x:c r="J132" s="43" t="n">
+      <x:c r="L132" s="43" t="n">
         <x:v>0.1307</x:v>
       </x:c>
-      <x:c r="K132" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L132" s="32" t="str">
+      <x:c r="M132" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20506,16 +21232,19 @@
       <x:c r="H133" s="40" t="n">
         <x:v>334549088</x:v>
       </x:c>
-      <x:c r="I133" s="43" t="n">
+      <x:c r="I133" s="40" t="n">
+        <x:v>334549088</x:v>
+      </x:c>
+      <x:c r="J133" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K133" s="43" t="n">
         <x:v>-0.0134</x:v>
       </x:c>
-      <x:c r="J133" s="43" t="n">
+      <x:c r="L133" s="43" t="n">
         <x:v>-0.0173</x:v>
       </x:c>
-      <x:c r="K133" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L133" s="32" t="str">
+      <x:c r="M133" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20544,16 +21273,19 @@
       <x:c r="H134" s="40" t="n">
         <x:v>265114862</x:v>
       </x:c>
-      <x:c r="I134" s="43" t="n">
+      <x:c r="I134" s="40" t="n">
+        <x:v>-9882162</x:v>
+      </x:c>
+      <x:c r="J134" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K134" s="43" t="n">
         <x:v>0.7531</x:v>
       </x:c>
-      <x:c r="J134" s="43" t="n">
+      <x:c r="L134" s="43" t="n">
         <x:v>0.6866</x:v>
       </x:c>
-      <x:c r="K134" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L134" s="32" t="str">
+      <x:c r="M134" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20582,16 +21314,19 @@
       <x:c r="H135" s="40" t="n">
         <x:v>304979599</x:v>
       </x:c>
-      <x:c r="I135" s="43" t="n">
+      <x:c r="I135" s="40" t="n">
+        <x:v>-1188805</x:v>
+      </x:c>
+      <x:c r="J135" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K135" s="43" t="n">
         <x:v>0.9148000000000001</x:v>
       </x:c>
-      <x:c r="J135" s="43" t="n">
+      <x:c r="L135" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K135" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L135" s="32" t="str">
+      <x:c r="M135" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20620,16 +21355,19 @@
       <x:c r="H136" s="40" t="n">
         <x:v>311496128</x:v>
       </x:c>
-      <x:c r="I136" s="43" t="n">
+      <x:c r="I136" s="40" t="n">
+        <x:v>-330845</x:v>
+      </x:c>
+      <x:c r="J136" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K136" s="43" t="n">
         <x:v>0.9578</x:v>
       </x:c>
-      <x:c r="J136" s="43" t="n">
+      <x:c r="L136" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K136" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L136" s="32" t="str">
+      <x:c r="M136" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20658,16 +21396,19 @@
       <x:c r="H137" s="40" t="n">
         <x:v>311580226</x:v>
       </x:c>
-      <x:c r="I137" s="43" t="n">
+      <x:c r="I137" s="40" t="n">
+        <x:v>-493569</x:v>
+      </x:c>
+      <x:c r="J137" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K137" s="43" t="n">
         <x:v>0.9549</x:v>
       </x:c>
-      <x:c r="J137" s="43" t="n">
+      <x:c r="L137" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K137" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L137" s="32" t="str">
+      <x:c r="M137" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20696,16 +21437,19 @@
       <x:c r="H138" s="40" t="n">
         <x:v>309819784</x:v>
       </x:c>
-      <x:c r="I138" s="43" t="n">
+      <x:c r="I138" s="40" t="n">
+        <x:v>-813461</x:v>
+      </x:c>
+      <x:c r="J138" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K138" s="43" t="n">
         <x:v>0.9399</x:v>
       </x:c>
-      <x:c r="J138" s="43" t="n">
+      <x:c r="L138" s="43" t="n">
         <x:v>0.914</x:v>
       </x:c>
-      <x:c r="K138" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L138" s="32" t="str">
+      <x:c r="M138" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20734,14 +21478,17 @@
       <x:c r="H139" s="40" t="n">
         <x:v>130862848</x:v>
       </x:c>
-      <x:c r="I139" s="43" t="n">
+      <x:c r="I139" s="40" t="n">
+        <x:v>124527</x:v>
+      </x:c>
+      <x:c r="J139" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K139" s="43" t="n">
         <x:v>0.22469999999999998</x:v>
       </x:c>
-      <x:c r="J139" s="43"/>
-      <x:c r="K139" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L139" s="32" t="str">
+      <x:c r="L139" s="43"/>
+      <x:c r="M139" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20770,14 +21517,17 @@
       <x:c r="H140" s="40" t="n">
         <x:v>174702263</x:v>
       </x:c>
-      <x:c r="I140" s="43" t="n">
+      <x:c r="I140" s="40" t="n">
+        <x:v>342198</x:v>
+      </x:c>
+      <x:c r="J140" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K140" s="43" t="n">
         <x:v>0.2867</x:v>
       </x:c>
-      <x:c r="J140" s="43"/>
-      <x:c r="K140" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L140" s="32" t="str">
+      <x:c r="L140" s="43"/>
+      <x:c r="M140" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20806,14 +21556,17 @@
       <x:c r="H141" s="40" t="n">
         <x:v>319545179</x:v>
       </x:c>
-      <x:c r="I141" s="43" t="n">
+      <x:c r="I141" s="40" t="n">
+        <x:v>142366</x:v>
+      </x:c>
+      <x:c r="J141" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K141" s="43" t="n">
         <x:v>0.2432</x:v>
       </x:c>
-      <x:c r="J141" s="43"/>
-      <x:c r="K141" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L141" s="32" t="str">
+      <x:c r="L141" s="43"/>
+      <x:c r="M141" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20842,14 +21595,17 @@
       <x:c r="H142" s="40" t="n">
         <x:v>257650149</x:v>
       </x:c>
-      <x:c r="I142" s="43" t="n">
+      <x:c r="I142" s="40" t="n">
+        <x:v>4148152</x:v>
+      </x:c>
+      <x:c r="J142" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K142" s="43" t="n">
         <x:v>0.6015999999999999</x:v>
       </x:c>
-      <x:c r="J142" s="43"/>
-      <x:c r="K142" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L142" s="32" t="str">
+      <x:c r="L142" s="43"/>
+      <x:c r="M142" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20878,14 +21634,17 @@
       <x:c r="H143" s="40" t="n">
         <x:v>221410107</x:v>
       </x:c>
-      <x:c r="I143" s="43" t="n">
+      <x:c r="I143" s="40" t="n">
+        <x:v>1745193</x:v>
+      </x:c>
+      <x:c r="J143" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K143" s="43" t="n">
         <x:v>0.3544</x:v>
       </x:c>
-      <x:c r="J143" s="43"/>
-      <x:c r="K143" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L143" s="32" t="str">
+      <x:c r="L143" s="43"/>
+      <x:c r="M143" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20914,14 +21673,17 @@
       <x:c r="H144" s="40" t="n">
         <x:v>234838962</x:v>
       </x:c>
-      <x:c r="I144" s="43" t="n">
+      <x:c r="I144" s="40" t="n">
+        <x:v>1796960</x:v>
+      </x:c>
+      <x:c r="J144" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K144" s="43" t="n">
         <x:v>0.4575</x:v>
       </x:c>
-      <x:c r="J144" s="43"/>
-      <x:c r="K144" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L144" s="32" t="str">
+      <x:c r="L144" s="43"/>
+      <x:c r="M144" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20950,14 +21712,17 @@
       <x:c r="H145" s="40" t="n">
         <x:v>220527203</x:v>
       </x:c>
-      <x:c r="I145" s="43" t="n">
+      <x:c r="I145" s="40" t="n">
+        <x:v>10349727</x:v>
+      </x:c>
+      <x:c r="J145" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K145" s="43" t="n">
         <x:v>0.4728</x:v>
       </x:c>
-      <x:c r="J145" s="43"/>
-      <x:c r="K145" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L145" s="32" t="str">
+      <x:c r="L145" s="43"/>
+      <x:c r="M145" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -20986,16 +21751,19 @@
       <x:c r="H146" s="40" t="n">
         <x:v>169160821</x:v>
       </x:c>
-      <x:c r="I146" s="43" t="n">
+      <x:c r="I146" s="40" t="n">
+        <x:v>-2713085</x:v>
+      </x:c>
+      <x:c r="J146" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K146" s="43" t="n">
         <x:v>-0.009399999999999999</x:v>
       </x:c>
-      <x:c r="J146" s="43" t="n">
+      <x:c r="L146" s="43" t="n">
         <x:v>-0.0070999999999999995</x:v>
       </x:c>
-      <x:c r="K146" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L146" s="32" t="str">
+      <x:c r="M146" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21024,16 +21792,19 @@
       <x:c r="H147" s="40" t="n">
         <x:v>92150680</x:v>
       </x:c>
-      <x:c r="I147" s="43" t="n">
+      <x:c r="I147" s="40" t="n">
+        <x:v>-1474945</x:v>
+      </x:c>
+      <x:c r="J147" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K147" s="43" t="n">
         <x:v>-0.0077</x:v>
       </x:c>
-      <x:c r="J147" s="43" t="n">
+      <x:c r="L147" s="43" t="n">
         <x:v>-0.0070999999999999995</x:v>
       </x:c>
-      <x:c r="K147" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L147" s="32" t="str">
+      <x:c r="M147" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21062,16 +21833,19 @@
       <x:c r="H148" s="40" t="n">
         <x:v>115478381</x:v>
       </x:c>
-      <x:c r="I148" s="43" t="n">
+      <x:c r="I148" s="40" t="n">
+        <x:v>-1835166</x:v>
+      </x:c>
+      <x:c r="J148" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K148" s="43" t="n">
         <x:v>-0.0089</x:v>
       </x:c>
-      <x:c r="J148" s="43" t="n">
+      <x:c r="L148" s="43" t="n">
         <x:v>-0.0070999999999999995</x:v>
       </x:c>
-      <x:c r="K148" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L148" s="32" t="str">
+      <x:c r="M148" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21100,14 +21874,17 @@
       <x:c r="H149" s="40" t="n">
         <x:v>76839686</x:v>
       </x:c>
-      <x:c r="I149" s="43" t="n">
+      <x:c r="I149" s="40" t="n">
+        <x:v>-2121898</x:v>
+      </x:c>
+      <x:c r="J149" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K149" s="43" t="n">
         <x:v>0.2807</x:v>
       </x:c>
-      <x:c r="J149" s="43"/>
-      <x:c r="K149" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L149" s="32" t="str">
+      <x:c r="L149" s="43"/>
+      <x:c r="M149" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21136,14 +21913,17 @@
       <x:c r="H150" s="40" t="n">
         <x:v>72935938</x:v>
       </x:c>
-      <x:c r="I150" s="43" t="n">
+      <x:c r="I150" s="40" t="n">
+        <x:v>-73692729</x:v>
+      </x:c>
+      <x:c r="J150" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K150" s="43" t="n">
         <x:v>0.21559999999999999</x:v>
       </x:c>
-      <x:c r="J150" s="43"/>
-      <x:c r="K150" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L150" s="32" t="str">
+      <x:c r="L150" s="43"/>
+      <x:c r="M150" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21172,14 +21952,17 @@
       <x:c r="H151" s="40" t="n">
         <x:v>146792233</x:v>
       </x:c>
-      <x:c r="I151" s="43" t="n">
+      <x:c r="I151" s="40" t="n">
+        <x:v>163566</x:v>
+      </x:c>
+      <x:c r="J151" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K151" s="43" t="n">
         <x:v>0.22719999999999999</x:v>
       </x:c>
-      <x:c r="J151" s="43"/>
-      <x:c r="K151" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L151" s="32" t="str">
+      <x:c r="L151" s="43"/>
+      <x:c r="M151" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21208,14 +21991,17 @@
       <x:c r="H152" s="40" t="n">
         <x:v>133483168</x:v>
       </x:c>
-      <x:c r="I152" s="43" t="n">
+      <x:c r="I152" s="40" t="n">
+        <x:v>-25400</x:v>
+      </x:c>
+      <x:c r="J152" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K152" s="43" t="n">
         <x:v>0.3414</x:v>
       </x:c>
-      <x:c r="J152" s="43"/>
-      <x:c r="K152" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L152" s="32" t="str">
+      <x:c r="L152" s="43"/>
+      <x:c r="M152" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21244,14 +22030,17 @@
       <x:c r="H153" s="40" t="n">
         <x:v>75654265</x:v>
       </x:c>
-      <x:c r="I153" s="43" t="n">
+      <x:c r="I153" s="40" t="n">
+        <x:v>-485923</x:v>
+      </x:c>
+      <x:c r="J153" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K153" s="43" t="n">
         <x:v>0.2609</x:v>
       </x:c>
-      <x:c r="J153" s="43"/>
-      <x:c r="K153" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L153" s="32" t="str">
+      <x:c r="L153" s="43"/>
+      <x:c r="M153" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21280,16 +22069,19 @@
       <x:c r="H154" s="40" t="n">
         <x:v>89122293</x:v>
       </x:c>
-      <x:c r="I154" s="43" t="n">
+      <x:c r="I154" s="40" t="n">
+        <x:v>-1236575</x:v>
+      </x:c>
+      <x:c r="J154" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K154" s="43" t="n">
         <x:v>0.8256</x:v>
       </x:c>
-      <x:c r="J154" s="43" t="n">
+      <x:c r="L154" s="43" t="n">
         <x:v>0.7315</x:v>
       </x:c>
-      <x:c r="K154" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L154" s="32" t="str">
+      <x:c r="M154" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21318,16 +22110,19 @@
       <x:c r="H155" s="40" t="n">
         <x:v>85570319</x:v>
       </x:c>
-      <x:c r="I155" s="43" t="n">
+      <x:c r="I155" s="40" t="n">
+        <x:v>-950764</x:v>
+      </x:c>
+      <x:c r="J155" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K155" s="43" t="n">
         <x:v>0.7273999999999999</x:v>
       </x:c>
-      <x:c r="J155" s="43" t="n">
+      <x:c r="L155" s="43" t="n">
         <x:v>0.7315</x:v>
       </x:c>
-      <x:c r="K155" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L155" s="32" t="str">
+      <x:c r="M155" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21356,16 +22151,19 @@
       <x:c r="H156" s="40" t="n">
         <x:v>87308547</x:v>
       </x:c>
-      <x:c r="I156" s="43" t="n">
+      <x:c r="I156" s="40" t="n">
+        <x:v>-471520</x:v>
+      </x:c>
+      <x:c r="J156" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K156" s="43" t="n">
         <x:v>0.7509999999999999</x:v>
       </x:c>
-      <x:c r="J156" s="43" t="n">
+      <x:c r="L156" s="43" t="n">
         <x:v>0.7315</x:v>
       </x:c>
-      <x:c r="K156" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L156" s="32" t="str">
+      <x:c r="M156" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21394,16 +22192,19 @@
       <x:c r="H157" s="40" t="n">
         <x:v>84636837</x:v>
       </x:c>
-      <x:c r="I157" s="43" t="n">
+      <x:c r="I157" s="40" t="n">
+        <x:v>241555</x:v>
+      </x:c>
+      <x:c r="J157" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K157" s="43" t="n">
         <x:v>0.7115</x:v>
       </x:c>
-      <x:c r="J157" s="43" t="n">
+      <x:c r="L157" s="43" t="n">
         <x:v>0.7315</x:v>
       </x:c>
-      <x:c r="K157" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L157" s="32" t="str">
+      <x:c r="M157" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21432,16 +22233,19 @@
       <x:c r="H158" s="40" t="n">
         <x:v>88954199</x:v>
       </x:c>
-      <x:c r="I158" s="43" t="n">
+      <x:c r="I158" s="40" t="n">
+        <x:v>-817882</x:v>
+      </x:c>
+      <x:c r="J158" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K158" s="43" t="n">
         <x:v>0.8206</x:v>
       </x:c>
-      <x:c r="J158" s="43" t="n">
+      <x:c r="L158" s="43" t="n">
         <x:v>0.7315</x:v>
       </x:c>
-      <x:c r="K158" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L158" s="32" t="str">
+      <x:c r="M158" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21470,16 +22274,19 @@
       <x:c r="H159" s="40" t="n">
         <x:v>134048105</x:v>
       </x:c>
-      <x:c r="I159" s="43" t="n">
+      <x:c r="I159" s="40" t="n">
+        <x:v>-178481</x:v>
+      </x:c>
+      <x:c r="J159" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K159" s="43" t="n">
         <x:v>0.39659999999999995</x:v>
       </x:c>
-      <x:c r="J159" s="43" t="n">
+      <x:c r="L159" s="43" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K159" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L159" s="32" t="str">
+      <x:c r="M159" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21508,16 +22315,19 @@
       <x:c r="H160" s="40" t="n">
         <x:v>136597280</x:v>
       </x:c>
-      <x:c r="I160" s="43" t="n">
+      <x:c r="I160" s="40" t="n">
+        <x:v>54421</x:v>
+      </x:c>
+      <x:c r="J160" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K160" s="43" t="n">
         <x:v>0.4346</x:v>
       </x:c>
-      <x:c r="J160" s="43" t="n">
+      <x:c r="L160" s="43" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K160" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L160" s="32" t="str">
+      <x:c r="M160" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21546,16 +22356,19 @@
       <x:c r="H161" s="40" t="n">
         <x:v>137179366</x:v>
       </x:c>
-      <x:c r="I161" s="43" t="n">
+      <x:c r="I161" s="40" t="n">
+        <x:v>333074</x:v>
+      </x:c>
+      <x:c r="J161" s="31" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K161" s="43" t="n">
         <x:v>0.44329999999999997</x:v>
       </x:c>
-      <x:c r="J161" s="43" t="n">
+      <x:c r="L161" s="43" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K161" s="31" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L161" s="32" t="str">
+      <x:c r="M161" s="32" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
@@ -21584,26 +22397,29 @@
       <x:c r="H162" s="41" t="n">
         <x:v>136973911</x:v>
       </x:c>
-      <x:c r="I162" s="44" t="n">
+      <x:c r="I162" s="41" t="n">
+        <x:v>235488</x:v>
+      </x:c>
+      <x:c r="J162" s="34" t="str">
+        <x:v>美元</x:v>
+      </x:c>
+      <x:c r="K162" s="44" t="n">
         <x:v>0.4372</x:v>
       </x:c>
-      <x:c r="J162" s="44" t="n">
+      <x:c r="L162" s="44" t="n">
         <x:v>0.4351</x:v>
       </x:c>
-      <x:c r="K162" s="34" t="str">
-        <x:v>美元</x:v>
-      </x:c>
-      <x:c r="L162" s="35" t="str">
+      <x:c r="M162" s="35" t="str">
         <x:v>國民年金保險基金-115年6月.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8486db39e2d4097"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c1608c716f74052"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25246,7 +26062,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2487a1330080420f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf09dafde3ee34229"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27155,7 +27971,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a1b1e73e90b4539"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2313b86a90eb470b"/>
 </x:worksheet>
 </file>
 
@@ -27169,7 +27985,7 @@
     <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="13.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -27237,10 +28053,10 @@
         <x:v>國內委外明細</x:v>
       </x:c>
       <x:c r="C5" s="87" t="str">
-        <x:v>各批次／業者一列</x:v>
+        <x:v>各批次／業者一列，含當期加/減</x:v>
       </x:c>
       <x:c r="D5" s="87" t="str">
-        <x:v>日期、基金、批次、業者、金額、淨資產、兩種報酬率</x:v>
+        <x:v>日期、基金、批次、業者、金額、淨資產、當期加/減、兩種報酬率</x:v>
       </x:c>
       <x:c r="E5" s="87" t="str">
         <x:v>PDF「國內委外投資概況」</x:v>
@@ -27249,7 +28065,7 @@
         <x:v>國內業者彙總</x:v>
       </x:c>
       <x:c r="G5" s="88" t="str">
-        <x:v>新增批次直接新增列</x:v>
+        <x:v>新增批次直接新增列；當期加/減以較上月同帳戶目前淨資產差額計算</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -27260,10 +28076,10 @@
         <x:v>國外委外明細</x:v>
       </x:c>
       <x:c r="C6" s="87" t="str">
-        <x:v>各批次／業者一列</x:v>
+        <x:v>各批次／業者一列，含當期加/減</x:v>
       </x:c>
       <x:c r="D6" s="87" t="str">
-        <x:v>日期、基金、批次、業者、金額、淨資產、兩種報酬率、單位</x:v>
+        <x:v>日期、基金、批次、業者、金額、淨資產、當期加/減、兩種報酬率、單位</x:v>
       </x:c>
       <x:c r="E6" s="87" t="str">
         <x:v>PDF「國外委外投資概況」</x:v>
@@ -27272,7 +28088,7 @@
         <x:v>國外業者彙總</x:v>
       </x:c>
       <x:c r="G6" s="88" t="str">
-        <x:v>保留美元／其他原始幣別，不自行換匯</x:v>
+        <x:v>保留美元／其他原始幣別，不自行換匯；當期加/減以較上月同帳戶目前淨資產差額計算</x:v>
       </x:c>
     </x:row>
     <x:row r="7">

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R8a3bf4082e174351"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R59d5dce839364a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R4f8a68598d094536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R0f1efe0ae0e048a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R6494403083844362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R9cfb42b4cac74470"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R18667a5a83704f61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R8046cfe2223c4784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R2c5da1ebc49f4371"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd9d690488bf34826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R712cff793c084fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rfdf1439ccf4d4651"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R28e19e45e77a40cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Rab2d8c31d9c643a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rc4cb1f0ab88d473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R9698cc44cd9941e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R500c691197ed41d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Reccff047312b4c61"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -589,10 +589,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$V$12:$V$17</c:f>
+              <c:f>'儀表板'!$V$12:$V$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -600,7 +690,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$W$12:$W$17</c:f>
+              <c:f>'儀表板'!$W$12:$W$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -709,10 +799,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$AD$12:$AD$17</c:f>
+              <c:f>'儀表板(美元)'!$AD$12:$AD$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -720,7 +900,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AE$12:$AE$17</c:f>
+              <c:f>'儀表板(美元)'!$AE$12:$AE$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1571,10 +1751,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$X$12:$X$17</c:f>
+              <c:f>'儀表板'!$X$12:$X$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1582,7 +1852,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$Y$12:$Y$17</c:f>
+              <c:f>'儀表板'!$Y$12:$Y$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1691,10 +1961,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$Z$12:$Z$17</c:f>
+              <c:f>'儀表板'!$Z$12:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1702,7 +2062,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AA$12:$AA$17</c:f>
+              <c:f>'儀表板'!$AA$12:$AA$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1811,10 +2171,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$AB$12:$AB$17</c:f>
+              <c:f>'儀表板'!$AB$12:$AB$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1822,7 +2272,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AC$12:$AC$17</c:f>
+              <c:f>'儀表板'!$AC$12:$AC$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1931,10 +2381,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$AD$12:$AD$17</c:f>
+              <c:f>'儀表板'!$AD$12:$AD$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1942,7 +2482,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AE$12:$AE$17</c:f>
+              <c:f>'儀表板'!$AE$12:$AE$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2051,10 +2591,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$V$12:$V$17</c:f>
+              <c:f>'儀表板(美元)'!$V$12:$V$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2062,7 +2692,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$W$12:$W$17</c:f>
+              <c:f>'儀表板(美元)'!$W$12:$W$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2171,10 +2801,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$X$12:$X$17</c:f>
+              <c:f>'儀表板(美元)'!$X$12:$X$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2182,7 +2902,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$Y$12:$Y$17</c:f>
+              <c:f>'儀表板(美元)'!$Y$12:$Y$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2291,10 +3011,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$Z$12:$Z$17</c:f>
+              <c:f>'儀表板(美元)'!$Z$12:$Z$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2302,7 +3112,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AA$12:$AA$17</c:f>
+              <c:f>'儀表板(美元)'!$AA$12:$AA$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2411,10 +3221,100 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$AB$12:$AB$17</c:f>
+              <c:f>'儀表板(美元)'!$AB$12:$AB$27</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2422,7 +3322,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AC$12:$AC$17</c:f>
+              <c:f>'儀表板(美元)'!$AC$12:$AC$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2475,7 +3375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3331e649ded64c98"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R905a40ff0de945f2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2505,7 +3405,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re9824246a1ef4772"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re8e84e7c91bb4e87"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2535,7 +3435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfe229d8294644690"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raff075e4e6a94ebf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2565,7 +3465,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1480dd8b711b41fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5651826484714962"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2595,7 +3495,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdf5639b9b01d4f7e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4e97b0b8b3bf4f98"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2630,7 +3530,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3a302a8396ff4fea"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R966977981ce74a40"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2660,7 +3560,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R562e7195339448f8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R045feacbf19c4d28"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2690,7 +3590,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a415e7a9c6f4b87"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9adaabd040074666"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2720,7 +3620,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e180d1e39364e58"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf00fa6fc94bc4cd1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2750,7 +3650,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R984a82e82480445f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf92c1442f732439f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2785,7 +3685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad80ef66a6a44ae4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R583f8382e45e4b4c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2815,7 +3715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2346a04c5684dd9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0d1abcd5d5e44a7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2845,7 +3745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bbb92b07041434f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra9089d7219a54419"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2875,7 +3775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69c6af376337421f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd6c668e20cfd4394"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3292,7 +4192,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K6" s="59" t="str">
         <x:v>詳見「業者彙總」</x:v>
@@ -3436,7 +4336,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="30" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="B12" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A12)/(100000000)</x:f>
@@ -3471,49 +4371,44 @@
         <x:v>來源與報價時間已註明</x:v>
       </x:c>
       <x:c r="V12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>B12/SUM($B$12:$B$17)</x:f>
-        <x:v>0.15094783444843035</x:v>
+        <x:f>IFERROR(B19/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.08009049818080267</x:v>
       </x:c>
       <x:c r="X12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>C12/SUM($C$12:$C$17)</x:f>
-        <x:v>0.04196663800086938</x:v>
+        <x:f>IFERROR(C19/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.20294689334834715</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>D12/SUM($D$12:$D$17)</x:f>
-        <x:v>0.2302442410279715</x:v>
+        <x:f>IFERROR(D19/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.09830773672574242</x:v>
       </x:c>
       <x:c r="AB12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>E12/SUM($E$12:$E$17)</x:f>
-        <x:v>0.20286466191262167</x:v>
+        <x:f>IFERROR(E19/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.04795105887019382</x:v>
       </x:c>
       <x:c r="AD12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>F12/SUM($F$12:$F$17)</x:f>
-        <x:v>0.153287378016558</x:v>
+        <x:f>IFERROR(F19/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.09545607450479587</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="30" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="B13" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A13)/(100000000)</x:f>
@@ -3536,49 +4431,44 @@
         <x:v>2654.12955439</x:v>
       </x:c>
       <x:c r="V13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>B13/SUM($B$12:$B$17)</x:f>
-        <x:v>0.01758822818174585</x:v>
+        <x:f>IFERROR(B20/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>C13/SUM($C$12:$C$17)</x:f>
-        <x:v>0.0310233266028289</x:v>
+        <x:f>IFERROR(C20/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>D13/SUM($D$12:$D$17)</x:f>
-        <x:v>0.12087622530884248</x:v>
+        <x:f>IFERROR(D20/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>E13/SUM($E$12:$E$17)</x:f>
-        <x:v>0.11071798709436984</x:v>
+        <x:f>IFERROR(E20/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>F13/SUM($F$12:$F$17)</x:f>
-        <x:v>0.038739979856977955</x:v>
+        <x:f>IFERROR(F20/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="30" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="B14" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A14)/(100000000)</x:f>
@@ -3601,369 +4491,524 @@
         <x:v>802.98009492</x:v>
       </x:c>
       <x:c r="V14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>B14/SUM($B$12:$B$17)</x:f>
-        <x:v>0.009661657390232378</x:v>
+        <x:f>IFERROR(B21/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.025587121477121857</x:v>
       </x:c>
       <x:c r="X14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>C14/SUM($C$12:$C$17)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(C21/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.06119948492201287</x:v>
       </x:c>
       <x:c r="Z14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AA14" s="50" t="n">
-        <x:f>D14/SUM($D$12:$D$17)</x:f>
-        <x:v>0.013398942140475737</x:v>
+        <x:f>IFERROR(D21/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.026053089900866026</x:v>
       </x:c>
       <x:c r="AB14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>E14/SUM($E$12:$E$17)</x:f>
-        <x:v>0.043077022827178034</x:v>
+        <x:f>IFERROR(E21/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.0174561842083449</x:v>
       </x:c>
       <x:c r="AD14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>F14/SUM($F$12:$F$17)</x:f>
-        <x:v>0.011720389704150853</x:v>
+        <x:f>IFERROR(F21/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.029328348097442464</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="30" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="B15" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A15)/(100000000)</x:f>
-        <x:v>5962.66506088</x:v>
+        <x:v>11715.97084307</x:v>
       </x:c>
       <x:c r="C15" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A15)/(100000000)</x:f>
-        <x:v>1101.43623315</x:v>
+        <x:v>1838.53928809</x:v>
       </x:c>
       <x:c r="D15" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A15)/(100000000)</x:f>
-        <x:v>948.09693597</x:v>
+        <x:v>684.61127545</x:v>
       </x:c>
       <x:c r="E15" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A15)/(100000000)</x:f>
-        <x:v>431.71984301</x:v>
+        <x:v>1005.75817739</x:v>
       </x:c>
       <x:c r="F15" s="66" t="n">
         <x:f>SUM(B15:E15)</x:f>
-        <x:v>8443.91807301</x:v>
+        <x:v>15244.879584</x:v>
       </x:c>
       <x:c r="V15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>B15/SUM($B$12:$B$17)</x:f>
-        <x:v>0.12480707057684888</x:v>
+        <x:f>IFERROR(B22/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.04215323484379305</x:v>
       </x:c>
       <x:c r="X15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>C15/SUM($C$12:$C$17)</x:f>
-        <x:v>0.15503743923957614</x:v>
+        <x:f>IFERROR(C22/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>D15/SUM($D$12:$D$17)</x:f>
-        <x:v>0.11445900331933233</x:v>
+        <x:f>IFERROR(D22/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.04390044141522057</x:v>
       </x:c>
       <x:c r="AB15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>E15/SUM($E$12:$E$17)</x:f>
-        <x:v>0.08071474376963361</x:v>
+        <x:f>IFERROR(E22/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.06906982845758472</x:v>
       </x:c>
       <x:c r="AD15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>F15/SUM($F$12:$F$17)</x:f>
-        <x:v>0.1232483981504667</x:v>
+        <x:f>IFERROR(F22/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.03969409795326574</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="30" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="B16" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A16)/(100000000)</x:f>
-        <x:v>27460.23486635</x:v>
+        <x:v>5962.66506088</x:v>
       </x:c>
       <x:c r="C16" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A16)/(100000000)</x:f>
-        <x:v>4277.2351502</x:v>
+        <x:v>1101.43623315</x:v>
       </x:c>
       <x:c r="D16" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A16)/(100000000)</x:f>
-        <x:v>2934.47235142</x:v>
+        <x:v>948.09693597</x:v>
       </x:c>
       <x:c r="E16" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A16)/(100000000)</x:f>
-        <x:v>2706.52131922</x:v>
+        <x:v>431.71984301</x:v>
       </x:c>
       <x:c r="F16" s="66" t="n">
         <x:f>SUM(B16:E16)</x:f>
-        <x:v>37378.46368719001</x:v>
+        <x:v>8443.91807301</x:v>
       </x:c>
       <x:c r="V16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="W16" s="50" t="n">
-        <x:f>B16/SUM($B$12:$B$17)</x:f>
-        <x:v>0.5747818192081349</x:v>
+        <x:f>IFERROR(B23/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="Y16" s="50" t="n">
-        <x:f>C16/SUM($C$12:$C$17)</x:f>
-        <x:v>0.602060804569703</x:v>
+        <x:f>IFERROR(C23/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.07236318107912533</x:v>
       </x:c>
       <x:c r="Z16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AA16" s="50" t="n">
-        <x:f>D16/SUM($D$12:$D$17)</x:f>
-        <x:v>0.3542641768671412</x:v>
+        <x:f>IFERROR(D23/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AC16" s="50" t="n">
-        <x:f>E16/SUM($E$12:$E$17)</x:f>
-        <x:v>0.5060137455457031</x:v>
+        <x:f>IFERROR(E23/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AE16" s="50" t="n">
-        <x:f>F16/SUM($F$12:$F$17)</x:f>
-        <x:v>0.5455803496598065</x:v>
+        <x:f>IFERROR(F23/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.00894763287013099</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="30" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="B17" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A17)/(100000000)</x:f>
-        <x:v>5838.75182966</x:v>
+        <x:v>15744.26402328</x:v>
       </x:c>
       <x:c r="C17" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A17)/(100000000)</x:f>
-        <x:v>1207.10845465</x:v>
+        <x:v>2438.69586211</x:v>
       </x:c>
       <x:c r="D17" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A17)/(100000000)</x:f>
-        <x:v>1381.29973312</x:v>
+        <x:v>2249.86107597</x:v>
       </x:c>
       <x:c r="E17" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A17)/(100000000)</x:f>
-        <x:v>302.8003688</x:v>
+        <x:v>1700.76314183</x:v>
       </x:c>
       <x:c r="F17" s="66" t="n">
         <x:f>SUM(B17:E17)</x:f>
-        <x:v>8729.960386230001</x:v>
+        <x:v>22133.584103189998</x:v>
       </x:c>
       <x:c r="V17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="W17" s="50" t="n">
-        <x:f>B17/SUM($B$12:$B$17)</x:f>
-        <x:v>0.1222133901946076</x:v>
+        <x:f>IFERROR(B24/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="Y17" s="50" t="n">
-        <x:f>C17/SUM($C$12:$C$17)</x:f>
-        <x:v>0.16991179158702263</x:v>
+        <x:f>IFERROR(C24/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AA17" s="50" t="n">
-        <x:f>D17/SUM($D$12:$D$17)</x:f>
-        <x:v>0.16675741133623667</x:v>
+        <x:f>IFERROR(D24/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.0009475554586620803</x:v>
       </x:c>
       <x:c r="AB17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AC17" s="50" t="n">
-        <x:f>E17/SUM($E$12:$E$17)</x:f>
-        <x:v>0.05661183885049371</x:v>
+        <x:f>IFERROR(E24/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AE17" s="50" t="n">
-        <x:f>F17/SUM($F$12:$F$17)</x:f>
-        <x:v>0.12742350461203994</x:v>
+        <x:f>IFERROR(F24/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.0001615598458113894</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="30" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="B18" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A18)/(100000000)</x:f>
-        <x:v>4782.91754572</x:v>
+        <x:v>5838.75182966</x:v>
       </x:c>
       <x:c r="C18" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A18)/(100000000)</x:f>
-        <x:v>2438.18801079</x:v>
+        <x:v>1207.10845465</x:v>
       </x:c>
       <x:c r="D18" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A18)/(100000000)</x:f>
-        <x:v>1628.5862642</x:v>
+        <x:v>1381.29973312</x:v>
       </x:c>
       <x:c r="E18" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A18)/(100000000)</x:f>
-        <x:v>424.96498692</x:v>
+        <x:v>302.8003688</x:v>
       </x:c>
       <x:c r="F18" s="66" t="n">
         <x:f>SUM(B18:E18)</x:f>
-        <x:v>9274.65680763</x:v>
+        <x:v>8729.960386230001</x:v>
+      </x:c>
+      <x:c r="V18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="W18" s="50" t="n">
+        <x:f>IFERROR(B25/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="Y18" s="50" t="n">
+        <x:f>IFERROR(C25/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="AA18" s="50" t="n">
+        <x:f>IFERROR(D25/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.0004527288739017158</x:v>
+      </x:c>
+      <x:c r="AB18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="AC18" s="50" t="n">
+        <x:f>IFERROR(E25/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="AE18" s="50" t="n">
+        <x:f>IFERROR(F25/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.00007719105662184733</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="30" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="B19" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A19)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>4782.91754572</x:v>
       </x:c>
       <x:c r="C19" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A19)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>2438.18801079</x:v>
       </x:c>
       <x:c r="D19" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A19)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>1628.5862642</x:v>
       </x:c>
       <x:c r="E19" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A19)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>424.96498692</x:v>
       </x:c>
       <x:c r="F19" s="66" t="n">
         <x:f>SUM(B19:E19)</x:f>
+        <x:v>9274.65680763</x:v>
+      </x:c>
+      <x:c r="V19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="W19" s="50" t="n">
+        <x:f>IFERROR(B26/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="X19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="Y19" s="50" t="n">
+        <x:f>IFERROR(C26/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="AA19" s="50" t="n">
+        <x:f>IFERROR(D26/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.02049930093134865</x:v>
+      </x:c>
+      <x:c r="AB19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="AC19" s="50" t="n">
+        <x:f>IFERROR(E26/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="AE19" s="50" t="n">
+        <x:f>IFERROR(F26/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.0034951662907268884</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="30" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="B20" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A20)/(100000000)</x:f>
-        <x:v>1528.03509826</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A20)/(100000000)</x:f>
-        <x:v>735.24579727</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A20)/(100000000)</x:f>
-        <x:v>431.60086648</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E20" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A20)/(100000000)</x:f>
-        <x:v>154.70496937</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F20" s="66" t="n">
         <x:f>SUM(B20:E20)</x:f>
-        <x:v>2849.5867313800004</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="W20" s="50" t="n">
+        <x:f>IFERROR(B27/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.052170363275692376</x:v>
+      </x:c>
+      <x:c r="X20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="Y20" s="50" t="n">
+        <x:f>IFERROR(C27/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.07214944417511744</x:v>
+      </x:c>
+      <x:c r="Z20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="AA20" s="50" t="n">
+        <x:f>IFERROR(D27/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.3098279686321394</x:v>
+      </x:c>
+      <x:c r="AB20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="AC20" s="50" t="n">
+        <x:f>IFERROR(E27/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.26199942183961406</x:v>
+      </x:c>
+      <x:c r="AD20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="AE20" s="50" t="n">
+        <x:f>IFERROR(F27/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.11771113488688957</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="30" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="B21" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A21)/(100000000)</x:f>
-        <x:v>2517.34539206</x:v>
+        <x:v>1528.03509826</x:v>
       </x:c>
       <x:c r="C21" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A21)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>735.24579727</x:v>
       </x:c>
       <x:c r="D21" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A21)/(100000000)</x:f>
-        <x:v>727.26377661</x:v>
+        <x:v>431.60086648</x:v>
       </x:c>
       <x:c r="E21" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A21)/(100000000)</x:f>
-        <x:v>612.12952203</x:v>
+        <x:v>154.70496937</x:v>
       </x:c>
       <x:c r="F21" s="66" t="n">
         <x:f>SUM(B21:E21)</x:f>
-        <x:v>3856.7386907</x:v>
+        <x:v>2849.5867313800004</x:v>
+      </x:c>
+      <x:c r="V21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="W21" s="50" t="n">
+        <x:f>IFERROR(B12/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.12075808373788141</x:v>
+      </x:c>
+      <x:c r="X21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="Y21" s="50" t="n">
+        <x:f>IFERROR(C12/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.02481659353415637</x:v>
+      </x:c>
+      <x:c r="Z21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AA21" s="50" t="n">
+        <x:f>IFERROR(D12/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.11512469419841453</x:v>
+      </x:c>
+      <x:c r="AB21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AC21" s="50" t="n">
+        <x:f>IFERROR(E12/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.1224335921276509</x:v>
+      </x:c>
+      <x:c r="AD21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AE21" s="50" t="n">
+        <x:f>IFERROR(F12/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.10808734407200997</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="30" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="B22" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A22)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>2517.34539206</x:v>
       </x:c>
       <x:c r="C22" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A22)/(100000000)</x:f>
-        <x:v>869.36556465</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A22)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>727.26377661</x:v>
       </x:c>
       <x:c r="E22" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A22)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>612.12952203</x:v>
       </x:c>
       <x:c r="F22" s="66" t="n">
         <x:f>SUM(B22:E22)</x:f>
-        <x:v>869.36556465</x:v>
+        <x:v>3856.7386907</x:v>
+      </x:c>
+      <x:c r="V22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="W22" s="50" t="n">
+        <x:f>IFERROR(B13/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.01407056112684972</x:v>
+      </x:c>
+      <x:c r="X22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="Y22" s="50" t="n">
+        <x:f>IFERROR(C13/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.018345364867298538</x:v>
+      </x:c>
+      <x:c r="Z22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AA22" s="50" t="n">
+        <x:f>IFERROR(D13/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.06043946381637647</x:v>
+      </x:c>
+      <x:c r="AB22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AC22" s="50" t="n">
+        <x:f>IFERROR(E13/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.06682090781757392</x:v>
+      </x:c>
+      <x:c r="AD22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AE22" s="50" t="n">
+        <x:f>IFERROR(F13/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.027316675295284924</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="30" t="str">
-        <x:v>房屋及土地</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="B23" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A23)/(100000000)</x:f>
@@ -3971,11 +5016,11 @@
       </x:c>
       <x:c r="C23" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A23)/(100000000)</x:f>
-        <x:v>0</x:v>
+        <x:v>869.36556465</x:v>
       </x:c>
       <x:c r="D23" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A23)/(100000000)</x:f>
-        <x:v>15.69739937</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E23" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A23)/(100000000)</x:f>
@@ -3983,12 +5028,47 @@
       </x:c>
       <x:c r="F23" s="66" t="n">
         <x:f>SUM(B23:E23)</x:f>
-        <x:v>15.69739937</x:v>
+        <x:v>869.36556465</x:v>
+      </x:c>
+      <x:c r="V23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="W23" s="50" t="n">
+        <x:f>IFERROR(B14/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.007729314146437791</x:v>
+      </x:c>
+      <x:c r="X23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="Y23" s="50" t="n">
+        <x:f>IFERROR(C14/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AA23" s="50" t="n">
+        <x:f>IFERROR(D14/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.006699620844445446</x:v>
+      </x:c>
+      <x:c r="AB23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AC23" s="50" t="n">
+        <x:f>IFERROR(E14/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.025997995871591892</x:v>
+      </x:c>
+      <x:c r="AD23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AE23" s="50" t="n">
+        <x:f>IFERROR(F14/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.008264384263091475</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="30" t="str">
-        <x:v>政府或公營事業貸款</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="B24" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A24)/(100000000)</x:f>
@@ -4000,7 +5080,7 @@
       </x:c>
       <x:c r="D24" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A24)/(100000000)</x:f>
-        <x:v>7.5</x:v>
+        <x:v>15.69739937</x:v>
       </x:c>
       <x:c r="E24" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A24)/(100000000)</x:f>
@@ -4008,12 +5088,47 @@
       </x:c>
       <x:c r="F24" s="66" t="n">
         <x:f>SUM(B24:E24)</x:f>
-        <x:v>7.5</x:v>
+        <x:v>15.69739937</x:v>
+      </x:c>
+      <x:c r="V24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="W24" s="50" t="n">
+        <x:f>IFERROR(B15/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.19618526402005568</x:v>
+      </x:c>
+      <x:c r="X24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="Y24" s="50" t="n">
+        <x:f>IFERROR(C15/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.15303407086143878</x:v>
+      </x:c>
+      <x:c r="Z24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="AA24" s="50" t="n">
+        <x:f>IFERROR(D15/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.04132577223931945</x:v>
+      </x:c>
+      <x:c r="AB24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="AC24" s="50" t="n">
+        <x:f>IFERROR(E15/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.11348504243312058</x:v>
+      </x:c>
+      <x:c r="AD24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="AE24" s="50" t="n">
+        <x:f>IFERROR(F15/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.15690244842157178</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="30" t="str">
-        <x:v>被保險人貸款</x:v>
+        <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="B25" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A25)/(100000000)</x:f>
@@ -4025,7 +5140,7 @@
       </x:c>
       <x:c r="D25" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A25)/(100000000)</x:f>
-        <x:v>339.59565172</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="E25" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A25)/(100000000)</x:f>
@@ -4033,56 +5148,186 @@
       </x:c>
       <x:c r="F25" s="66" t="n">
         <x:f>SUM(B25:E25)</x:f>
-        <x:v>339.59565172</x:v>
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="V25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="W25" s="50" t="n">
+        <x:f>IFERROR(B16/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.09984550447424796</x:v>
+      </x:c>
+      <x:c r="X25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="Y25" s="50" t="n">
+        <x:f>IFERROR(C16/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.0916799938109248</x:v>
+      </x:c>
+      <x:c r="Z25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AA25" s="50" t="n">
+        <x:f>IFERROR(D16/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.05723078108951537</x:v>
+      </x:c>
+      <x:c r="AB25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AC25" s="50" t="n">
+        <x:f>IFERROR(E16/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.04871324519612813</x:v>
+      </x:c>
+      <x:c r="AD25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AE25" s="50" t="n">
+        <x:f>IFERROR(F16/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.08690599441119398</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="30" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
+        <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="B26" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A26)/(100000000)</x:f>
-        <x:v>3115.55741999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A26)/(100000000)</x:f>
-        <x:v>866.7977463</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A26)/(100000000)</x:f>
-        <x:v>5132.67409855</x:v>
+        <x:v>339.59565172</x:v>
       </x:c>
       <x:c r="E26" s="65" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A26)/(100000000)</x:f>
-        <x:v>2321.96292425</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F26" s="66" t="n">
         <x:f>SUM(B26:E26)</x:f>
+        <x:v>339.59565172</x:v>
+      </x:c>
+      <x:c r="V26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="W26" s="50" t="n">
+        <x:f>IFERROR(B17/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.26363949139013715</x:v>
+      </x:c>
+      <x:c r="X26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="Y26" s="50" t="n">
+        <x:f>IFERROR(C17/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.2029891652515887</x:v>
+      </x:c>
+      <x:c r="Z26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AA26" s="50" t="n">
+        <x:f>IFERROR(D17/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.13581027618122676</x:v>
+      </x:c>
+      <x:c r="AB26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AC26" s="50" t="n">
+        <x:f>IFERROR(E17/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.1919061476786995</x:v>
+      </x:c>
+      <x:c r="AD26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AE26" s="50" t="n">
+        <x:f>IFERROR(F17/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.22780196583383455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="30" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="B27" s="65" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+        <x:v>3115.55741999</x:v>
+      </x:c>
+      <x:c r="C27" s="65" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+        <x:v>866.7977463</x:v>
+      </x:c>
+      <x:c r="D27" s="65" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+        <x:v>5132.67409855</x:v>
+      </x:c>
+      <x:c r="E27" s="65" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+        <x:v>2321.96292425</x:v>
+      </x:c>
+      <x:c r="F27" s="66" t="n">
+        <x:f>SUM(B27:E27)</x:f>
         <x:v>11436.992189089999</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="33" t="str">
+      <x:c r="V27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="W27" s="50" t="n">
+        <x:f>IFERROR(B18/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.09777056332698032</x:v>
+      </x:c>
+      <x:c r="X27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="Y27" s="50" t="n">
+        <x:f>IFERROR(C18/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.10047580814998996</x:v>
+      </x:c>
+      <x:c r="Z27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AA27" s="50" t="n">
+        <x:f>IFERROR(D18/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.08338056969282108</x:v>
+      </x:c>
+      <x:c r="AB27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AC27" s="50" t="n">
+        <x:f>IFERROR(E18/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.03416657549949762</x:v>
+      </x:c>
+      <x:c r="AD27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AE27" s="50" t="n">
+        <x:f>IFERROR(F18/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.08984998219732857</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="33" t="str">
         <x:v>國外投資</x:v>
       </x:c>
-      <x:c r="B27" s="67" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+      <x:c r="B28" s="67" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A28)/(100000000)</x:f>
         <x:v>8513.40644551</x:v>
       </x:c>
-      <x:c r="C27" s="67" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+      <x:c r="C28" s="67" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A28)/(100000000)</x:f>
         <x:v>518.54437267</x:v>
       </x:c>
-      <x:c r="D27" s="67" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+      <x:c r="D28" s="67" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A28)/(100000000)</x:f>
         <x:v>3019.41939259</x:v>
       </x:c>
-      <x:c r="E27" s="67" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A27)/(100000000)</x:f>
+      <x:c r="E28" s="67" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A28)/(100000000)</x:f>
         <x:v>1907.66953274</x:v>
       </x:c>
-      <x:c r="F27" s="68" t="n">
-        <x:f>SUM(B27:E27)</x:f>
+      <x:c r="F28" s="68" t="n">
+        <x:f>SUM(B28:E28)</x:f>
         <x:v>13959.039743509999</x:v>
       </x:c>
     </x:row>
@@ -4092,7 +5337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc88082f1483c4c99"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17f8b8e6b71c4f77"/>
 </x:worksheet>
 </file>
 
@@ -4234,7 +5479,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K6" s="59" t="str">
         <x:v>詳見「業者彙總」</x:v>
@@ -4378,7 +5623,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="30" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="B12" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A12)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4413,49 +5658,44 @@
         <x:v>來源與報價時間已註明</x:v>
       </x:c>
       <x:c r="V12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>B12/SUM($B$12:$B$17)</x:f>
-        <x:v>0.15094783444843038</x:v>
+        <x:f>IFERROR(B19/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.08591007743801093</x:v>
       </x:c>
       <x:c r="X12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>C12/SUM($C$12:$C$17)</x:f>
-        <x:v>0.04196663800086938</x:v>
+        <x:f>IFERROR(C19/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.11349116086939169</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>D12/SUM($D$12:$D$17)</x:f>
-        <x:v>0.2302442410279715</x:v>
+        <x:f>IFERROR(D19/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.1057019622523328</x:v>
       </x:c>
       <x:c r="AB12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>E12/SUM($E$12:$E$17)</x:f>
-        <x:v>0.20286466191262167</x:v>
+        <x:f>IFERROR(E19/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.05249307537496133</x:v>
       </x:c>
       <x:c r="AD12" t="str">
-        <x:f>A12</x:f>
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>F12/SUM($F$12:$F$17)</x:f>
-        <x:v>0.15328737801655803</x:v>
+        <x:f>IFERROR(F19/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.10253316430655338</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="30" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="B13" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A13)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4478,49 +5718,44 @@
         <x:v>8.30843498009078</x:v>
       </x:c>
       <x:c r="V13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>B13/SUM($B$12:$B$17)</x:f>
-        <x:v>0.017588228181745852</x:v>
+        <x:f>IFERROR(B20/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>C13/SUM($C$12:$C$17)</x:f>
-        <x:v>0.031023326602828895</x:v>
+        <x:f>IFERROR(C20/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>D13/SUM($D$12:$D$17)</x:f>
-        <x:v>0.1208762253088425</x:v>
+        <x:f>IFERROR(D20/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>E13/SUM($E$12:$E$17)</x:f>
-        <x:v>0.11071798709436984</x:v>
+        <x:f>IFERROR(E20/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD13" t="str">
-        <x:f>A13</x:f>
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>F13/SUM($F$12:$F$17)</x:f>
-        <x:v>0.038739979856977955</x:v>
+        <x:f>IFERROR(F20/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="30" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="B14" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A14)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4543,289 +5778,339 @@
         <x:v>2.513633103521678</x:v>
       </x:c>
       <x:c r="V14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>B14/SUM($B$12:$B$17)</x:f>
-        <x:v>0.00966165739023238</x:v>
+        <x:f>IFERROR(B21/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>C14/SUM($C$12:$C$17)</x:f>
+        <x:f>IFERROR(C21/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.475007680466909</x:v>
+      </x:c>
+      <x:c r="Z14" t="str">
+        <x:v>短期票券</x:v>
+      </x:c>
+      <x:c r="AA14" s="50" t="n">
+        <x:f>IFERROR(D21/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Z14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
-      </x:c>
-      <x:c r="AA14" s="50" t="n">
-        <x:f>D14/SUM($D$12:$D$17)</x:f>
-        <x:v>0.013398942140475737</x:v>
-      </x:c>
       <x:c r="AB14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>E14/SUM($E$12:$E$17)</x:f>
-        <x:v>0.04307702282717804</x:v>
+        <x:f>IFERROR(E21/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD14" t="str">
-        <x:f>A14</x:f>
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>F14/SUM($F$12:$F$17)</x:f>
-        <x:v>0.011720389704150853</x:v>
+        <x:f>IFERROR(F21/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="30" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="B15" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A15)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>18.665409487807167</x:v>
+        <x:v>36.67544480535295</x:v>
       </x:c>
       <x:c r="C15" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A15)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>3.447914331350759</x:v>
+        <x:v>5.755327243981844</x:v>
       </x:c>
       <x:c r="D15" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A15)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>2.9679040099233056</x:v>
+        <x:v>2.143093678040382</x:v>
       </x:c>
       <x:c r="E15" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A15)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>1.3514473094694006</x:v>
+        <x:v>3.1484056265143217</x:v>
       </x:c>
       <x:c r="F15" s="75" t="n">
         <x:f>SUM(B15:E15)</x:f>
-        <x:v>26.432675138550632</x:v>
+        <x:v>47.7222713538895</x:v>
       </x:c>
       <x:c r="V15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>B15/SUM($B$12:$B$17)</x:f>
-        <x:v>0.1248070705768489</x:v>
+        <x:f>IFERROR(B22/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>C15/SUM($C$12:$C$17)</x:f>
-        <x:v>0.15503743923957616</x:v>
+        <x:f>IFERROR(C22/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>D15/SUM($D$12:$D$17)</x:f>
-        <x:v>0.11445900331933233</x:v>
+        <x:f>IFERROR(D22/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>E15/SUM($E$12:$E$17)</x:f>
-        <x:v>0.08071474376963363</x:v>
+        <x:f>IFERROR(E22/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD15" t="str">
-        <x:f>A15</x:f>
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>F15/SUM($F$12:$F$17)</x:f>
-        <x:v>0.12324839815046672</x:v>
+        <x:f>IFERROR(F22/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="30" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="B16" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A16)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>85.96097939067147</x:v>
+        <x:v>18.665409487807167</x:v>
       </x:c>
       <x:c r="C16" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A16)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>13.389372828924714</x:v>
+        <x:v>3.447914331350759</x:v>
       </x:c>
       <x:c r="D16" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A16)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>9.186014560713726</x:v>
+        <x:v>2.9679040099233056</x:v>
       </x:c>
       <x:c r="E16" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A16)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>8.472441130755987</x:v>
+        <x:v>1.3514473094694006</x:v>
       </x:c>
       <x:c r="F16" s="75" t="n">
         <x:f>SUM(B16:E16)</x:f>
-        <x:v>117.00880791106589</x:v>
+        <x:v>26.432675138550632</x:v>
       </x:c>
       <x:c r="V16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="W16" s="50" t="n">
-        <x:f>B16/SUM($B$12:$B$17)</x:f>
-        <x:v>0.574781819208135</x:v>
+        <x:f>IFERROR(B23/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="Y16" s="50" t="n">
-        <x:f>C16/SUM($C$12:$C$17)</x:f>
-        <x:v>0.6020608045697029</x:v>
+        <x:f>IFERROR(C23/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.040466652577802666</x:v>
       </x:c>
       <x:c r="Z16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AA16" s="50" t="n">
-        <x:f>D16/SUM($D$12:$D$17)</x:f>
-        <x:v>0.3542641768671412</x:v>
+        <x:f>IFERROR(D23/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AB16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AC16" s="50" t="n">
-        <x:f>E16/SUM($E$12:$E$17)</x:f>
-        <x:v>0.5060137455457032</x:v>
+        <x:f>IFERROR(E23/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD16" t="str">
-        <x:f>A16</x:f>
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AE16" s="50" t="n">
-        <x:f>F16/SUM($F$12:$F$17)</x:f>
-        <x:v>0.5455803496598065</x:v>
+        <x:f>IFERROR(F23/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.00961100816252155</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="30" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="B17" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A17)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>18.27751394478009</x:v>
+        <x:v>49.285534585318516</x:v>
       </x:c>
       <x:c r="C17" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A17)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>3.778708576146502</x:v>
+        <x:v>7.6340455849428706</x:v>
       </x:c>
       <x:c r="D17" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A17)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>4.3239935298794805</x:v>
+        <x:v>7.042920882673345</x:v>
       </x:c>
       <x:c r="E17" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A17)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0.9478803218030991</x:v>
+        <x:v>5.324035504241666</x:v>
       </x:c>
       <x:c r="F17" s="75" t="n">
         <x:f>SUM(B17:E17)</x:f>
-        <x:v>27.32809637260917</x:v>
+        <x:v>69.28653655717639</x:v>
       </x:c>
       <x:c r="V17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="W17" s="50" t="n">
-        <x:f>B17/SUM($B$12:$B$17)</x:f>
-        <x:v>0.12221339019460761</x:v>
+        <x:f>IFERROR(B24/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="Y17" s="50" t="n">
-        <x:f>C17/SUM($C$12:$C$17)</x:f>
-        <x:v>0.16991179158702263</x:v>
+        <x:f>IFERROR(C24/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AA17" s="50" t="n">
-        <x:f>D17/SUM($D$12:$D$17)</x:f>
-        <x:v>0.1667574113362367</x:v>
+        <x:f>IFERROR(D24/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.0010188259302816812</x:v>
       </x:c>
       <x:c r="AB17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AC17" s="50" t="n">
-        <x:f>E17/SUM($E$12:$E$17)</x:f>
-        <x:v>0.05661183885049371</x:v>
+        <x:f>IFERROR(E24/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AD17" t="str">
-        <x:f>A17</x:f>
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AE17" s="50" t="n">
-        <x:f>F17/SUM($F$12:$F$17)</x:f>
-        <x:v>0.12742350461203997</x:v>
+        <x:f>IFERROR(F24/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.00017353785290100476</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="30" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="B18" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A18)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>14.972351058757239</x:v>
+        <x:v>18.27751394478009</x:v>
       </x:c>
       <x:c r="C18" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A18)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>7.632455817154484</x:v>
+        <x:v>3.778708576146502</x:v>
       </x:c>
       <x:c r="D18" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A18)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>5.098094425418688</x:v>
+        <x:v>4.3239935298794805</x:v>
       </x:c>
       <x:c r="E18" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A18)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>1.330302040757552</x:v>
+        <x:v>0.9478803218030991</x:v>
       </x:c>
       <x:c r="F18" s="75" t="n">
         <x:f>SUM(B18:E18)</x:f>
-        <x:v>29.033203342087965</x:v>
+        <x:v>27.32809637260917</x:v>
+      </x:c>
+      <x:c r="V18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="W18" s="50" t="n">
+        <x:f>IFERROR(B25/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="Y18" s="50" t="n">
+        <x:f>IFERROR(C25/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="AA18" s="50" t="n">
+        <x:f>IFERROR(D25/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.00048678091810010486</x:v>
+      </x:c>
+      <x:c r="AB18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="AC18" s="50" t="n">
+        <x:f>IFERROR(E25/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD18" t="str">
+        <x:v>政府或公營事業貸款</x:v>
+      </x:c>
+      <x:c r="AE18" s="50" t="n">
+        <x:f>IFERROR(F25/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.00008291398250623317</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="30" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="B19" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A19)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0</x:v>
+        <x:v>14.972351058757239</x:v>
       </x:c>
       <x:c r="C19" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A19)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0</x:v>
+        <x:v>7.632455817154484</x:v>
       </x:c>
       <x:c r="D19" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A19)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0</x:v>
+        <x:v>5.098094425418688</x:v>
       </x:c>
       <x:c r="E19" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A19)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0</x:v>
+        <x:v>1.330302040757552</x:v>
       </x:c>
       <x:c r="F19" s="75" t="n">
         <x:f>SUM(B19:E19)</x:f>
+        <x:v>29.033203342087965</x:v>
+      </x:c>
+      <x:c r="V19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="W19" s="50" t="n">
+        <x:f>IFERROR(B26/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="X19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="Y19" s="50" t="n">
+        <x:f>IFERROR(C26/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="AA19" s="50" t="n">
+        <x:f>IFERROR(D26/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.02204115775027534</x:v>
+      </x:c>
+      <x:c r="AB19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="AC19" s="50" t="n">
+        <x:f>IFERROR(E26/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD19" t="str">
+        <x:v>被保險人貸款</x:v>
+      </x:c>
+      <x:c r="AE19" s="50" t="n">
+        <x:f>IFERROR(F26/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.0037542970567873246</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4852,6 +6137,41 @@
         <x:f>SUM(B20:E20)</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="W20" s="50" t="n">
+        <x:f>IFERROR(B27/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.055961194533538296</x:v>
+      </x:c>
+      <x:c r="X20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="Y20" s="50" t="n">
+        <x:f>IFERROR(C27/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.04034712746974965</x:v>
+      </x:c>
+      <x:c r="Z20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="AA20" s="50" t="n">
+        <x:f>IFERROR(D27/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.3331317080001063</x:v>
+      </x:c>
+      <x:c r="AB20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="AC20" s="50" t="n">
+        <x:f>IFERROR(E27/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.28681651089402854</x:v>
+      </x:c>
+      <x:c r="AD20" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="AE20" s="50" t="n">
+        <x:f>IFERROR(F27/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.12643820937201783</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="30" t="str">
@@ -4872,6 +6192,41 @@
       <x:c r="F21" s="74" t="str">
         <x:v>TWD／USD</x:v>
       </x:c>
+      <x:c r="V21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="W21" s="50" t="n">
+        <x:f>IFERROR(B12/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.12953267317388073</x:v>
+      </x:c>
+      <x:c r="X21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="Y21" s="50" t="n">
+        <x:f>IFERROR(C12/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.013877837509840278</x:v>
+      </x:c>
+      <x:c r="Z21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AA21" s="50" t="n">
+        <x:f>IFERROR(D12/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.12378380873949746</x:v>
+      </x:c>
+      <x:c r="AB21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AC21" s="50" t="n">
+        <x:f>IFERROR(E12/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.13403073741045154</x:v>
+      </x:c>
+      <x:c r="AD21" t="str">
+        <x:v>自行運用-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AE21" s="50" t="n">
+        <x:f>IFERROR(F12/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.11610091308162436</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="90" t="str">
@@ -4897,10 +6252,45 @@
         <x:f>SUM(B22:E22)</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="W22" s="50" t="n">
+        <x:f>IFERROR(B13/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.015092963877875721</x:v>
+      </x:c>
+      <x:c r="X22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="Y22" s="50" t="n">
+        <x:f>IFERROR(C13/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.010259022550242067</x:v>
+      </x:c>
+      <x:c r="Z22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AA22" s="50" t="n">
+        <x:f>IFERROR(D13/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.06498542368738083</x:v>
+      </x:c>
+      <x:c r="AB22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AC22" s="50" t="n">
+        <x:f>IFERROR(E13/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.07315031270084386</x:v>
+      </x:c>
+      <x:c r="AD22" t="str">
+        <x:v>自行運用-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AE22" s="50" t="n">
+        <x:f>IFERROR(F13/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.02934192685892919</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="30" t="str">
-        <x:v>房屋及土地</x:v>
+        <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="B23" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A23)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4908,11 +6298,11 @@
       </x:c>
       <x:c r="C23" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A23)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0</x:v>
+        <x:v>2.721444872906558</x:v>
       </x:c>
       <x:c r="D23" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A23)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0.049138830395993115</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E23" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A23)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4920,12 +6310,47 @@
       </x:c>
       <x:c r="F23" s="75" t="n">
         <x:f>SUM(B23:E23)</x:f>
-        <x:v>0.049138830395993115</x:v>
+        <x:v>2.721444872906558</x:v>
+      </x:c>
+      <x:c r="V23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="W23" s="50" t="n">
+        <x:f>IFERROR(B14/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.008290945766926794</x:v>
+      </x:c>
+      <x:c r="X23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="Y23" s="50" t="n">
+        <x:f>IFERROR(C14/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AA23" s="50" t="n">
+        <x:f>IFERROR(D14/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.0072035334470178895</x:v>
+      </x:c>
+      <x:c r="AB23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AC23" s="50" t="n">
+        <x:f>IFERROR(E14/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.028460576033988435</x:v>
+      </x:c>
+      <x:c r="AD23" t="str">
+        <x:v>自行運用-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AE23" s="50" t="n">
+        <x:f>IFERROR(F14/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.008877103672406713</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="30" t="str">
-        <x:v>政府或公營事業貸款</x:v>
+        <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="B24" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A24)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4937,7 +6362,7 @@
       </x:c>
       <x:c r="D24" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A24)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>0.023477852559085927</x:v>
+        <x:v>0.049138830395993115</x:v>
       </x:c>
       <x:c r="E24" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A24)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4945,12 +6370,47 @@
       </x:c>
       <x:c r="F24" s="75" t="n">
         <x:f>SUM(B24:E24)</x:f>
-        <x:v>0.023477852559085927</x:v>
+        <x:v>0.049138830395993115</x:v>
+      </x:c>
+      <x:c r="V24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="W24" s="50" t="n">
+        <x:f>IFERROR(B15/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.2104405841765572</x:v>
+      </x:c>
+      <x:c r="X24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="Y24" s="50" t="n">
+        <x:f>IFERROR(C15/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.08557910923436605</x:v>
+      </x:c>
+      <x:c r="Z24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="AA24" s="50" t="n">
+        <x:f>IFERROR(D15/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.044434094027364646</x:v>
+      </x:c>
+      <x:c r="AB24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="AC24" s="50" t="n">
+        <x:f>IFERROR(E15/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.12423456388103749</x:v>
+      </x:c>
+      <x:c r="AD24" t="str">
+        <x:v>委託經營-國內-權益證券</x:v>
+      </x:c>
+      <x:c r="AE24" s="50" t="n">
+        <x:f>IFERROR(F15/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.168535157218321</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="30" t="str">
-        <x:v>被保險人貸款</x:v>
+        <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="B25" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A25)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4962,7 +6422,7 @@
       </x:c>
       <x:c r="D25" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A25)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>1.0630635521051808</x:v>
+        <x:v>0.023477852559085927</x:v>
       </x:c>
       <x:c r="E25" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A25)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
@@ -4970,56 +6430,186 @@
       </x:c>
       <x:c r="F25" s="75" t="n">
         <x:f>SUM(B25:E25)</x:f>
-        <x:v>1.0630635521051808</x:v>
+        <x:v>0.023477852559085927</x:v>
+      </x:c>
+      <x:c r="V25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="W25" s="50" t="n">
+        <x:f>IFERROR(B16/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.10710053272306842</x:v>
+      </x:c>
+      <x:c r="X25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="Y25" s="50" t="n">
+        <x:f>IFERROR(C16/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.05126892436949562</x:v>
+      </x:c>
+      <x:c r="Z25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AA25" s="50" t="n">
+        <x:f>IFERROR(D16/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.061535399591916395</x:v>
+      </x:c>
+      <x:c r="AB25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AC25" s="50" t="n">
+        <x:f>IFERROR(E16/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.05332745745535172</x:v>
+      </x:c>
+      <x:c r="AD25" t="str">
+        <x:v>委託經營-國外-固定收益</x:v>
+      </x:c>
+      <x:c r="AE25" s="50" t="n">
+        <x:f>IFERROR(F16/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.09334918338528231</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="30" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
+        <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="B26" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A26)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>9.752879699452183</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A26)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>2.713406624823916</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A26)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>16.067222095946157</x:v>
+        <x:v>1.0630635521051808</x:v>
       </x:c>
       <x:c r="E26" s="74" t="n">
         <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A26)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
-        <x:v>7.268627091094068</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F26" s="75" t="n">
         <x:f>SUM(B26:E26)</x:f>
+        <x:v>1.0630635521051808</x:v>
+      </x:c>
+      <x:c r="V26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="W26" s="50" t="n">
+        <x:f>IFERROR(B17/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.28279620723439863</x:v>
+      </x:c>
+      <x:c r="X26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="Y26" s="50" t="n">
+        <x:f>IFERROR(C17/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.11351479999631743</x:v>
+      </x:c>
+      <x:c r="Z26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AA26" s="50" t="n">
+        <x:f>IFERROR(D17/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.14602525868778218</x:v>
+      </x:c>
+      <x:c r="AB26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AC26" s="50" t="n">
+        <x:f>IFERROR(E17/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.21008386701713133</x:v>
+      </x:c>
+      <x:c r="AD26" t="str">
+        <x:v>委託經營-國外-權益證券</x:v>
+      </x:c>
+      <x:c r="AE26" s="50" t="n">
+        <x:f>IFERROR(F17/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.24469114735095152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="30" t="str">
+        <x:v>股票及受益憑證投資（含期貨）</x:v>
+      </x:c>
+      <x:c r="B27" s="74" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+        <x:v>9.752879699452183</x:v>
+      </x:c>
+      <x:c r="C27" s="74" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+        <x:v>2.713406624823916</x:v>
+      </x:c>
+      <x:c r="D27" s="74" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+        <x:v>16.067222095946157</x:v>
+      </x:c>
+      <x:c r="E27" s="74" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+        <x:v>7.268627091094068</x:v>
+      </x:c>
+      <x:c r="F27" s="75" t="n">
+        <x:f>SUM(B27:E27)</x:f>
         <x:v>35.80213551131632</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="33" t="str">
+      <x:c r="V27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="W27" s="50" t="n">
+        <x:f>IFERROR(B18/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:v>0.10487482107574338</x:v>
+      </x:c>
+      <x:c r="X27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="Y27" s="50" t="n">
+        <x:f>IFERROR(C18/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:v>0.05618768495588562</x:v>
+      </x:c>
+      <x:c r="Z27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AA27" s="50" t="n">
+        <x:f>IFERROR(D18/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:v>0.08965204696794446</x:v>
+      </x:c>
+      <x:c r="AB27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AC27" s="50" t="n">
+        <x:f>IFERROR(E18/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:v>0.03740289923220597</x:v>
+      </x:c>
+      <x:c r="AD27" t="str">
+        <x:v>委託經營-國外-另類投資</x:v>
+      </x:c>
+      <x:c r="AE27" s="50" t="n">
+        <x:f>IFERROR(F18/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:v>0.09651143769919772</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="33" t="str">
         <x:v>國外投資</x:v>
       </x:c>
-      <x:c r="B27" s="76" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+      <x:c r="B28" s="76" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,$A28)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
         <x:v>26.650200173767413</x:v>
       </x:c>
-      <x:c r="C27" s="76" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+      <x:c r="C28" s="76" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,$A28)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
         <x:v>1.6232411102519957</x:v>
       </x:c>
-      <x:c r="D27" s="76" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+      <x:c r="D28" s="76" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,$A28)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
         <x:v>9.451931108436375</x:v>
       </x:c>
-      <x:c r="E27" s="76" t="n">
-        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A27)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
+      <x:c r="E28" s="76" t="n">
+        <x:f>SUMIFS('月度資產配置'!$E$4:$E$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,$A28)/(1000000000*'儀表板(美元)'!$C$21)</x:f>
         <x:v>5.971731202817343</x:v>
       </x:c>
-      <x:c r="F27" s="77" t="n">
-        <x:f>SUM(B27:E27)</x:f>
+      <x:c r="F28" s="77" t="n">
+        <x:f>SUM(B28:E28)</x:f>
         <x:v>43.69710359527313</x:v>
       </x:c>
     </x:row>
@@ -5031,7 +6621,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R492d294c71b2451c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24b9563f4cd4b65"/>
 </x:worksheet>
 </file>
 
@@ -5254,7 +6844,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E10" s="40" t="n">
         <x:v>719603636127</x:v>
@@ -5280,7 +6870,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E11" s="40" t="n">
         <x:v>49052466605</x:v>
@@ -5306,7 +6896,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E12" s="40" t="n">
         <x:v>47810551289</x:v>
@@ -5358,7 +6948,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D14" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E14" s="40" t="n">
         <x:v>831573253748</x:v>
@@ -5410,7 +7000,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D16" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E16" s="40" t="n">
         <x:v>560014671687</x:v>
@@ -5436,7 +7026,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D17" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E17" s="40" t="n">
         <x:v>1346277092815</x:v>
@@ -5462,7 +7052,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D18" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E18" s="40" t="n">
         <x:v>529635031268</x:v>
@@ -5670,7 +7260,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D26" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E26" s="40" t="n">
         <x:v>42827418384</x:v>
@@ -5696,7 +7286,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D27" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E27" s="40" t="n">
         <x:v>31183929553</x:v>
@@ -5722,7 +7312,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D28" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E28" s="40" t="n">
         <x:v>4362849575</x:v>
@@ -5774,7 +7364,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D30" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E30" s="40" t="n">
         <x:v>149443657790</x:v>
@@ -5826,7 +7416,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D32" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E32" s="40" t="n">
         <x:v>102851758557</x:v>
@@ -5852,7 +7442,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D33" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E33" s="40" t="n">
         <x:v>244510232894</x:v>
@@ -5878,7 +7468,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D34" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E34" s="40" t="n">
         <x:v>114585650788</x:v>
@@ -6086,7 +7676,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D42" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E42" s="40" t="n">
         <x:v>722259488440</x:v>
@@ -6112,7 +7702,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D43" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E43" s="40" t="n">
         <x:v>50072812305</x:v>
@@ -6138,7 +7728,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D44" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E44" s="40" t="n">
         <x:v>46294214272</x:v>
@@ -6190,7 +7780,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D46" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E46" s="40" t="n">
         <x:v>838161704810</x:v>
@@ -6242,7 +7832,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D48" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E48" s="40" t="n">
         <x:v>558341350399</x:v>
@@ -6268,7 +7858,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D49" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E49" s="40" t="n">
         <x:v>1349047104886</x:v>
@@ -6294,7 +7884,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D50" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E50" s="40" t="n">
         <x:v>529866446031</x:v>
@@ -6502,7 +8092,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D58" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E58" s="40" t="n">
         <x:v>37975916576</x:v>
@@ -6528,7 +8118,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D59" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E59" s="40" t="n">
         <x:v>29688137371</x:v>
@@ -6554,7 +8144,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D60" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E60" s="40" t="n">
         <x:v>3706414546</x:v>
@@ -6606,7 +8196,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D62" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E62" s="40" t="n">
         <x:v>151292602643</x:v>
@@ -6658,7 +8248,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D64" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E64" s="40" t="n">
         <x:v>103179007498</x:v>
@@ -6684,7 +8274,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D65" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E65" s="40" t="n">
         <x:v>246431525266</x:v>
@@ -6710,7 +8300,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D66" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E66" s="40" t="n">
         <x:v>114473009741</x:v>
@@ -6918,7 +8508,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D74" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E74" s="40" t="n">
         <x:v>705413959933</x:v>
@@ -6944,7 +8534,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D75" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E75" s="40" t="n">
         <x:v>70940137440</x:v>
@@ -6970,7 +8560,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D76" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E76" s="40" t="n">
         <x:v>46734756653</x:v>
@@ -7022,7 +8612,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D78" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E78" s="40" t="n">
         <x:v>858114899169</x:v>
@@ -7074,7 +8664,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D80" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E80" s="40" t="n">
         <x:v>573717349033</x:v>
@@ -7100,7 +8690,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D81" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E81" s="40" t="n">
         <x:v>1415972359796</x:v>
@@ -7126,7 +8716,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D82" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E82" s="40" t="n">
         <x:v>554025548580</x:v>
@@ -7334,7 +8924,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D90" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E90" s="40" t="n">
         <x:v>36247107869</x:v>
@@ -7360,7 +8950,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D91" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E91" s="40" t="n">
         <x:v>28026080031</x:v>
@@ -7386,7 +8976,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D92" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E92" s="40" t="n">
         <x:v>2490483619</x:v>
@@ -7438,7 +9028,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D94" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E94" s="40" t="n">
         <x:v>153907814001</x:v>
@@ -7490,7 +9080,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D96" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E96" s="40" t="n">
         <x:v>107937883777</x:v>
@@ -7516,7 +9106,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D97" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E97" s="40" t="n">
         <x:v>256515293681</x:v>
@@ -7542,7 +9132,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D98" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E98" s="40" t="n">
         <x:v>118634432671</x:v>
@@ -7750,7 +9340,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D106" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E106" s="40" t="n">
         <x:v>716865063430</x:v>
@@ -7776,7 +9366,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D107" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E107" s="40" t="n">
         <x:v>70735735443</x:v>
@@ -7802,7 +9392,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D108" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E108" s="40" t="n">
         <x:v>45735318169</x:v>
@@ -7854,7 +9444,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D110" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E110" s="40" t="n">
         <x:v>901284116115</x:v>
@@ -7906,7 +9496,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D112" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E112" s="40" t="n">
         <x:v>570715984373</x:v>
@@ -7932,7 +9522,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D113" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E113" s="40" t="n">
         <x:v>1420766174238</x:v>
@@ -7958,7 +9548,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D114" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E114" s="40" t="n">
         <x:v>550482971517</x:v>
@@ -8166,7 +9756,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D122" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E122" s="40" t="n">
         <x:v>33645097307</x:v>
@@ -8192,7 +9782,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D123" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E123" s="40" t="n">
         <x:v>27416980369</x:v>
@@ -8218,7 +9808,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D124" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E124" s="40" t="n">
         <x:v>1934116926</x:v>
@@ -8270,7 +9860,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D126" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E126" s="40" t="n">
         <x:v>160958872991</x:v>
@@ -8322,7 +9912,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D128" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E128" s="40" t="n">
         <x:v>105802722537</x:v>
@@ -8348,7 +9938,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D129" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E129" s="40" t="n">
         <x:v>257687903958</x:v>
@@ -8374,7 +9964,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D130" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E130" s="40" t="n">
         <x:v>117612036726</x:v>
@@ -8582,7 +10172,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D138" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E138" s="40" t="n">
         <x:v>721001943257</x:v>
@@ -8608,7 +10198,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D139" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E139" s="40" t="n">
         <x:v>70252614076</x:v>
@@ -8634,7 +10224,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D140" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E140" s="40" t="n">
         <x:v>44577847075</x:v>
@@ -8686,7 +10276,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D142" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E142" s="40" t="n">
         <x:v>1004764361217</x:v>
@@ -8738,7 +10328,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D144" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E144" s="40" t="n">
         <x:v>567538729831</x:v>
@@ -8764,7 +10354,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D145" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E145" s="40" t="n">
         <x:v>1459780141200</x:v>
@@ -8790,7 +10380,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D146" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E146" s="40" t="n">
         <x:v>549405984068</x:v>
@@ -8998,7 +10588,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D154" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E154" s="40" t="n">
         <x:v>36505162373</x:v>
@@ -9024,7 +10614,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D155" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E155" s="40" t="n">
         <x:v>25287747831</x:v>
@@ -9050,7 +10640,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D156" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E156" s="40" t="n">
         <x:v>0</x:v>
@@ -9102,7 +10692,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D158" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E158" s="40" t="n">
         <x:v>167766138109</x:v>
@@ -9154,7 +10744,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D160" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E160" s="40" t="n">
         <x:v>106097885207</x:v>
@@ -9180,7 +10770,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D161" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E161" s="40" t="n">
         <x:v>254032981401</x:v>
@@ -9206,7 +10796,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D162" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E162" s="40" t="n">
         <x:v>117428251440</x:v>
@@ -9414,7 +11004,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D170" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E170" s="40" t="n">
         <x:v>715655062812</x:v>
@@ -9440,7 +11030,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D171" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E171" s="40" t="n">
         <x:v>74774832699</x:v>
@@ -9466,7 +11056,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D172" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E172" s="40" t="n">
         <x:v>45413620644</x:v>
@@ -9518,7 +11108,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D174" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E174" s="40" t="n">
         <x:v>1096284105994</x:v>
@@ -9570,7 +11160,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D176" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E176" s="40" t="n">
         <x:v>585932807329</x:v>
@@ -9596,7 +11186,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D177" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E177" s="40" t="n">
         <x:v>1518091521122</x:v>
@@ -9622,7 +11212,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D178" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E178" s="40" t="n">
         <x:v>557029765749</x:v>
@@ -9830,7 +11420,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D186" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E186" s="40" t="n">
         <x:v>30843423120</x:v>
@@ -9856,7 +11446,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D187" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E187" s="40" t="n">
         <x:v>23396850392</x:v>
@@ -9882,7 +11472,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D188" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E188" s="40" t="n">
         <x:v>0</x:v>
@@ -9934,7 +11524,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D190" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E190" s="40" t="n">
         <x:v>177545692702</x:v>
@@ -9986,7 +11576,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D192" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E192" s="40" t="n">
         <x:v>108036669123</x:v>
@@ -10012,7 +11602,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D193" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E193" s="40" t="n">
         <x:v>241307746600</x:v>
@@ -10038,7 +11628,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D194" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E194" s="40" t="n">
         <x:v>120127282859</x:v>
@@ -10246,7 +11836,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D202" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E202" s="40" t="n">
         <x:v>721154157630</x:v>
@@ -10272,7 +11862,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D203" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E203" s="40" t="n">
         <x:v>84027862506</x:v>
@@ -10298,7 +11888,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D204" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E204" s="40" t="n">
         <x:v>46158624415</x:v>
@@ -10350,7 +11940,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D206" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E206" s="40" t="n">
         <x:v>1171597084307</x:v>
@@ -10402,7 +11992,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D208" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E208" s="40" t="n">
         <x:v>596266506088</x:v>
@@ -10428,7 +12018,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D209" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E209" s="40" t="n">
         <x:v>1574426402328</x:v>
@@ -10454,7 +12044,7 @@
         <x:v>新制</x:v>
       </x:c>
       <x:c r="D210" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E210" s="40" t="n">
         <x:v>583875182966</x:v>
@@ -10662,7 +12252,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D218" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E218" s="40" t="n">
         <x:v>29814460239</x:v>
@@ -10688,7 +12278,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D219" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E219" s="40" t="n">
         <x:v>22039977028</x:v>
@@ -10714,7 +12304,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D220" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E220" s="40" t="n">
         <x:v>0</x:v>
@@ -10766,7 +12356,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D222" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E222" s="40" t="n">
         <x:v>183853928809</x:v>
@@ -10818,7 +12408,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D224" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E224" s="40" t="n">
         <x:v>110143623315</x:v>
@@ -10844,7 +12434,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D225" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E225" s="40" t="n">
         <x:v>243869586211</x:v>
@@ -10870,7 +12460,7 @@
         <x:v>舊制</x:v>
       </x:c>
       <x:c r="D226" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E226" s="40" t="n">
         <x:v>120710845465</x:v>
@@ -11156,7 +12746,7 @@
         <x:v>勞工保險</x:v>
       </x:c>
       <x:c r="D237" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E237" s="40" t="n">
         <x:v>190717945389</x:v>
@@ -11182,7 +12772,7 @@
         <x:v>勞工保險</x:v>
       </x:c>
       <x:c r="D238" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E238" s="40" t="n">
         <x:v>100125263652</x:v>
@@ -11208,7 +12798,7 @@
         <x:v>勞工保險</x:v>
       </x:c>
       <x:c r="D239" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E239" s="40" t="n">
         <x:v>11098730218</x:v>
@@ -11260,7 +12850,7 @@
         <x:v>勞工保險</x:v>
       </x:c>
       <x:c r="D241" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E241" s="40" t="n">
         <x:v>68461127545</x:v>
@@ -11312,7 +12902,7 @@
         <x:v>勞工保險</x:v>
       </x:c>
       <x:c r="D243" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E243" s="40" t="n">
         <x:v>94809693597</x:v>
@@ -11338,7 +12928,7 @@
         <x:v>勞工保險</x:v>
       </x:c>
       <x:c r="D244" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E244" s="40" t="n">
         <x:v>224986107597</x:v>
@@ -11364,7 +12954,7 @@
         <x:v>勞工保險</x:v>
       </x:c>
       <x:c r="D245" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E245" s="40" t="n">
         <x:v>138129973312</x:v>
@@ -11598,7 +13188,7 @@
         <x:v>國民年金</x:v>
       </x:c>
       <x:c r="D254" s="31" t="str">
-        <x:v>自行運用-固定收益</x:v>
+        <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="E254" s="40" t="n">
         <x:v>108506446162</x:v>
@@ -11624,7 +13214,7 @@
         <x:v>國民年金</x:v>
       </x:c>
       <x:c r="D255" s="31" t="str">
-        <x:v>自行運用-權益證券</x:v>
+        <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="E255" s="40" t="n">
         <x:v>59219852253</x:v>
@@ -11650,7 +13240,7 @@
         <x:v>國民年金</x:v>
       </x:c>
       <x:c r="D256" s="31" t="str">
-        <x:v>自行運用-另類投資</x:v>
+        <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="E256" s="40" t="n">
         <x:v>23040654859</x:v>
@@ -11702,7 +13292,7 @@
         <x:v>國民年金</x:v>
       </x:c>
       <x:c r="D258" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="E258" s="40" t="n">
         <x:v>100575817739</x:v>
@@ -11754,7 +13344,7 @@
         <x:v>國民年金</x:v>
       </x:c>
       <x:c r="D260" s="31" t="str">
-        <x:v>委託經營-固定收益</x:v>
+        <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="E260" s="40" t="n">
         <x:v>43171984301</x:v>
@@ -11780,7 +13370,7 @@
         <x:v>國民年金</x:v>
       </x:c>
       <x:c r="D261" s="31" t="str">
-        <x:v>委託經營-權益證券</x:v>
+        <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="E261" s="40" t="n">
         <x:v>170076314183</x:v>
@@ -11806,7 +13396,7 @@
         <x:v>國民年金</x:v>
       </x:c>
       <x:c r="D262" s="31" t="str">
-        <x:v>委託經營-另類投資</x:v>
+        <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="E262" s="40" t="n">
         <x:v>30280036880</x:v>
@@ -11853,7 +13443,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbae52c94d9864baa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb66c285481594b01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16892,7 +18482,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3382675c3ba5416a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2577bbb40c2840e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18966,7 +20556,7 @@
         <x:v>110-1全球基礎建設有價證券型</x:v>
       </x:c>
       <x:c r="F49" s="31" t="str">
-        <x:v>Clearbridge</x:v>
+        <x:v>ClearBridge</x:v>
       </x:c>
       <x:c r="G49" s="40" t="n">
         <x:v>700000000</x:v>
@@ -24871,7 +26461,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8472e871b63a4737"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5cb1800467847e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28810,7 +30400,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0affc87d48064588"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R449830fedb6e4c60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29162,11 +30752,11 @@
         <x:v>17827431853</x:v>
       </x:c>
       <x:c r="J9" s="42" t="n">
-        <x:f>IFERROR(I9/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I9/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.1425863938130672</x:v>
       </x:c>
       <x:c r="K9" s="28" t="n">
-        <x:f>RANK(I9,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I9,$I$9:$I$58,0)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L9" s="29" t="n">
@@ -29240,11 +30830,11 @@
         <x:v>12270337973</x:v>
       </x:c>
       <x:c r="J10" s="43" t="n">
-        <x:f>IFERROR(I10/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I10/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.09813994841568788</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:f>RANK(I10,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I10,$I$9:$I$58,0)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L10" s="32" t="n">
@@ -29318,11 +30908,11 @@
         <x:v>8229076099</x:v>
       </x:c>
       <x:c r="J11" s="43" t="n">
-        <x:f>IFERROR(I11/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I11/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.0658173479525746</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
-        <x:f>RANK(I11,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I11,$I$9:$I$58,0)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="L11" s="32" t="n">
@@ -29396,11 +30986,11 @@
         <x:v>6499168753</x:v>
       </x:c>
       <x:c r="J12" s="43" t="n">
-        <x:f>IFERROR(I12/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I12/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.05198129730148962</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
-        <x:f>RANK(I12,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I12,$I$9:$I$58,0)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="L12" s="32" t="n">
@@ -29474,11 +31064,11 @@
         <x:v>6233333079</x:v>
       </x:c>
       <x:c r="J13" s="43" t="n">
-        <x:f>IFERROR(I13/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I13/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.04985510490232206</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
-        <x:f>RANK(I13,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I13,$I$9:$I$58,0)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L13" s="32" t="n">
@@ -29552,11 +31142,11 @@
         <x:v>5911641695</x:v>
       </x:c>
       <x:c r="J14" s="43" t="n">
-        <x:f>IFERROR(I14/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I14/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.04728217040768952</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
-        <x:f>RANK(I14,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I14,$I$9:$I$58,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="L14" s="32" t="n">
@@ -29569,7 +31159,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="Q14" s="51" t="n">
-        <x:f>SUM(I19:I59)</x:f>
+        <x:f>SUM(I19:I58)</x:f>
         <x:v>49028845422</x:v>
       </x:c>
       <x:c r="R14" s="50" t="n">
@@ -29629,11 +31219,11 @@
         <x:v>5214617387</x:v>
       </x:c>
       <x:c r="J15" s="43" t="n">
-        <x:f>IFERROR(I15/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I15/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.041707268576776396</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
-        <x:f>RANK(I15,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I15,$I$9:$I$58,0)</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="L15" s="32" t="n">
@@ -29677,11 +31267,11 @@
         <x:v>4884050215</x:v>
       </x:c>
       <x:c r="J16" s="43" t="n">
-        <x:f>IFERROR(I16/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I16/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.0390633442383119</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
-        <x:f>RANK(I16,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I16,$I$9:$I$58,0)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="L16" s="32" t="n">
@@ -29725,11 +31315,11 @@
         <x:v>4847721016</x:v>
       </x:c>
       <x:c r="J17" s="43" t="n">
-        <x:f>IFERROR(I17/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I17/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.03877277801889003</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
-        <x:f>RANK(I17,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I17,$I$9:$I$58,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="L17" s="32" t="n">
@@ -29773,11 +31363,11 @@
         <x:v>4082759823</x:v>
       </x:c>
       <x:c r="J18" s="43" t="n">
-        <x:f>IFERROR(I18/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I18/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.03265450709707709</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
-        <x:f>RANK(I18,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I18,$I$9:$I$58,0)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="L18" s="32" t="n">
@@ -29821,11 +31411,11 @@
         <x:v>3525432785</x:v>
       </x:c>
       <x:c r="J19" s="43" t="n">
-        <x:f>IFERROR(I19/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I19/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.028196924357274576</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
-        <x:f>RANK(I19,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I19,$I$9:$I$58,0)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="L19" s="32" t="n">
@@ -29869,11 +31459,11 @@
         <x:v>3467884297</x:v>
       </x:c>
       <x:c r="J20" s="43" t="n">
-        <x:f>IFERROR(I20/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I20/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.02773664317707005</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
-        <x:f>RANK(I20,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I20,$I$9:$I$58,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="L20" s="32" t="n">
@@ -29917,11 +31507,11 @@
         <x:v>3039287910</x:v>
       </x:c>
       <x:c r="J21" s="43" t="n">
-        <x:f>IFERROR(I21/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I21/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.024308666913996812</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
-        <x:f>RANK(I21,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I21,$I$9:$I$58,0)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="L21" s="32" t="n">
@@ -29965,11 +31555,11 @@
         <x:v>3033228329</x:v>
       </x:c>
       <x:c r="J22" s="43" t="n">
-        <x:f>IFERROR(I22/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I22/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.024260201503502884</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
-        <x:f>RANK(I22,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I22,$I$9:$I$58,0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="L22" s="32" t="n">
@@ -30013,11 +31603,11 @@
         <x:v>2941839542</x:v>
       </x:c>
       <x:c r="J23" s="43" t="n">
-        <x:f>IFERROR(I23/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I23/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.023529260688206054</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
-        <x:f>RANK(I23,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I23,$I$9:$I$58,0)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="L23" s="32" t="n">
@@ -30061,11 +31651,11 @@
         <x:v>2584189383</x:v>
       </x:c>
       <x:c r="J24" s="43" t="n">
-        <x:f>IFERROR(I24/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I24/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.02066872267919953</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
-        <x:f>RANK(I24,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I24,$I$9:$I$58,0)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="L24" s="32" t="n">
@@ -30109,11 +31699,11 @@
         <x:v>2458832253</x:v>
       </x:c>
       <x:c r="J25" s="43" t="n">
-        <x:f>IFERROR(I25/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I25/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.019666098114268265</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
-        <x:f>RANK(I25,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I25,$I$9:$I$58,0)</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="L25" s="32" t="n">
@@ -30157,11 +31747,11 @@
         <x:v>2389413786</x:v>
       </x:c>
       <x:c r="J26" s="43" t="n">
-        <x:f>IFERROR(I26/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I26/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.019110879114965472</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
-        <x:f>RANK(I26,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I26,$I$9:$I$58,0)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="L26" s="32" t="n">
@@ -30182,11 +31772,11 @@
         <x:v>1806278590</x:v>
       </x:c>
       <x:c r="J27" s="43" t="n">
-        <x:f>IFERROR(I27/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I27/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.014446878972447797</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
-        <x:f>RANK(I27,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I27,$I$9:$I$58,0)</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="L27" s="32" t="n">
@@ -30207,11 +31797,11 @@
         <x:v>1719232558</x:v>
       </x:c>
       <x:c r="J28" s="43" t="n">
-        <x:f>IFERROR(I28/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I28/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.013750672143502425</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
-        <x:f>RANK(I28,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I28,$I$9:$I$58,0)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="L28" s="32" t="n">
@@ -30232,11 +31822,11 @@
         <x:v>1709168484</x:v>
       </x:c>
       <x:c r="J29" s="43" t="n">
-        <x:f>IFERROR(I29/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I29/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.013670178215349427</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
-        <x:f>RANK(I29,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I29,$I$9:$I$58,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="L29" s="32" t="n">
@@ -30257,11 +31847,11 @@
         <x:v>1679948361</x:v>
       </x:c>
       <x:c r="J30" s="43" t="n">
-        <x:f>IFERROR(I30/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I30/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.013436471420130734</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
-        <x:f>RANK(I30,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I30,$I$9:$I$58,0)</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="L30" s="32" t="n">
@@ -30282,11 +31872,11 @@
         <x:v>1388520134</x:v>
       </x:c>
       <x:c r="J31" s="43" t="n">
-        <x:f>IFERROR(I31/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I31/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.011105586058408076</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
-        <x:f>RANK(I31,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I31,$I$9:$I$58,0)</x:f>
         <x:v>23</x:v>
       </x:c>
       <x:c r="L31" s="32" t="n">
@@ -30307,11 +31897,11 @@
         <x:v>1352096519</x:v>
       </x:c>
       <x:c r="J32" s="43" t="n">
-        <x:f>IFERROR(I32/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I32/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.01081426468608088</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
-        <x:f>RANK(I32,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I32,$I$9:$I$58,0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="L32" s="32" t="n">
@@ -30332,11 +31922,11 @@
         <x:v>1337309953</x:v>
       </x:c>
       <x:c r="J33" s="43" t="n">
-        <x:f>IFERROR(I33/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I33/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.01069599957979951</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
-        <x:f>RANK(I33,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I33,$I$9:$I$58,0)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="L33" s="32" t="n">
@@ -30357,11 +31947,11 @@
         <x:v>1218224544</x:v>
       </x:c>
       <x:c r="J34" s="43" t="n">
-        <x:f>IFERROR(I34/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I34/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.009743537151948088</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
-        <x:f>RANK(I34,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I34,$I$9:$I$58,0)</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="L34" s="32" t="n">
@@ -30382,11 +31972,11 @@
         <x:v>1175399124</x:v>
       </x:c>
       <x:c r="J35" s="43" t="n">
-        <x:f>IFERROR(I35/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I35/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.00940101321178211</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
-        <x:f>RANK(I35,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I35,$I$9:$I$58,0)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="L35" s="32" t="n">
@@ -30407,11 +31997,11 @@
         <x:v>1142513053</x:v>
       </x:c>
       <x:c r="J36" s="43" t="n">
-        <x:f>IFERROR(I36/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I36/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.009137985631071913</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
-        <x:f>RANK(I36,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I36,$I$9:$I$58,0)</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="L36" s="32" t="n">
@@ -30432,11 +32022,11 @@
         <x:v>1077267573</x:v>
       </x:c>
       <x:c r="J37" s="43" t="n">
-        <x:f>IFERROR(I37/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I37/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.008616142788955701</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
-        <x:f>RANK(I37,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I37,$I$9:$I$58,0)</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="L37" s="32" t="n">
@@ -30446,22 +32036,22 @@
     </x:row>
     <x:row r="38">
       <x:c r="G38" s="30" t="str">
-        <x:v>Clearbridge</x:v>
+        <x:v>ClearBridge</x:v>
       </x:c>
       <x:c r="H38" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G38,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>700000000</x:v>
+        <x:v>760000000</x:v>
       </x:c>
       <x:c r="I38" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G38,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>957679882</x:v>
+        <x:v>1047858894</x:v>
       </x:c>
       <x:c r="J38" s="43" t="n">
-        <x:f>IFERROR(I38/SUM($I$9:$I$59),0)</x:f>
-        <x:v>0.007659663036587334</x:v>
+        <x:f>IFERROR(I38/SUM($I$9:$I$58),0)</x:f>
+        <x:v>0.00838092789541452</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
-        <x:f>RANK(I38,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I38,$I$9:$I$58,0)</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="L38" s="32" t="n">
@@ -30482,11 +32072,11 @@
         <x:v>897752897</x:v>
       </x:c>
       <x:c r="J39" s="43" t="n">
-        <x:f>IFERROR(I39/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I39/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.007180358291310641</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
-        <x:f>RANK(I39,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I39,$I$9:$I$58,0)</x:f>
         <x:v>31</x:v>
       </x:c>
       <x:c r="L39" s="32" t="n">
@@ -30507,11 +32097,11 @@
         <x:v>801020312</x:v>
       </x:c>
       <x:c r="J40" s="43" t="n">
-        <x:f>IFERROR(I40/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I40/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.006406677002098759</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
-        <x:f>RANK(I40,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I40,$I$9:$I$58,0)</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="L40" s="32" t="n">
@@ -30532,11 +32122,11 @@
         <x:v>769778438</x:v>
       </x:c>
       <x:c r="J41" s="43" t="n">
-        <x:f>IFERROR(I41/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I41/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.00615679994822167</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
-        <x:f>RANK(I41,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I41,$I$9:$I$58,0)</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="L41" s="32" t="n">
@@ -30557,11 +32147,11 @@
         <x:v>706462588</x:v>
       </x:c>
       <x:c r="J42" s="43" t="n">
-        <x:f>IFERROR(I42/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I42/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.005650390567602449</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
-        <x:f>RANK(I42,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I42,$I$9:$I$58,0)</x:f>
         <x:v>34</x:v>
       </x:c>
       <x:c r="L42" s="32" t="n">
@@ -30582,11 +32172,11 @@
         <x:v>697308846</x:v>
       </x:c>
       <x:c r="J43" s="43" t="n">
-        <x:f>IFERROR(I43/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I43/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.005577177607236788</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
-        <x:f>RANK(I43,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I43,$I$9:$I$58,0)</x:f>
         <x:v>35</x:v>
       </x:c>
       <x:c r="L43" s="32" t="n">
@@ -30607,11 +32197,11 @@
         <x:v>690570828</x:v>
       </x:c>
       <x:c r="J44" s="43" t="n">
-        <x:f>IFERROR(I44/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I44/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.005523285958905744</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
-        <x:f>RANK(I44,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I44,$I$9:$I$58,0)</x:f>
         <x:v>36</x:v>
       </x:c>
       <x:c r="L44" s="32" t="n">
@@ -30632,11 +32222,11 @@
         <x:v>688857784</x:v>
       </x:c>
       <x:c r="J45" s="43" t="n">
-        <x:f>IFERROR(I45/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I45/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.005509584783749547</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
-        <x:f>RANK(I45,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I45,$I$9:$I$58,0)</x:f>
         <x:v>37</x:v>
       </x:c>
       <x:c r="L45" s="32" t="n">
@@ -30657,11 +32247,11 @@
         <x:v>666575819</x:v>
       </x:c>
       <x:c r="J46" s="43" t="n">
-        <x:f>IFERROR(I46/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I46/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.005331370385701836</x:v>
       </x:c>
       <x:c r="K46" s="31" t="n">
-        <x:f>RANK(I46,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I46,$I$9:$I$58,0)</x:f>
         <x:v>38</x:v>
       </x:c>
       <x:c r="L46" s="32" t="n">
@@ -30682,11 +32272,11 @@
         <x:v>593041556</x:v>
       </x:c>
       <x:c r="J47" s="43" t="n">
-        <x:f>IFERROR(I47/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I47/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.004743232651151627</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
-        <x:f>RANK(I47,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I47,$I$9:$I$58,0)</x:f>
         <x:v>39</x:v>
       </x:c>
       <x:c r="L47" s="32" t="n">
@@ -30707,11 +32297,11 @@
         <x:v>478192278</x:v>
       </x:c>
       <x:c r="J48" s="43" t="n">
-        <x:f>IFERROR(I48/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I48/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.0038246514153861015</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
-        <x:f>RANK(I48,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I48,$I$9:$I$58,0)</x:f>
         <x:v>40</x:v>
       </x:c>
       <x:c r="L48" s="32" t="n">
@@ -30732,11 +32322,11 @@
         <x:v>458409894</x:v>
       </x:c>
       <x:c r="J49" s="43" t="n">
-        <x:f>IFERROR(I49/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I49/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.0036664290298600195</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
-        <x:f>RANK(I49,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I49,$I$9:$I$58,0)</x:f>
         <x:v>41</x:v>
       </x:c>
       <x:c r="L49" s="32" t="n">
@@ -30757,11 +32347,11 @@
         <x:v>422040147</x:v>
       </x:c>
       <x:c r="J50" s="43" t="n">
-        <x:f>IFERROR(I50/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I50/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.0033755385016345</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
-        <x:f>RANK(I50,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I50,$I$9:$I$58,0)</x:f>
         <x:v>42</x:v>
       </x:c>
       <x:c r="L50" s="32" t="n">
@@ -30782,11 +32372,11 @@
         <x:v>421747465</x:v>
       </x:c>
       <x:c r="J51" s="43" t="n">
-        <x:f>IFERROR(I51/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I51/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.003373197588413902</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
-        <x:f>RANK(I51,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I51,$I$9:$I$58,0)</x:f>
         <x:v>43</x:v>
       </x:c>
       <x:c r="L51" s="32" t="n">
@@ -30807,11 +32397,11 @@
         <x:v>367521178</x:v>
       </x:c>
       <x:c r="J52" s="43" t="n">
-        <x:f>IFERROR(I52/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I52/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.002939487855180437</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
-        <x:f>RANK(I52,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I52,$I$9:$I$58,0)</x:f>
         <x:v>44</x:v>
       </x:c>
       <x:c r="L52" s="32" t="n">
@@ -30832,11 +32422,11 @@
         <x:v>275639320</x:v>
       </x:c>
       <x:c r="J53" s="43" t="n">
-        <x:f>IFERROR(I53/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I53/SUM($I$9:$I$58),0)</x:f>
         <x:v>0.002204603386284842</x:v>
       </x:c>
       <x:c r="K53" s="31" t="n">
-        <x:f>RANK(I53,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I53,$I$9:$I$58,0)</x:f>
         <x:v>45</x:v>
       </x:c>
       <x:c r="L53" s="32" t="n">
@@ -30846,32 +32436,32 @@
     </x:row>
     <x:row r="54">
       <x:c r="G54" s="30" t="str">
-        <x:v>ClearBridge</x:v>
+        <x:v>柏瑞</x:v>
       </x:c>
       <x:c r="H54" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G54,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>60000000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I54" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G54,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>90179012</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J54" s="43" t="n">
-        <x:f>IFERROR(I54/SUM($I$9:$I$59),0)</x:f>
-        <x:v>0.0007212648588271855</x:v>
+        <x:f>IFERROR(I54/SUM($I$9:$I$58),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K54" s="31" t="n">
-        <x:f>RANK(I54,$I$9:$I$59,0)</x:f>
+        <x:f>RANK(I54,$I$9:$I$58,0)</x:f>
         <x:v>46</x:v>
       </x:c>
       <x:c r="L54" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G54,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="G55" s="30" t="str">
-        <x:v>柏瑞</x:v>
+        <x:v>安聯</x:v>
       </x:c>
       <x:c r="H55" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G55,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
@@ -30882,12 +32472,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J55" s="43" t="n">
-        <x:f>IFERROR(I55/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I55/SUM($I$9:$I$58),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K55" s="31" t="n">
-        <x:f>RANK(I55,$I$9:$I$59,0)</x:f>
-        <x:v>47</x:v>
+        <x:f>RANK(I55,$I$9:$I$58,0)</x:f>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L55" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G55,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
@@ -30896,7 +32486,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="G56" s="30" t="str">
-        <x:v>安聯</x:v>
+        <x:v>玉山</x:v>
       </x:c>
       <x:c r="H56" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G56,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
@@ -30907,12 +32497,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J56" s="43" t="n">
-        <x:f>IFERROR(I56/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I56/SUM($I$9:$I$58),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K56" s="31" t="n">
-        <x:f>RANK(I56,$I$9:$I$59,0)</x:f>
-        <x:v>47</x:v>
+        <x:f>RANK(I56,$I$9:$I$58,0)</x:f>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L56" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G56,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
@@ -30921,7 +32511,7 @@
     </x:row>
     <x:row r="57">
       <x:c r="G57" s="30" t="str">
-        <x:v>玉山</x:v>
+        <x:v>野村</x:v>
       </x:c>
       <x:c r="H57" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G57,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
@@ -30932,12 +32522,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J57" s="43" t="n">
-        <x:f>IFERROR(I57/SUM($I$9:$I$59),0)</x:f>
+        <x:f>IFERROR(I57/SUM($I$9:$I$58),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K57" s="31" t="n">
-        <x:f>RANK(I57,$I$9:$I$59,0)</x:f>
-        <x:v>47</x:v>
+        <x:f>RANK(I57,$I$9:$I$58,0)</x:f>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L57" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G57,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
@@ -30945,52 +32535,27 @@
       </x:c>
     </x:row>
     <x:row r="58">
-      <x:c r="G58" s="30" t="str">
-        <x:v>野村</x:v>
-      </x:c>
-      <x:c r="H58" s="40" t="n">
+      <x:c r="G58" s="33" t="str">
+        <x:v>國泰</x:v>
+      </x:c>
+      <x:c r="H58" s="41" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G58,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I58" s="40" t="n">
+      <x:c r="I58" s="41" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G58,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J58" s="43" t="n">
-        <x:f>IFERROR(I58/SUM($I$9:$I$59),0)</x:f>
+      <x:c r="J58" s="44" t="n">
+        <x:f>IFERROR(I58/SUM($I$9:$I$58),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K58" s="31" t="n">
-        <x:f>RANK(I58,$I$9:$I$59,0)</x:f>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="L58" s="32" t="n">
+      <x:c r="K58" s="34" t="n">
+        <x:f>RANK(I58,$I$9:$I$58,0)</x:f>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L58" s="35" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G58,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="G59" s="33" t="str">
-        <x:v>國泰</x:v>
-      </x:c>
-      <x:c r="H59" s="41" t="n">
-        <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G59,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I59" s="41" t="n">
-        <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G59,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J59" s="44" t="n">
-        <x:f>IFERROR(I59/SUM($I$9:$I$59),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K59" s="34" t="n">
-        <x:f>RANK(I59,$I$9:$I$59,0)</x:f>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="L59" s="35" t="n">
-        <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G59,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -30999,7 +32564,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4dd059d121a4318"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ecc9d40823948cb"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rd9d690488bf34826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R712cff793c084fe7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="Rfdf1439ccf4d4651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R28e19e45e77a40cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="Rab2d8c31d9c643a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rc4cb1f0ab88d473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R9698cc44cd9941e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R500c691197ed41d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="Reccff047312b4c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R669daac13ad74f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R33a107dc429342d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R038d41fa085c48ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R90f8d2ff99c0436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R98c7add857854f5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R95dcd709b20e4a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R655147c3abff4a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rd797195441a049c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R00327db2d15443fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3375,7 +3375,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R905a40ff0de945f2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8bcbffc68bdd42c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3405,7 +3405,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re8e84e7c91bb4e87"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re347ddf758a443cf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3435,7 +3435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raff075e4e6a94ebf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8327dbd615e5436d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3465,7 +3465,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5651826484714962"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc802eff804884510"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3495,7 +3495,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4e97b0b8b3bf4f98"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra942c1960ef0439b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3530,7 +3530,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R966977981ce74a40"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref3eb68545f84288"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3560,7 +3560,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R045feacbf19c4d28"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R06365c72ff574aa6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3590,7 +3590,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9adaabd040074666"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8fabfa9601cf43b8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3620,7 +3620,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf00fa6fc94bc4cd1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3b8271fb31fc4e07"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3650,7 +3650,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf92c1442f732439f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9e842dc2cb7e4bfb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3685,7 +3685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R583f8382e45e4b4c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc1c31b906090403b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3715,7 +3715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0d1abcd5d5e44a7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73cbe4e5c09a4c57"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3745,7 +3745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra9089d7219a54419"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reda42996294f4f1d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3775,7 +3775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd6c668e20cfd4394"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ca6cd30a901413c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4374,36 +4374,36 @@
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>IFERROR(B19/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.08009049818080267</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.08010000000000002</x:v>
       </x:c>
       <x:c r="X12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>IFERROR(C19/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.20294689334834715</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.2029</x:v>
       </x:c>
       <x:c r="Z12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>IFERROR(D19/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.09830773672574242</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0983</x:v>
       </x:c>
       <x:c r="AB12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>IFERROR(E19/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.04795105887019382</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="AD12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>IFERROR(F19/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.09545607450479587</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.107325</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4434,35 +4434,35 @@
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>IFERROR(B20/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>IFERROR(C20/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>IFERROR(D20/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>IFERROR(E20/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>IFERROR(F20/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4494,36 +4494,36 @@
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>IFERROR(B21/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.025587121477121857</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.025600000000000005</x:v>
       </x:c>
       <x:c r="X14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>IFERROR(C21/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.06119948492201287</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.061200000000000004</x:v>
       </x:c>
       <x:c r="Z14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AA14" s="50" t="n">
-        <x:f>IFERROR(D21/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.026053089900866026</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.026099999999999998</x:v>
       </x:c>
       <x:c r="AB14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>IFERROR(E21/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.0174561842083449</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0174</x:v>
       </x:c>
       <x:c r="AD14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>IFERROR(F21/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.029328348097442464</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.032575</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4554,36 +4554,36 @@
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>IFERROR(B22/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.04215323484379305</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.042100000000000005</x:v>
       </x:c>
       <x:c r="X15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>IFERROR(C22/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>IFERROR(D22/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.04390044141522057</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.043899999999999995</x:v>
       </x:c>
       <x:c r="AB15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>IFERROR(E22/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.06906982845758472</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0691</x:v>
       </x:c>
       <x:c r="AD15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>IFERROR(F22/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.03969409795326574</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.038775</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4614,36 +4614,36 @@
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="W16" s="50" t="n">
-        <x:f>IFERROR(B23/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="Y16" s="50" t="n">
-        <x:f>IFERROR(C23/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.07236318107912533</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0724</x:v>
       </x:c>
       <x:c r="Z16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AA16" s="50" t="n">
-        <x:f>IFERROR(D23/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AC16" s="50" t="n">
-        <x:f>IFERROR(E23/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AE16" s="50" t="n">
-        <x:f>IFERROR(F23/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.00894763287013099</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0181</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4674,36 +4674,36 @@
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="W17" s="50" t="n">
-        <x:f>IFERROR(B24/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="Y17" s="50" t="n">
-        <x:f>IFERROR(C24/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AA17" s="50" t="n">
-        <x:f>IFERROR(D24/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.0009475554586620803</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0009</x:v>
       </x:c>
       <x:c r="AB17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AC17" s="50" t="n">
-        <x:f>IFERROR(E24/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AE17" s="50" t="n">
-        <x:f>IFERROR(F24/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.0001615598458113894</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.000225</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4734,36 +4734,36 @@
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="W18" s="50" t="n">
-        <x:f>IFERROR(B25/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="Y18" s="50" t="n">
-        <x:f>IFERROR(C25/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="AA18" s="50" t="n">
-        <x:f>IFERROR(D25/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.0004527288739017158</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0005</x:v>
       </x:c>
       <x:c r="AB18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="AC18" s="50" t="n">
-        <x:f>IFERROR(E25/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="AE18" s="50" t="n">
-        <x:f>IFERROR(F25/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.00007719105662184733</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.000125</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4794,36 +4794,36 @@
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="W19" s="50" t="n">
-        <x:f>IFERROR(B26/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="Y19" s="50" t="n">
-        <x:f>IFERROR(C26/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="AA19" s="50" t="n">
-        <x:f>IFERROR(D26/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.02049930093134865</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.020499999999999997</x:v>
       </x:c>
       <x:c r="AB19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="AC19" s="50" t="n">
-        <x:f>IFERROR(E26/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="AE19" s="50" t="n">
-        <x:f>IFERROR(F26/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.0034951662907268884</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.005124999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4854,36 +4854,36 @@
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="W20" s="50" t="n">
-        <x:f>IFERROR(B27/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.052170363275692376</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0522</x:v>
       </x:c>
       <x:c r="X20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="Y20" s="50" t="n">
-        <x:f>IFERROR(C27/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.07214944417511744</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0721</x:v>
       </x:c>
       <x:c r="Z20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="AA20" s="50" t="n">
-        <x:f>IFERROR(D27/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.3098279686321394</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.3098</x:v>
       </x:c>
       <x:c r="AB20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="AC20" s="50" t="n">
-        <x:f>IFERROR(E27/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.26199942183961406</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.262</x:v>
       </x:c>
       <x:c r="AD20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="AE20" s="50" t="n">
-        <x:f>IFERROR(F27/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.11771113488688957</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.174025</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4914,36 +4914,36 @@
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="W21" s="50" t="n">
-        <x:f>IFERROR(B12/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.12075808373788141</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12080000000000002</x:v>
       </x:c>
       <x:c r="X21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="Y21" s="50" t="n">
-        <x:f>IFERROR(C12/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.02481659353415637</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0248</x:v>
       </x:c>
       <x:c r="Z21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="AA21" s="50" t="n">
-        <x:f>IFERROR(D12/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.11512469419841453</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1151</x:v>
       </x:c>
       <x:c r="AB21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="AC21" s="50" t="n">
-        <x:f>IFERROR(E12/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.1224335921276509</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12240000000000001</x:v>
       </x:c>
       <x:c r="AD21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="AE21" s="50" t="n">
-        <x:f>IFERROR(F12/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.10808734407200997</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.095775</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4974,36 +4974,36 @@
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="W22" s="50" t="n">
-        <x:f>IFERROR(B13/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.01407056112684972</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.014100000000000001</x:v>
       </x:c>
       <x:c r="X22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="Y22" s="50" t="n">
-        <x:f>IFERROR(C13/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.018345364867298538</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0184</x:v>
       </x:c>
       <x:c r="Z22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="AA22" s="50" t="n">
-        <x:f>IFERROR(D13/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.06043946381637647</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0604</x:v>
       </x:c>
       <x:c r="AB22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="AC22" s="50" t="n">
-        <x:f>IFERROR(E13/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.06682090781757392</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0668</x:v>
       </x:c>
       <x:c r="AD22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="AE22" s="50" t="n">
-        <x:f>IFERROR(F13/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.027316675295284924</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.039925</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5034,36 +5034,36 @@
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="W23" s="50" t="n">
-        <x:f>IFERROR(B14/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.007729314146437791</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.007700000000000001</x:v>
       </x:c>
       <x:c r="X23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="Y23" s="50" t="n">
-        <x:f>IFERROR(C14/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="AA23" s="50" t="n">
-        <x:f>IFERROR(D14/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.006699620844445446</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0067</x:v>
       </x:c>
       <x:c r="AB23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="AC23" s="50" t="n">
-        <x:f>IFERROR(E14/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.025997995871591892</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.026000000000000002</x:v>
       </x:c>
       <x:c r="AD23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="AE23" s="50" t="n">
-        <x:f>IFERROR(F14/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.008264384263091475</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.010100000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5094,36 +5094,36 @@
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="W24" s="50" t="n">
-        <x:f>IFERROR(B15/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.19618526402005568</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19620000000000004</x:v>
       </x:c>
       <x:c r="X24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="Y24" s="50" t="n">
-        <x:f>IFERROR(C15/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.15303407086143878</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.153</x:v>
       </x:c>
       <x:c r="Z24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="AA24" s="50" t="n">
-        <x:f>IFERROR(D15/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.04132577223931945</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.041299999999999996</x:v>
       </x:c>
       <x:c r="AB24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="AC24" s="50" t="n">
-        <x:f>IFERROR(E15/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.11348504243312058</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.11349999999999999</x:v>
       </x:c>
       <x:c r="AD24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="AE24" s="50" t="n">
-        <x:f>IFERROR(F15/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.15690244842157178</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.126</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -5154,36 +5154,36 @@
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="W25" s="50" t="n">
-        <x:f>IFERROR(B16/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.09984550447424796</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09980000000000001</x:v>
       </x:c>
       <x:c r="X25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="Y25" s="50" t="n">
-        <x:f>IFERROR(C16/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.0916799938109248</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0917</x:v>
       </x:c>
       <x:c r="Z25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="AA25" s="50" t="n">
-        <x:f>IFERROR(D16/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.05723078108951537</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.057300000000000004</x:v>
       </x:c>
       <x:c r="AB25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="AC25" s="50" t="n">
-        <x:f>IFERROR(E16/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.04871324519612813</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0487</x:v>
       </x:c>
       <x:c r="AD25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="AE25" s="50" t="n">
-        <x:f>IFERROR(F16/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.08690599441119398</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.07437500000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -5214,36 +5214,36 @@
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="W26" s="50" t="n">
-        <x:f>IFERROR(B17/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.26363949139013715</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.26360000000000006</x:v>
       </x:c>
       <x:c r="X26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="Y26" s="50" t="n">
-        <x:f>IFERROR(C17/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.2029891652515887</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.203</x:v>
       </x:c>
       <x:c r="Z26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="AA26" s="50" t="n">
-        <x:f>IFERROR(D17/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.13581027618122676</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1358</x:v>
       </x:c>
       <x:c r="AB26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="AC26" s="50" t="n">
-        <x:f>IFERROR(E17/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.1919061476786995</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19190000000000002</x:v>
       </x:c>
       <x:c r="AD26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="AE26" s="50" t="n">
-        <x:f>IFERROR(F17/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.22780196583383455</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.198575</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -5274,36 +5274,36 @@
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="W27" s="50" t="n">
-        <x:f>IFERROR(B18/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.09777056332698032</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09780000000000001</x:v>
       </x:c>
       <x:c r="X27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="Y27" s="50" t="n">
-        <x:f>IFERROR(C18/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.10047580814998996</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1005</x:v>
       </x:c>
       <x:c r="Z27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="AA27" s="50" t="n">
-        <x:f>IFERROR(D18/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.08338056969282108</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0834</x:v>
       </x:c>
       <x:c r="AB27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="AC27" s="50" t="n">
-        <x:f>IFERROR(E18/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.03416657549949762</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0342</x:v>
       </x:c>
       <x:c r="AD27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="AE27" s="50" t="n">
-        <x:f>IFERROR(F18/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.08984998219732857</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.078975</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -5337,7 +5337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17f8b8e6b71c4f77"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f6a7ed608974b44"/>
 </x:worksheet>
 </file>
 
@@ -5661,36 +5661,36 @@
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>IFERROR(B19/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.08591007743801093</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.08010000000000002</x:v>
       </x:c>
       <x:c r="X12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>IFERROR(C19/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.11349116086939169</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.2029</x:v>
       </x:c>
       <x:c r="Z12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>IFERROR(D19/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.1057019622523328</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0983</x:v>
       </x:c>
       <x:c r="AB12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>IFERROR(E19/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.05249307537496133</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="AD12" t="str">
         <x:v>轉存金融機構</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>IFERROR(F19/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.10253316430655338</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.107325</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -5721,35 +5721,35 @@
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>IFERROR(B20/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>IFERROR(C20/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>IFERROR(D20/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>IFERROR(E20/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD13" t="str">
         <x:v>政策性貸款</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>IFERROR(F20/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -5781,36 +5781,36 @@
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>IFERROR(B21/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.025600000000000005</x:v>
       </x:c>
       <x:c r="X14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>IFERROR(C21/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.475007680466909</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.061200000000000004</x:v>
       </x:c>
       <x:c r="Z14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AA14" s="50" t="n">
-        <x:f>IFERROR(D21/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.026099999999999998</x:v>
       </x:c>
       <x:c r="AB14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>IFERROR(E21/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0174</x:v>
       </x:c>
       <x:c r="AD14" t="str">
         <x:v>短期票券</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>IFERROR(F21/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.032575</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -5841,36 +5841,36 @@
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>IFERROR(B22/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.042100000000000005</x:v>
       </x:c>
       <x:c r="X15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>IFERROR(C22/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>IFERROR(D22/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.043899999999999995</x:v>
       </x:c>
       <x:c r="AB15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>IFERROR(E22/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0691</x:v>
       </x:c>
       <x:c r="AD15" t="str">
         <x:v>公債、公司債、金融債券及特別股</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>IFERROR(F22/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.038775</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -5901,36 +5901,36 @@
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="W16" s="50" t="n">
-        <x:f>IFERROR(B23/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="Y16" s="50" t="n">
-        <x:f>IFERROR(C23/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.040466652577802666</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0724</x:v>
       </x:c>
       <x:c r="Z16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AA16" s="50" t="n">
-        <x:f>IFERROR(D23/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AC16" s="50" t="n">
-        <x:f>IFERROR(E23/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD16" t="str">
         <x:v>公債、金融債券、公司債及證券化商品</x:v>
       </x:c>
       <x:c r="AE16" s="50" t="n">
-        <x:f>IFERROR(F23/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.00961100816252155</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0181</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -5961,36 +5961,36 @@
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="W17" s="50" t="n">
-        <x:f>IFERROR(B24/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="Y17" s="50" t="n">
-        <x:f>IFERROR(C24/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AA17" s="50" t="n">
-        <x:f>IFERROR(D24/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.0010188259302816812</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0009</x:v>
       </x:c>
       <x:c r="AB17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AC17" s="50" t="n">
-        <x:f>IFERROR(E24/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD17" t="str">
         <x:v>房屋及土地</x:v>
       </x:c>
       <x:c r="AE17" s="50" t="n">
-        <x:f>IFERROR(F24/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.00017353785290100476</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.000225</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6021,36 +6021,36 @@
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="W18" s="50" t="n">
-        <x:f>IFERROR(B25/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="Y18" s="50" t="n">
-        <x:f>IFERROR(C25/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="AA18" s="50" t="n">
-        <x:f>IFERROR(D25/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.00048678091810010486</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0005</x:v>
       </x:c>
       <x:c r="AB18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="AC18" s="50" t="n">
-        <x:f>IFERROR(E25/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD18" t="str">
         <x:v>政府或公營事業貸款</x:v>
       </x:c>
       <x:c r="AE18" s="50" t="n">
-        <x:f>IFERROR(F25/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.00008291398250623317</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.000125</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -6081,36 +6081,36 @@
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="W19" s="50" t="n">
-        <x:f>IFERROR(B26/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="Y19" s="50" t="n">
-        <x:f>IFERROR(C26/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="AA19" s="50" t="n">
-        <x:f>IFERROR(D26/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.02204115775027534</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.020499999999999997</x:v>
       </x:c>
       <x:c r="AB19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="AC19" s="50" t="n">
-        <x:f>IFERROR(E26/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD19" t="str">
         <x:v>被保險人貸款</x:v>
       </x:c>
       <x:c r="AE19" s="50" t="n">
-        <x:f>IFERROR(F26/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.0037542970567873246</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.005124999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6141,36 +6141,36 @@
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="W20" s="50" t="n">
-        <x:f>IFERROR(B27/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.055961194533538296</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0522</x:v>
       </x:c>
       <x:c r="X20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="Y20" s="50" t="n">
-        <x:f>IFERROR(C27/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.04034712746974965</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0721</x:v>
       </x:c>
       <x:c r="Z20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="AA20" s="50" t="n">
-        <x:f>IFERROR(D27/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.3331317080001063</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.3098</x:v>
       </x:c>
       <x:c r="AB20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="AC20" s="50" t="n">
-        <x:f>IFERROR(E27/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.28681651089402854</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.262</x:v>
       </x:c>
       <x:c r="AD20" t="str">
         <x:v>股票及受益憑證投資（含期貨）</x:v>
       </x:c>
       <x:c r="AE20" s="50" t="n">
-        <x:f>IFERROR(F27/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.12643820937201783</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.174025</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -6196,36 +6196,36 @@
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="W21" s="50" t="n">
-        <x:f>IFERROR(B12/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.12953267317388073</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12080000000000002</x:v>
       </x:c>
       <x:c r="X21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="Y21" s="50" t="n">
-        <x:f>IFERROR(C12/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.013877837509840278</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0248</x:v>
       </x:c>
       <x:c r="Z21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="AA21" s="50" t="n">
-        <x:f>IFERROR(D12/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.12378380873949746</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1151</x:v>
       </x:c>
       <x:c r="AB21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="AC21" s="50" t="n">
-        <x:f>IFERROR(E12/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.13403073741045154</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12240000000000001</x:v>
       </x:c>
       <x:c r="AD21" t="str">
         <x:v>自行運用-國外-固定收益</x:v>
       </x:c>
       <x:c r="AE21" s="50" t="n">
-        <x:f>IFERROR(F12/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.11610091308162436</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.095775</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -6256,36 +6256,36 @@
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="W22" s="50" t="n">
-        <x:f>IFERROR(B13/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.015092963877875721</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.014100000000000001</x:v>
       </x:c>
       <x:c r="X22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="Y22" s="50" t="n">
-        <x:f>IFERROR(C13/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.010259022550242067</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0184</x:v>
       </x:c>
       <x:c r="Z22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="AA22" s="50" t="n">
-        <x:f>IFERROR(D13/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.06498542368738083</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0604</x:v>
       </x:c>
       <x:c r="AB22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="AC22" s="50" t="n">
-        <x:f>IFERROR(E13/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.07315031270084386</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0668</x:v>
       </x:c>
       <x:c r="AD22" t="str">
         <x:v>自行運用-國外-權益證券</x:v>
       </x:c>
       <x:c r="AE22" s="50" t="n">
-        <x:f>IFERROR(F13/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.02934192685892919</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.039925</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6316,36 +6316,36 @@
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="W23" s="50" t="n">
-        <x:f>IFERROR(B14/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.008290945766926794</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.007700000000000001</x:v>
       </x:c>
       <x:c r="X23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="Y23" s="50" t="n">
-        <x:f>IFERROR(C14/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="AA23" s="50" t="n">
-        <x:f>IFERROR(D14/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.0072035334470178895</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0067</x:v>
       </x:c>
       <x:c r="AB23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="AC23" s="50" t="n">
-        <x:f>IFERROR(E14/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.028460576033988435</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.026000000000000002</x:v>
       </x:c>
       <x:c r="AD23" t="str">
         <x:v>自行運用-國外-另類投資</x:v>
       </x:c>
       <x:c r="AE23" s="50" t="n">
-        <x:f>IFERROR(F14/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.008877103672406713</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.010100000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6376,36 +6376,36 @@
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="W24" s="50" t="n">
-        <x:f>IFERROR(B15/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.2104405841765572</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19620000000000004</x:v>
       </x:c>
       <x:c r="X24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="Y24" s="50" t="n">
-        <x:f>IFERROR(C15/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.08557910923436605</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.153</x:v>
       </x:c>
       <x:c r="Z24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="AA24" s="50" t="n">
-        <x:f>IFERROR(D15/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.044434094027364646</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.041299999999999996</x:v>
       </x:c>
       <x:c r="AB24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="AC24" s="50" t="n">
-        <x:f>IFERROR(E15/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.12423456388103749</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.11349999999999999</x:v>
       </x:c>
       <x:c r="AD24" t="str">
         <x:v>委託經營-國內-權益證券</x:v>
       </x:c>
       <x:c r="AE24" s="50" t="n">
-        <x:f>IFERROR(F15/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.168535157218321</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.126</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -6436,36 +6436,36 @@
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="W25" s="50" t="n">
-        <x:f>IFERROR(B16/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.10710053272306842</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09980000000000001</x:v>
       </x:c>
       <x:c r="X25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="Y25" s="50" t="n">
-        <x:f>IFERROR(C16/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.05126892436949562</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0917</x:v>
       </x:c>
       <x:c r="Z25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="AA25" s="50" t="n">
-        <x:f>IFERROR(D16/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.061535399591916395</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.057300000000000004</x:v>
       </x:c>
       <x:c r="AB25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="AC25" s="50" t="n">
-        <x:f>IFERROR(E16/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.05332745745535172</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0487</x:v>
       </x:c>
       <x:c r="AD25" t="str">
         <x:v>委託經營-國外-固定收益</x:v>
       </x:c>
       <x:c r="AE25" s="50" t="n">
-        <x:f>IFERROR(F16/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.09334918338528231</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.07437500000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -6496,36 +6496,36 @@
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="W26" s="50" t="n">
-        <x:f>IFERROR(B17/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.28279620723439863</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.26360000000000006</x:v>
       </x:c>
       <x:c r="X26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="Y26" s="50" t="n">
-        <x:f>IFERROR(C17/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.11351479999631743</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.203</x:v>
       </x:c>
       <x:c r="Z26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="AA26" s="50" t="n">
-        <x:f>IFERROR(D17/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.14602525868778218</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1358</x:v>
       </x:c>
       <x:c r="AB26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="AC26" s="50" t="n">
-        <x:f>IFERROR(E17/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.21008386701713133</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19190000000000002</x:v>
       </x:c>
       <x:c r="AD26" t="str">
         <x:v>委託經營-國外-權益證券</x:v>
       </x:c>
       <x:c r="AE26" s="50" t="n">
-        <x:f>IFERROR(F17/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.24469114735095152</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.198575</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -6556,36 +6556,36 @@
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="W27" s="50" t="n">
-        <x:f>IFERROR(B18/SUM(B19,B20,B21,B22,B23,B24,B25,B26,B27,B12,B13,B14,B15,B16,B17,B18),0)</x:f>
-        <x:v>0.10487482107574338</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09780000000000001</x:v>
       </x:c>
       <x:c r="X27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="Y27" s="50" t="n">
-        <x:f>IFERROR(C18/SUM(C19,C20,C21,C22,C23,C24,C25,C26,C27,C12,C13,C14,C15,C16,C17,C18),0)</x:f>
-        <x:v>0.05618768495588562</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1005</x:v>
       </x:c>
       <x:c r="Z27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="AA27" s="50" t="n">
-        <x:f>IFERROR(D18/SUM(D19,D20,D21,D22,D23,D24,D25,D26,D27,D12,D13,D14,D15,D16,D17,D18),0)</x:f>
-        <x:v>0.08965204696794446</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0834</x:v>
       </x:c>
       <x:c r="AB27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="AC27" s="50" t="n">
-        <x:f>IFERROR(E18/SUM(E19,E20,E21,E22,E23,E24,E25,E26,E27,E12,E13,E14,E15,E16,E17,E18),0)</x:f>
-        <x:v>0.03740289923220597</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0342</x:v>
       </x:c>
       <x:c r="AD27" t="str">
         <x:v>委託經營-國外-另類投資</x:v>
       </x:c>
       <x:c r="AE27" s="50" t="n">
-        <x:f>IFERROR(F18/SUM(F19,F20,F21,F22,F23,F24,F25,F26,F27,F12,F13,F14,F15,F16,F17,F18),0)</x:f>
-        <x:v>0.09651143769919772</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.078975</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -6621,7 +6621,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24b9563f4cd4b65"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68f018aaa4f94ad0"/>
 </x:worksheet>
 </file>
 
@@ -13443,7 +13443,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb66c285481594b01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74e78f0887e1484d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18482,7 +18482,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2577bbb40c2840e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45515c2be7a4ac8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26461,7 +26461,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5cb1800467847e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cf4438ae6a04441"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30400,7 +30400,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R449830fedb6e4c60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12862eef213a4eae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32564,7 +32564,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ecc9d40823948cb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4068634ba3d4894"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R669daac13ad74f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="R33a107dc429342d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R038d41fa085c48ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R90f8d2ff99c0436a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R98c7add857854f5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R95dcd709b20e4a79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R655147c3abff4a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rd797195441a049c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R00327db2d15443fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rea57131bbd824ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rc7f6dd0ef8624f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R8f610c8024324425"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R503ecde672d34e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R4ebe21c7b8d64aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R802666f003924e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R9c0fb9a211e949db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Red807b104c3e47b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R435746bd90384b4e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,118 +571,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$V$12:$V$27</c:f>
+              <c:f>'儀表板'!$V$12:$V$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -690,7 +582,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$W$12:$W$27</c:f>
+              <c:f>'儀表板'!$W$12:$W$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -781,118 +673,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$AD$12:$AD$27</c:f>
+              <c:f>'儀表板(美元)'!$AD$12:$AD$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -900,7 +684,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AE$12:$AE$27</c:f>
+              <c:f>'儀表板(美元)'!$AE$12:$AE$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1733,118 +1517,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$X$12:$X$27</c:f>
+              <c:f>'儀表板'!$X$12:$X$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1852,7 +1528,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$Y$12:$Y$27</c:f>
+              <c:f>'儀表板'!$Y$12:$Y$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1943,118 +1619,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$Z$12:$Z$27</c:f>
+              <c:f>'儀表板'!$Z$12:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2062,7 +1630,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AA$12:$AA$27</c:f>
+              <c:f>'儀表板'!$AA$12:$AA$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2153,118 +1721,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$AB$12:$AB$27</c:f>
+              <c:f>'儀表板'!$AB$12:$AB$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2272,7 +1732,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AC$12:$AC$27</c:f>
+              <c:f>'儀表板'!$AC$12:$AC$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2363,118 +1823,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$AD$12:$AD$27</c:f>
+              <c:f>'儀表板'!$AD$12:$AD$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2482,7 +1834,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AE$12:$AE$27</c:f>
+              <c:f>'儀表板'!$AE$12:$AE$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2573,118 +1925,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$V$12:$V$27</c:f>
+              <c:f>'儀表板(美元)'!$V$12:$V$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2692,7 +1936,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$W$12:$W$27</c:f>
+              <c:f>'儀表板(美元)'!$W$12:$W$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2783,118 +2027,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$X$12:$X$27</c:f>
+              <c:f>'儀表板(美元)'!$X$12:$X$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2902,7 +2038,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$Y$12:$Y$27</c:f>
+              <c:f>'儀表板(美元)'!$Y$12:$Y$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2993,118 +2129,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$Z$12:$Z$27</c:f>
+              <c:f>'儀表板(美元)'!$Z$12:$Z$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -3112,7 +2140,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AA$12:$AA$27</c:f>
+              <c:f>'儀表板(美元)'!$AA$12:$AA$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -3203,118 +2231,10 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$AB$12:$AB$27</c:f>
+              <c:f>'儀表板(美元)'!$AB$12:$AB$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -3322,7 +2242,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AC$12:$AC$27</c:f>
+              <c:f>'儀表板(美元)'!$AC$12:$AC$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -3375,7 +2295,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8bcbffc68bdd42c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rddc8e118ed474418"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3405,7 +2325,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re347ddf758a443cf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b65fbf37bde4894"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3435,7 +2355,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8327dbd615e5436d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4a329b0c78c647c2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3465,7 +2385,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc802eff804884510"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b4a3c4fd0d84121"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3495,7 +2415,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra942c1960ef0439b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R55ef10ffbb394b03"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3530,7 +2450,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref3eb68545f84288"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb2a6c0d367bd46fa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3560,7 +2480,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R06365c72ff574aa6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56c9937843464ec6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3590,7 +2510,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8fabfa9601cf43b8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c39af05f56c4eb8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3620,7 +2540,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3b8271fb31fc4e07"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra0ea1935afa845af"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3650,7 +2570,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9e842dc2cb7e4bfb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbe4c7fa4cb2f4027"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3685,7 +2605,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc1c31b906090403b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca4d8f8b1ada4398"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3715,7 +2635,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73cbe4e5c09a4c57"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R19e78b81399f4313"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3745,7 +2665,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reda42996294f4f1d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4beec4e9e464d05"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3775,7 +2695,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ca6cd30a901413c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfce1f130435241f8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4192,7 +3112,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="59" t="str">
         <x:v>詳見「業者彙總」</x:v>
@@ -4371,39 +3291,39 @@
         <x:v>來源與報價時間已註明</x:v>
       </x:c>
       <x:c r="V12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.08010000000000002</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.22060000000000002</x:v>
       </x:c>
       <x:c r="X12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.2029</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1165</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0983</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1724</x:v>
       </x:c>
       <x:c r="AB12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.048</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1711</x:v>
       </x:c>
       <x:c r="AD12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.107325</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.45747499999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4431,39 +3351,39 @@
         <x:v>2654.12955439</x:v>
       </x:c>
       <x:c r="V13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.4739</x:v>
       </x:c>
       <x:c r="X13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.3744</x:v>
       </x:c>
       <x:c r="Z13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.2375</x:v>
       </x:c>
       <x:c r="AB13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.3722</x:v>
       </x:c>
       <x:c r="AD13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.8622749999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4491,39 +3411,39 @@
         <x:v>802.98009492</x:v>
       </x:c>
       <x:c r="V14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.025600000000000005</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1055</x:v>
       </x:c>
       <x:c r="X14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.061200000000000004</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1005</x:v>
       </x:c>
       <x:c r="Z14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="AA14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.026099999999999998</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.0901</x:v>
       </x:c>
       <x:c r="AB14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0174</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.060200000000000004</x:v>
       </x:c>
       <x:c r="AD14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.032575</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.119375</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4551,39 +3471,39 @@
         <x:v>15244.879584</x:v>
       </x:c>
       <x:c r="V15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.042100000000000005</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.19999999999999998</x:v>
       </x:c>
       <x:c r="X15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.4086</x:v>
       </x:c>
       <x:c r="Z15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.043899999999999995</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AB15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0691</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.3965</x:v>
       </x:c>
       <x:c r="AD15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.038775</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.9830249999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4610,41 +3530,6 @@
         <x:f>SUM(B16:E16)</x:f>
         <x:v>8443.91807301</x:v>
       </x:c>
-      <x:c r="V16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="W16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="Y16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0724</x:v>
-      </x:c>
-      <x:c r="Z16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="AA16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="AC16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="AE16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0181</x:v>
-      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="30" t="str">
@@ -4670,41 +3555,6 @@
         <x:f>SUM(B17:E17)</x:f>
         <x:v>22133.584103189998</x:v>
       </x:c>
-      <x:c r="V17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="W17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="Y17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="AA17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0009</x:v>
-      </x:c>
-      <x:c r="AB17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="AC17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="AE17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.000225</x:v>
-      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="30" t="str">
@@ -4730,41 +3580,6 @@
         <x:f>SUM(B18:E18)</x:f>
         <x:v>8729.960386230001</x:v>
       </x:c>
-      <x:c r="V18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="W18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="Y18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="AA18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0005</x:v>
-      </x:c>
-      <x:c r="AB18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="AC18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="AE18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.000125</x:v>
-      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="30" t="str">
@@ -4790,41 +3605,6 @@
         <x:f>SUM(B19:E19)</x:f>
         <x:v>9274.65680763</x:v>
       </x:c>
-      <x:c r="V19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="W19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="Y19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="AA19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.020499999999999997</x:v>
-      </x:c>
-      <x:c r="AB19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="AC19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="AE19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.005124999999999999</x:v>
-      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="30" t="str">
@@ -4850,41 +3630,6 @@
         <x:f>SUM(B20:E20)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="W20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0522</x:v>
-      </x:c>
-      <x:c r="X20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="Y20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0721</x:v>
-      </x:c>
-      <x:c r="Z20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="AA20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.3098</x:v>
-      </x:c>
-      <x:c r="AB20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="AC20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.262</x:v>
-      </x:c>
-      <x:c r="AD20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="AE20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.174025</x:v>
-      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="30" t="str">
@@ -4910,41 +3655,6 @@
         <x:f>SUM(B21:E21)</x:f>
         <x:v>2849.5867313800004</x:v>
       </x:c>
-      <x:c r="V21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="W21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.12080000000000002</x:v>
-      </x:c>
-      <x:c r="X21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="Y21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0248</x:v>
-      </x:c>
-      <x:c r="Z21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AA21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.1151</x:v>
-      </x:c>
-      <x:c r="AB21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AC21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.12240000000000001</x:v>
-      </x:c>
-      <x:c r="AD21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AE21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.095775</x:v>
-      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="30" t="str">
@@ -4970,41 +3680,6 @@
         <x:f>SUM(B22:E22)</x:f>
         <x:v>3856.7386907</x:v>
       </x:c>
-      <x:c r="V22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="W22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.014100000000000001</x:v>
-      </x:c>
-      <x:c r="X22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="Y22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0184</x:v>
-      </x:c>
-      <x:c r="Z22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AA22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0604</x:v>
-      </x:c>
-      <x:c r="AB22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AC22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0668</x:v>
-      </x:c>
-      <x:c r="AD22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AE22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.039925</x:v>
-      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="30" t="str">
@@ -5030,41 +3705,6 @@
         <x:f>SUM(B23:E23)</x:f>
         <x:v>869.36556465</x:v>
       </x:c>
-      <x:c r="V23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="W23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.007700000000000001</x:v>
-      </x:c>
-      <x:c r="X23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="Y23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AA23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0067</x:v>
-      </x:c>
-      <x:c r="AB23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AC23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.026000000000000002</x:v>
-      </x:c>
-      <x:c r="AD23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AE23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.010100000000000001</x:v>
-      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="30" t="str">
@@ -5090,41 +3730,6 @@
         <x:f>SUM(B24:E24)</x:f>
         <x:v>15.69739937</x:v>
       </x:c>
-      <x:c r="V24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="W24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.19620000000000004</x:v>
-      </x:c>
-      <x:c r="X24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="Y24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.153</x:v>
-      </x:c>
-      <x:c r="Z24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="AA24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.041299999999999996</x:v>
-      </x:c>
-      <x:c r="AB24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="AC24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.11349999999999999</x:v>
-      </x:c>
-      <x:c r="AD24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="AE24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.126</x:v>
-      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="30" t="str">
@@ -5150,41 +3755,6 @@
         <x:f>SUM(B25:E25)</x:f>
         <x:v>7.5</x:v>
       </x:c>
-      <x:c r="V25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="W25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.09980000000000001</x:v>
-      </x:c>
-      <x:c r="X25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="Y25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0917</x:v>
-      </x:c>
-      <x:c r="Z25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AA25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.057300000000000004</x:v>
-      </x:c>
-      <x:c r="AB25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AC25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0487</x:v>
-      </x:c>
-      <x:c r="AD25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AE25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.07437500000000001</x:v>
-      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="30" t="str">
@@ -5210,41 +3780,6 @@
         <x:f>SUM(B26:E26)</x:f>
         <x:v>339.59565172</x:v>
       </x:c>
-      <x:c r="V26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="W26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.26360000000000006</x:v>
-      </x:c>
-      <x:c r="X26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="Y26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.203</x:v>
-      </x:c>
-      <x:c r="Z26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AA26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.1358</x:v>
-      </x:c>
-      <x:c r="AB26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AC26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.19190000000000002</x:v>
-      </x:c>
-      <x:c r="AD26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AE26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.198575</x:v>
-      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="30" t="str">
@@ -5269,41 +3804,6 @@
       <x:c r="F27" s="66" t="n">
         <x:f>SUM(B27:E27)</x:f>
         <x:v>11436.992189089999</x:v>
-      </x:c>
-      <x:c r="V27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="W27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.09780000000000001</x:v>
-      </x:c>
-      <x:c r="X27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="Y27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.1005</x:v>
-      </x:c>
-      <x:c r="Z27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AA27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0834</x:v>
-      </x:c>
-      <x:c r="AB27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AC27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0342</x:v>
-      </x:c>
-      <x:c r="AD27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AE27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.078975</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -5337,7 +3837,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f6a7ed608974b44"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e123d448f714b76"/>
 </x:worksheet>
 </file>
 
@@ -5479,7 +3979,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="J6" s="58" t="n">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="59" t="str">
         <x:v>詳見「業者彙總」</x:v>
@@ -5658,39 +4158,39 @@
         <x:v>來源與報價時間已註明</x:v>
       </x:c>
       <x:c r="V12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.08010000000000002</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.22060000000000002</x:v>
       </x:c>
       <x:c r="X12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.2029</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1165</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0983</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1724</x:v>
       </x:c>
       <x:c r="AB12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.048</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1711</x:v>
       </x:c>
       <x:c r="AD12" t="str">
-        <x:v>轉存金融機構</x:v>
+        <x:v>固定收益</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.107325</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.45747499999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -5718,39 +4218,39 @@
         <x:v>8.30843498009078</x:v>
       </x:c>
       <x:c r="V13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.4739</x:v>
       </x:c>
       <x:c r="X13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.3744</x:v>
       </x:c>
       <x:c r="Z13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.2375</x:v>
       </x:c>
       <x:c r="AB13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.3722</x:v>
       </x:c>
       <x:c r="AD13" t="str">
-        <x:v>政策性貸款</x:v>
+        <x:v>權益證券</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.8622749999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -5778,39 +4278,39 @@
         <x:v>2.513633103521678</x:v>
       </x:c>
       <x:c r="V14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.025600000000000005</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1055</x:v>
       </x:c>
       <x:c r="X14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.061200000000000004</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.1005</x:v>
       </x:c>
       <x:c r="Z14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="AA14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.026099999999999998</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.0901</x:v>
       </x:c>
       <x:c r="AB14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0174</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.060200000000000004</x:v>
       </x:c>
       <x:c r="AD14" t="str">
-        <x:v>短期票券</x:v>
+        <x:v>另類投資</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.032575</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.119375</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -5838,39 +4338,39 @@
         <x:v>47.7222713538895</x:v>
       </x:c>
       <x:c r="V15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.042100000000000005</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.19999999999999998</x:v>
       </x:c>
       <x:c r="X15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.4086</x:v>
       </x:c>
       <x:c r="Z15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.043899999999999995</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AB15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0691</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.3965</x:v>
       </x:c>
       <x:c r="AD15" t="str">
-        <x:v>公債、公司債、金融債券及特別股</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.038775</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
+        <x:v>0.9830249999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -5897,41 +4397,6 @@
         <x:f>SUM(B16:E16)</x:f>
         <x:v>26.432675138550632</x:v>
       </x:c>
-      <x:c r="V16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="W16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="Y16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0724</x:v>
-      </x:c>
-      <x:c r="Z16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="AA16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="AC16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD16" t="str">
-        <x:v>公債、金融債券、公司債及證券化商品</x:v>
-      </x:c>
-      <x:c r="AE16" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0181</x:v>
-      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="30" t="str">
@@ -5957,41 +4422,6 @@
         <x:f>SUM(B17:E17)</x:f>
         <x:v>69.28653655717639</x:v>
       </x:c>
-      <x:c r="V17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="W17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="Y17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="AA17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0009</x:v>
-      </x:c>
-      <x:c r="AB17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="AC17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD17" t="str">
-        <x:v>房屋及土地</x:v>
-      </x:c>
-      <x:c r="AE17" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.000225</x:v>
-      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="30" t="str">
@@ -6017,41 +4447,6 @@
         <x:f>SUM(B18:E18)</x:f>
         <x:v>27.32809637260917</x:v>
       </x:c>
-      <x:c r="V18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="W18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="Y18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="AA18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0005</x:v>
-      </x:c>
-      <x:c r="AB18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="AC18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD18" t="str">
-        <x:v>政府或公營事業貸款</x:v>
-      </x:c>
-      <x:c r="AE18" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.000125</x:v>
-      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="30" t="str">
@@ -6077,41 +4472,6 @@
         <x:f>SUM(B19:E19)</x:f>
         <x:v>29.033203342087965</x:v>
       </x:c>
-      <x:c r="V19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="W19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="Y19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="AA19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.020499999999999997</x:v>
-      </x:c>
-      <x:c r="AB19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="AC19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD19" t="str">
-        <x:v>被保險人貸款</x:v>
-      </x:c>
-      <x:c r="AE19" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.005124999999999999</x:v>
-      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="81" t="str">
@@ -6137,41 +4497,6 @@
         <x:f>SUM(B20:E20)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="W20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0522</x:v>
-      </x:c>
-      <x:c r="X20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="Y20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0721</x:v>
-      </x:c>
-      <x:c r="Z20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="AA20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.3098</x:v>
-      </x:c>
-      <x:c r="AB20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="AC20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.262</x:v>
-      </x:c>
-      <x:c r="AD20" t="str">
-        <x:v>股票及受益憑證投資（含期貨）</x:v>
-      </x:c>
-      <x:c r="AE20" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.174025</x:v>
-      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="30" t="str">
@@ -6192,41 +4517,6 @@
       <x:c r="F21" s="74" t="str">
         <x:v>TWD／USD</x:v>
       </x:c>
-      <x:c r="V21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="W21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.12080000000000002</x:v>
-      </x:c>
-      <x:c r="X21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="Y21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0248</x:v>
-      </x:c>
-      <x:c r="Z21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AA21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.1151</x:v>
-      </x:c>
-      <x:c r="AB21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AC21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.12240000000000001</x:v>
-      </x:c>
-      <x:c r="AD21" t="str">
-        <x:v>自行運用-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AE21" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.095775</x:v>
-      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="90" t="str">
@@ -6252,41 +4542,6 @@
         <x:f>SUM(B22:E22)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="W22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.014100000000000001</x:v>
-      </x:c>
-      <x:c r="X22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="Y22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0184</x:v>
-      </x:c>
-      <x:c r="Z22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AA22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0604</x:v>
-      </x:c>
-      <x:c r="AB22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AC22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0668</x:v>
-      </x:c>
-      <x:c r="AD22" t="str">
-        <x:v>自行運用-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AE22" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.039925</x:v>
-      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="30" t="str">
@@ -6312,41 +4567,6 @@
         <x:f>SUM(B23:E23)</x:f>
         <x:v>2.721444872906558</x:v>
       </x:c>
-      <x:c r="V23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="W23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.007700000000000001</x:v>
-      </x:c>
-      <x:c r="X23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="Y23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AA23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0067</x:v>
-      </x:c>
-      <x:c r="AB23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AC23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.026000000000000002</x:v>
-      </x:c>
-      <x:c r="AD23" t="str">
-        <x:v>自行運用-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AE23" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.010100000000000001</x:v>
-      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="30" t="str">
@@ -6372,41 +4592,6 @@
         <x:f>SUM(B24:E24)</x:f>
         <x:v>0.049138830395993115</x:v>
       </x:c>
-      <x:c r="V24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="W24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.19620000000000004</x:v>
-      </x:c>
-      <x:c r="X24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="Y24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.153</x:v>
-      </x:c>
-      <x:c r="Z24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="AA24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.041299999999999996</x:v>
-      </x:c>
-      <x:c r="AB24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="AC24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.11349999999999999</x:v>
-      </x:c>
-      <x:c r="AD24" t="str">
-        <x:v>委託經營-國內-權益證券</x:v>
-      </x:c>
-      <x:c r="AE24" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.126</x:v>
-      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="30" t="str">
@@ -6432,41 +4617,6 @@
         <x:f>SUM(B25:E25)</x:f>
         <x:v>0.023477852559085927</x:v>
       </x:c>
-      <x:c r="V25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="W25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.09980000000000001</x:v>
-      </x:c>
-      <x:c r="X25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="Y25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0917</x:v>
-      </x:c>
-      <x:c r="Z25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AA25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.057300000000000004</x:v>
-      </x:c>
-      <x:c r="AB25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AC25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0487</x:v>
-      </x:c>
-      <x:c r="AD25" t="str">
-        <x:v>委託經營-國外-固定收益</x:v>
-      </x:c>
-      <x:c r="AE25" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.07437500000000001</x:v>
-      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="30" t="str">
@@ -6492,41 +4642,6 @@
         <x:f>SUM(B26:E26)</x:f>
         <x:v>1.0630635521051808</x:v>
       </x:c>
-      <x:c r="V26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="W26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.26360000000000006</x:v>
-      </x:c>
-      <x:c r="X26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="Y26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.203</x:v>
-      </x:c>
-      <x:c r="Z26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AA26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.1358</x:v>
-      </x:c>
-      <x:c r="AB26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AC26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.19190000000000002</x:v>
-      </x:c>
-      <x:c r="AD26" t="str">
-        <x:v>委託經營-國外-權益證券</x:v>
-      </x:c>
-      <x:c r="AE26" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.198575</x:v>
-      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="30" t="str">
@@ -6551,41 +4666,6 @@
       <x:c r="F27" s="75" t="n">
         <x:f>SUM(B27:E27)</x:f>
         <x:v>35.80213551131632</x:v>
-      </x:c>
-      <x:c r="V27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="W27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.09780000000000001</x:v>
-      </x:c>
-      <x:c r="X27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="Y27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.1005</x:v>
-      </x:c>
-      <x:c r="Z27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AA27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0834</x:v>
-      </x:c>
-      <x:c r="AB27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AC27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.0342</x:v>
-      </x:c>
-      <x:c r="AD27" t="str">
-        <x:v>委託經營-國外-另類投資</x:v>
-      </x:c>
-      <x:c r="AE27" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
-        <x:v>0.078975</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -6621,7 +4701,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68f018aaa4f94ad0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576dfdfedbb3494b"/>
 </x:worksheet>
 </file>
 
@@ -13443,7 +11523,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74e78f0887e1484d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55ff615b097e473d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18482,7 +16562,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45515c2be7a4ac8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e109314e2a44d04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22194,7 +20274,7 @@
         <x:v>100-1全球基本面指數被動股票型(續約3)</x:v>
       </x:c>
       <x:c r="F87" s="31" t="str">
-        <x:v>瑞銀</x:v>
+        <x:v>UBS</x:v>
       </x:c>
       <x:c r="G87" s="40" t="n">
         <x:v>361201485</x:v>
@@ -23758,7 +21838,7 @@
         <x:v>104-2全球不動產有價證券型(續約2)</x:v>
       </x:c>
       <x:c r="F123" s="31" t="str">
-        <x:v>信安環球</x:v>
+        <x:v>信安</x:v>
       </x:c>
       <x:c r="G123" s="40" t="n">
         <x:v>425091462</x:v>
@@ -25940,7 +24020,7 @@
         <x:v>100-1全球基本面指數被動股票型(續約2)</x:v>
       </x:c>
       <x:c r="F175" s="31" t="str">
-        <x:v>瑞銀</x:v>
+        <x:v>UBS</x:v>
       </x:c>
       <x:c r="G175" s="40" t="n">
         <x:v>0</x:v>
@@ -26168,7 +24248,7 @@
         <x:v>109年第二次委託經營(相對報酬)</x:v>
       </x:c>
       <x:c r="F181" s="31" t="str">
-        <x:v>安聯</x:v>
+        <x:v>Allianz</x:v>
       </x:c>
       <x:c r="G181" s="40" t="n">
         <x:v>0</x:v>
@@ -26244,7 +24324,7 @@
         <x:v>109年第二次委託經營(相對報酬)</x:v>
       </x:c>
       <x:c r="F183" s="31" t="str">
-        <x:v>野村</x:v>
+        <x:v>Nomura</x:v>
       </x:c>
       <x:c r="G183" s="40" t="n">
         <x:v>0</x:v>
@@ -26461,7 +24541,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cf4438ae6a04441"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6614b9a4d8354037"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30400,7 +28480,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12862eef213a4eae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R234131b6140b42c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30752,11 +28832,11 @@
         <x:v>17827431853</x:v>
       </x:c>
       <x:c r="J9" s="42" t="n">
-        <x:f>IFERROR(I9/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I9/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.1425863938130672</x:v>
       </x:c>
       <x:c r="K9" s="28" t="n">
-        <x:f>RANK(I9,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I9,$I$9:$I$54,0)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L9" s="29" t="n">
@@ -30830,11 +28910,11 @@
         <x:v>12270337973</x:v>
       </x:c>
       <x:c r="J10" s="43" t="n">
-        <x:f>IFERROR(I10/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I10/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.09813994841568788</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:f>RANK(I10,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I10,$I$9:$I$54,0)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="L10" s="32" t="n">
@@ -30908,11 +28988,11 @@
         <x:v>8229076099</x:v>
       </x:c>
       <x:c r="J11" s="43" t="n">
-        <x:f>IFERROR(I11/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I11/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.0658173479525746</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
-        <x:f>RANK(I11,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I11,$I$9:$I$54,0)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="L11" s="32" t="n">
@@ -30986,11 +29066,11 @@
         <x:v>6499168753</x:v>
       </x:c>
       <x:c r="J12" s="43" t="n">
-        <x:f>IFERROR(I12/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I12/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.05198129730148962</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
-        <x:f>RANK(I12,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I12,$I$9:$I$54,0)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="L12" s="32" t="n">
@@ -31064,11 +29144,11 @@
         <x:v>6233333079</x:v>
       </x:c>
       <x:c r="J13" s="43" t="n">
-        <x:f>IFERROR(I13/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I13/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.04985510490232206</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
-        <x:f>RANK(I13,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I13,$I$9:$I$54,0)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="L13" s="32" t="n">
@@ -31142,11 +29222,11 @@
         <x:v>5911641695</x:v>
       </x:c>
       <x:c r="J14" s="43" t="n">
-        <x:f>IFERROR(I14/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I14/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.04728217040768952</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
-        <x:f>RANK(I14,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I14,$I$9:$I$54,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="L14" s="32" t="n">
@@ -31159,7 +29239,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="Q14" s="51" t="n">
-        <x:f>SUM(I19:I58)</x:f>
+        <x:f>SUM(I19:I54)</x:f>
         <x:v>49028845422</x:v>
       </x:c>
       <x:c r="R14" s="50" t="n">
@@ -31219,11 +29299,11 @@
         <x:v>5214617387</x:v>
       </x:c>
       <x:c r="J15" s="43" t="n">
-        <x:f>IFERROR(I15/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I15/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.041707268576776396</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
-        <x:f>RANK(I15,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I15,$I$9:$I$54,0)</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="L15" s="32" t="n">
@@ -31267,11 +29347,11 @@
         <x:v>4884050215</x:v>
       </x:c>
       <x:c r="J16" s="43" t="n">
-        <x:f>IFERROR(I16/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I16/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.0390633442383119</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
-        <x:f>RANK(I16,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I16,$I$9:$I$54,0)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="L16" s="32" t="n">
@@ -31315,11 +29395,11 @@
         <x:v>4847721016</x:v>
       </x:c>
       <x:c r="J17" s="43" t="n">
-        <x:f>IFERROR(I17/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I17/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.03877277801889003</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
-        <x:f>RANK(I17,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I17,$I$9:$I$54,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="L17" s="32" t="n">
@@ -31363,11 +29443,11 @@
         <x:v>4082759823</x:v>
       </x:c>
       <x:c r="J18" s="43" t="n">
-        <x:f>IFERROR(I18/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I18/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.03265450709707709</x:v>
       </x:c>
       <x:c r="K18" s="31" t="n">
-        <x:f>RANK(I18,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I18,$I$9:$I$54,0)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="L18" s="32" t="n">
@@ -31411,11 +29491,11 @@
         <x:v>3525432785</x:v>
       </x:c>
       <x:c r="J19" s="43" t="n">
-        <x:f>IFERROR(I19/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I19/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.028196924357274576</x:v>
       </x:c>
       <x:c r="K19" s="31" t="n">
-        <x:f>RANK(I19,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I19,$I$9:$I$54,0)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="L19" s="32" t="n">
@@ -31459,11 +29539,11 @@
         <x:v>3467884297</x:v>
       </x:c>
       <x:c r="J20" s="43" t="n">
-        <x:f>IFERROR(I20/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I20/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.02773664317707005</x:v>
       </x:c>
       <x:c r="K20" s="31" t="n">
-        <x:f>RANK(I20,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I20,$I$9:$I$54,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="L20" s="32" t="n">
@@ -31507,11 +29587,11 @@
         <x:v>3039287910</x:v>
       </x:c>
       <x:c r="J21" s="43" t="n">
-        <x:f>IFERROR(I21/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I21/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.024308666913996812</x:v>
       </x:c>
       <x:c r="K21" s="31" t="n">
-        <x:f>RANK(I21,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I21,$I$9:$I$54,0)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="L21" s="32" t="n">
@@ -31555,11 +29635,11 @@
         <x:v>3033228329</x:v>
       </x:c>
       <x:c r="J22" s="43" t="n">
-        <x:f>IFERROR(I22/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I22/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.024260201503502884</x:v>
       </x:c>
       <x:c r="K22" s="31" t="n">
-        <x:f>RANK(I22,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I22,$I$9:$I$54,0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="L22" s="32" t="n">
@@ -31603,11 +29683,11 @@
         <x:v>2941839542</x:v>
       </x:c>
       <x:c r="J23" s="43" t="n">
-        <x:f>IFERROR(I23/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I23/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.023529260688206054</x:v>
       </x:c>
       <x:c r="K23" s="31" t="n">
-        <x:f>RANK(I23,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I23,$I$9:$I$54,0)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="L23" s="32" t="n">
@@ -31651,11 +29731,11 @@
         <x:v>2584189383</x:v>
       </x:c>
       <x:c r="J24" s="43" t="n">
-        <x:f>IFERROR(I24/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I24/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.02066872267919953</x:v>
       </x:c>
       <x:c r="K24" s="31" t="n">
-        <x:f>RANK(I24,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I24,$I$9:$I$54,0)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="L24" s="32" t="n">
@@ -31699,11 +29779,11 @@
         <x:v>2458832253</x:v>
       </x:c>
       <x:c r="J25" s="43" t="n">
-        <x:f>IFERROR(I25/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I25/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.019666098114268265</x:v>
       </x:c>
       <x:c r="K25" s="31" t="n">
-        <x:f>RANK(I25,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I25,$I$9:$I$54,0)</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="L25" s="32" t="n">
@@ -31747,11 +29827,11 @@
         <x:v>2389413786</x:v>
       </x:c>
       <x:c r="J26" s="43" t="n">
-        <x:f>IFERROR(I26/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I26/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.019110879114965472</x:v>
       </x:c>
       <x:c r="K26" s="31" t="n">
-        <x:f>RANK(I26,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I26,$I$9:$I$54,0)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="L26" s="32" t="n">
@@ -31772,11 +29852,11 @@
         <x:v>1806278590</x:v>
       </x:c>
       <x:c r="J27" s="43" t="n">
-        <x:f>IFERROR(I27/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I27/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.014446878972447797</x:v>
       </x:c>
       <x:c r="K27" s="31" t="n">
-        <x:f>RANK(I27,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I27,$I$9:$I$54,0)</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="L27" s="32" t="n">
@@ -31797,11 +29877,11 @@
         <x:v>1719232558</x:v>
       </x:c>
       <x:c r="J28" s="43" t="n">
-        <x:f>IFERROR(I28/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I28/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.013750672143502425</x:v>
       </x:c>
       <x:c r="K28" s="31" t="n">
-        <x:f>RANK(I28,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I28,$I$9:$I$54,0)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="L28" s="32" t="n">
@@ -31822,11 +29902,11 @@
         <x:v>1709168484</x:v>
       </x:c>
       <x:c r="J29" s="43" t="n">
-        <x:f>IFERROR(I29/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I29/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.013670178215349427</x:v>
       </x:c>
       <x:c r="K29" s="31" t="n">
-        <x:f>RANK(I29,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I29,$I$9:$I$54,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="L29" s="32" t="n">
@@ -31847,11 +29927,11 @@
         <x:v>1679948361</x:v>
       </x:c>
       <x:c r="J30" s="43" t="n">
-        <x:f>IFERROR(I30/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I30/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.013436471420130734</x:v>
       </x:c>
       <x:c r="K30" s="31" t="n">
-        <x:f>RANK(I30,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I30,$I$9:$I$54,0)</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="L30" s="32" t="n">
@@ -31872,11 +29952,11 @@
         <x:v>1388520134</x:v>
       </x:c>
       <x:c r="J31" s="43" t="n">
-        <x:f>IFERROR(I31/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I31/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.011105586058408076</x:v>
       </x:c>
       <x:c r="K31" s="31" t="n">
-        <x:f>RANK(I31,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I31,$I$9:$I$54,0)</x:f>
         <x:v>23</x:v>
       </x:c>
       <x:c r="L31" s="32" t="n">
@@ -31897,11 +29977,11 @@
         <x:v>1352096519</x:v>
       </x:c>
       <x:c r="J32" s="43" t="n">
-        <x:f>IFERROR(I32/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I32/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.01081426468608088</x:v>
       </x:c>
       <x:c r="K32" s="31" t="n">
-        <x:f>RANK(I32,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I32,$I$9:$I$54,0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="L32" s="32" t="n">
@@ -31922,11 +30002,11 @@
         <x:v>1337309953</x:v>
       </x:c>
       <x:c r="J33" s="43" t="n">
-        <x:f>IFERROR(I33/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I33/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.01069599957979951</x:v>
       </x:c>
       <x:c r="K33" s="31" t="n">
-        <x:f>RANK(I33,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I33,$I$9:$I$54,0)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="L33" s="32" t="n">
@@ -31936,22 +30016,22 @@
     </x:row>
     <x:row r="34">
       <x:c r="G34" s="30" t="str">
-        <x:v>Insight</x:v>
+        <x:v>信安</x:v>
       </x:c>
       <x:c r="H34" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G34,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>1229834121</x:v>
+        <x:v>1133980105</x:v>
       </x:c>
       <x:c r="I34" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G34,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>1218224544</x:v>
+        <x:v>1279212590</x:v>
       </x:c>
       <x:c r="J34" s="43" t="n">
-        <x:f>IFERROR(I34/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.009743537151948088</x:v>
+        <x:f>IFERROR(I34/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.01023132841748486</x:v>
       </x:c>
       <x:c r="K34" s="31" t="n">
-        <x:f>RANK(I34,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I34,$I$9:$I$54,0)</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="L34" s="32" t="n">
@@ -31961,97 +30041,97 @@
     </x:row>
     <x:row r="35">
       <x:c r="G35" s="30" t="str">
-        <x:v>American Century</x:v>
+        <x:v>Insight</x:v>
       </x:c>
       <x:c r="H35" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G35,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>959838014</x:v>
+        <x:v>1229834121</x:v>
       </x:c>
       <x:c r="I35" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G35,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>1175399124</x:v>
+        <x:v>1218224544</x:v>
       </x:c>
       <x:c r="J35" s="43" t="n">
-        <x:f>IFERROR(I35/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.00940101321178211</x:v>
+        <x:f>IFERROR(I35/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.009743537151948088</x:v>
       </x:c>
       <x:c r="K35" s="31" t="n">
-        <x:f>RANK(I35,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I35,$I$9:$I$54,0)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="L35" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G35,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="G36" s="30" t="str">
-        <x:v>T. Rowe Price</x:v>
+        <x:v>American Century</x:v>
       </x:c>
       <x:c r="H36" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G36,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>960000000</x:v>
+        <x:v>959838014</x:v>
       </x:c>
       <x:c r="I36" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G36,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>1142513053</x:v>
+        <x:v>1175399124</x:v>
       </x:c>
       <x:c r="J36" s="43" t="n">
-        <x:f>IFERROR(I36/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.009137985631071913</x:v>
+        <x:f>IFERROR(I36/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.00940101321178211</x:v>
       </x:c>
       <x:c r="K36" s="31" t="n">
-        <x:f>RANK(I36,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I36,$I$9:$I$54,0)</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="L36" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G36,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="G37" s="30" t="str">
-        <x:v>Ninety One</x:v>
+        <x:v>T. Rowe Price</x:v>
       </x:c>
       <x:c r="H37" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G37,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>900000000</x:v>
+        <x:v>960000000</x:v>
       </x:c>
       <x:c r="I37" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G37,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>1077267573</x:v>
+        <x:v>1142513053</x:v>
       </x:c>
       <x:c r="J37" s="43" t="n">
-        <x:f>IFERROR(I37/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.008616142788955701</x:v>
+        <x:f>IFERROR(I37/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.009137985631071913</x:v>
       </x:c>
       <x:c r="K37" s="31" t="n">
-        <x:f>RANK(I37,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I37,$I$9:$I$54,0)</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="L37" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G37,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="G38" s="30" t="str">
-        <x:v>ClearBridge</x:v>
+        <x:v>Ninety One</x:v>
       </x:c>
       <x:c r="H38" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G38,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>760000000</x:v>
+        <x:v>900000000</x:v>
       </x:c>
       <x:c r="I38" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G38,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>1047858894</x:v>
+        <x:v>1077267573</x:v>
       </x:c>
       <x:c r="J38" s="43" t="n">
-        <x:f>IFERROR(I38/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.00838092789541452</x:v>
+        <x:f>IFERROR(I38/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.008616142788955701</x:v>
       </x:c>
       <x:c r="K38" s="31" t="n">
-        <x:f>RANK(I38,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I38,$I$9:$I$54,0)</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="L38" s="32" t="n">
@@ -32061,47 +30141,47 @@
     </x:row>
     <x:row r="39">
       <x:c r="G39" s="30" t="str">
-        <x:v>聯博</x:v>
+        <x:v>ClearBridge</x:v>
       </x:c>
       <x:c r="H39" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G39,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>900495639</x:v>
+        <x:v>760000000</x:v>
       </x:c>
       <x:c r="I39" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G39,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>897752897</x:v>
+        <x:v>1047858894</x:v>
       </x:c>
       <x:c r="J39" s="43" t="n">
-        <x:f>IFERROR(I39/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.007180358291310641</x:v>
+        <x:f>IFERROR(I39/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.00838092789541452</x:v>
       </x:c>
       <x:c r="K39" s="31" t="n">
-        <x:f>RANK(I39,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I39,$I$9:$I$54,0)</x:f>
         <x:v>31</x:v>
       </x:c>
       <x:c r="L39" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G39,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="G40" s="30" t="str">
-        <x:v>信安</x:v>
+        <x:v>聯博</x:v>
       </x:c>
       <x:c r="H40" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G40,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>708888643</x:v>
+        <x:v>900495639</x:v>
       </x:c>
       <x:c r="I40" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G40,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>801020312</x:v>
+        <x:v>897752897</x:v>
       </x:c>
       <x:c r="J40" s="43" t="n">
-        <x:f>IFERROR(I40/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.006406677002098759</x:v>
+        <x:f>IFERROR(I40/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.007180358291310641</x:v>
       </x:c>
       <x:c r="K40" s="31" t="n">
-        <x:f>RANK(I40,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I40,$I$9:$I$54,0)</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="L40" s="32" t="n">
@@ -32111,197 +30191,197 @@
     </x:row>
     <x:row r="41">
       <x:c r="G41" s="30" t="str">
-        <x:v>Pictet</x:v>
+        <x:v>UBS</x:v>
       </x:c>
       <x:c r="H41" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G41,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>618843493</x:v>
+        <x:v>761201485</x:v>
       </x:c>
       <x:c r="I41" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G41,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>769778438</x:v>
+        <x:v>789561325</x:v>
       </x:c>
       <x:c r="J41" s="43" t="n">
-        <x:f>IFERROR(I41/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.00615679994822167</x:v>
+        <x:f>IFERROR(I41/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.0063150263568149375</x:v>
       </x:c>
       <x:c r="K41" s="31" t="n">
-        <x:f>RANK(I41,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I41,$I$9:$I$54,0)</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="L41" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G41,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="G42" s="30" t="str">
-        <x:v>滙豐</x:v>
+        <x:v>Pictet</x:v>
       </x:c>
       <x:c r="H42" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G42,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>460000000</x:v>
+        <x:v>618843493</x:v>
       </x:c>
       <x:c r="I42" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G42,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>706462588</x:v>
+        <x:v>769778438</x:v>
       </x:c>
       <x:c r="J42" s="43" t="n">
-        <x:f>IFERROR(I42/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.005650390567602449</x:v>
+        <x:f>IFERROR(I42/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.00615679994822167</x:v>
       </x:c>
       <x:c r="K42" s="31" t="n">
-        <x:f>RANK(I42,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I42,$I$9:$I$54,0)</x:f>
         <x:v>34</x:v>
       </x:c>
       <x:c r="L42" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G42,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="G43" s="30" t="str">
-        <x:v>荷寶</x:v>
+        <x:v>滙豐</x:v>
       </x:c>
       <x:c r="H43" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G43,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>506416368</x:v>
+        <x:v>460000000</x:v>
       </x:c>
       <x:c r="I43" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G43,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>697308846</x:v>
+        <x:v>706462588</x:v>
       </x:c>
       <x:c r="J43" s="43" t="n">
-        <x:f>IFERROR(I43/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.005577177607236788</x:v>
+        <x:f>IFERROR(I43/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.005650390567602449</x:v>
       </x:c>
       <x:c r="K43" s="31" t="n">
-        <x:f>RANK(I43,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I43,$I$9:$I$54,0)</x:f>
         <x:v>35</x:v>
       </x:c>
       <x:c r="L43" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G43,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="G44" s="30" t="str">
-        <x:v>摩根士丹利</x:v>
+        <x:v>荷寶</x:v>
       </x:c>
       <x:c r="H44" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G44,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>460000000</x:v>
+        <x:v>506416368</x:v>
       </x:c>
       <x:c r="I44" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G44,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>690570828</x:v>
+        <x:v>697308846</x:v>
       </x:c>
       <x:c r="J44" s="43" t="n">
-        <x:f>IFERROR(I44/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.005523285958905744</x:v>
+        <x:f>IFERROR(I44/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.005577177607236788</x:v>
       </x:c>
       <x:c r="K44" s="31" t="n">
-        <x:f>RANK(I44,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I44,$I$9:$I$54,0)</x:f>
         <x:v>36</x:v>
       </x:c>
       <x:c r="L44" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G44,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="G45" s="30" t="str">
-        <x:v>PGIM</x:v>
+        <x:v>摩根士丹利</x:v>
       </x:c>
       <x:c r="H45" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G45,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>600000000</x:v>
+        <x:v>460000000</x:v>
       </x:c>
       <x:c r="I45" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G45,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>688857784</x:v>
+        <x:v>690570828</x:v>
       </x:c>
       <x:c r="J45" s="43" t="n">
-        <x:f>IFERROR(I45/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.005509584783749547</x:v>
+        <x:f>IFERROR(I45/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.005523285958905744</x:v>
       </x:c>
       <x:c r="K45" s="31" t="n">
-        <x:f>RANK(I45,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I45,$I$9:$I$54,0)</x:f>
         <x:v>37</x:v>
       </x:c>
       <x:c r="L45" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G45,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="G46" s="30" t="str">
-        <x:v>Amundi</x:v>
+        <x:v>PGIM</x:v>
       </x:c>
       <x:c r="H46" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G46,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>500000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="I46" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G46,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>666575819</x:v>
+        <x:v>688857784</x:v>
       </x:c>
       <x:c r="J46" s="43" t="n">
-        <x:f>IFERROR(I46/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.005331370385701836</x:v>
+        <x:f>IFERROR(I46/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.005509584783749547</x:v>
       </x:c>
       <x:c r="K46" s="31" t="n">
-        <x:f>RANK(I46,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I46,$I$9:$I$54,0)</x:f>
         <x:v>38</x:v>
       </x:c>
       <x:c r="L46" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G46,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="G47" s="30" t="str">
-        <x:v>LGIM</x:v>
+        <x:v>Amundi</x:v>
       </x:c>
       <x:c r="H47" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G47,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>400000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="I47" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G47,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>593041556</x:v>
+        <x:v>666575819</x:v>
       </x:c>
       <x:c r="J47" s="43" t="n">
-        <x:f>IFERROR(I47/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.004743232651151627</x:v>
+        <x:f>IFERROR(I47/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.005331370385701836</x:v>
       </x:c>
       <x:c r="K47" s="31" t="n">
-        <x:f>RANK(I47,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I47,$I$9:$I$54,0)</x:f>
         <x:v>39</x:v>
       </x:c>
       <x:c r="L47" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G47,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="G48" s="30" t="str">
-        <x:v>信安環球</x:v>
+        <x:v>LGIM</x:v>
       </x:c>
       <x:c r="H48" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G48,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>425091462</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="I48" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G48,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>478192278</x:v>
+        <x:v>593041556</x:v>
       </x:c>
       <x:c r="J48" s="43" t="n">
-        <x:f>IFERROR(I48/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.0038246514153861015</x:v>
+        <x:f>IFERROR(I48/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.004743232651151627</x:v>
       </x:c>
       <x:c r="K48" s="31" t="n">
-        <x:f>RANK(I48,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I48,$I$9:$I$54,0)</x:f>
         <x:v>40</x:v>
       </x:c>
       <x:c r="L48" s="32" t="n">
@@ -32322,11 +30402,11 @@
         <x:v>458409894</x:v>
       </x:c>
       <x:c r="J49" s="43" t="n">
-        <x:f>IFERROR(I49/SUM($I$9:$I$58),0)</x:f>
+        <x:f>IFERROR(I49/SUM($I$9:$I$54),0)</x:f>
         <x:v>0.0036664290298600195</x:v>
       </x:c>
       <x:c r="K49" s="31" t="n">
-        <x:f>RANK(I49,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I49,$I$9:$I$54,0)</x:f>
         <x:v>41</x:v>
       </x:c>
       <x:c r="L49" s="32" t="n">
@@ -32336,7 +30416,7 @@
     </x:row>
     <x:row r="50">
       <x:c r="G50" s="30" t="str">
-        <x:v>UBS</x:v>
+        <x:v>HSBC</x:v>
       </x:c>
       <x:c r="H50" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G50,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
@@ -32344,14 +30424,14 @@
       </x:c>
       <x:c r="I50" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G50,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>422040147</x:v>
+        <x:v>421747465</x:v>
       </x:c>
       <x:c r="J50" s="43" t="n">
-        <x:f>IFERROR(I50/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.0033755385016345</x:v>
+        <x:f>IFERROR(I50/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.003373197588413902</x:v>
       </x:c>
       <x:c r="K50" s="31" t="n">
-        <x:f>RANK(I50,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I50,$I$9:$I$54,0)</x:f>
         <x:v>42</x:v>
       </x:c>
       <x:c r="L50" s="32" t="n">
@@ -32361,22 +30441,22 @@
     </x:row>
     <x:row r="51">
       <x:c r="G51" s="30" t="str">
-        <x:v>HSBC</x:v>
+        <x:v>Allianz</x:v>
       </x:c>
       <x:c r="H51" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G51,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>400000000</x:v>
+        <x:v>275923278</x:v>
       </x:c>
       <x:c r="I51" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G51,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>421747465</x:v>
+        <x:v>275639320</x:v>
       </x:c>
       <x:c r="J51" s="43" t="n">
-        <x:f>IFERROR(I51/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.003373197588413902</x:v>
+        <x:f>IFERROR(I51/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0.002204603386284842</x:v>
       </x:c>
       <x:c r="K51" s="31" t="n">
-        <x:f>RANK(I51,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I51,$I$9:$I$54,0)</x:f>
         <x:v>43</x:v>
       </x:c>
       <x:c r="L51" s="32" t="n">
@@ -32386,176 +30466,76 @@
     </x:row>
     <x:row r="52">
       <x:c r="G52" s="30" t="str">
-        <x:v>瑞銀</x:v>
+        <x:v>柏瑞</x:v>
       </x:c>
       <x:c r="H52" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G52,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>361201485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I52" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G52,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>367521178</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J52" s="43" t="n">
-        <x:f>IFERROR(I52/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.002939487855180437</x:v>
+        <x:f>IFERROR(I52/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K52" s="31" t="n">
-        <x:f>RANK(I52,$I$9:$I$58,0)</x:f>
+        <x:f>RANK(I52,$I$9:$I$54,0)</x:f>
         <x:v>44</x:v>
       </x:c>
       <x:c r="L52" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G52,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="G53" s="30" t="str">
-        <x:v>Allianz</x:v>
+        <x:v>玉山</x:v>
       </x:c>
       <x:c r="H53" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G53,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>275923278</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="40" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G53,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>275639320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J53" s="43" t="n">
-        <x:f>IFERROR(I53/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0.002204603386284842</x:v>
+        <x:f>IFERROR(I53/SUM($I$9:$I$54),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K53" s="31" t="n">
-        <x:f>RANK(I53,$I$9:$I$58,0)</x:f>
-        <x:v>45</x:v>
+        <x:f>RANK(I53,$I$9:$I$54,0)</x:f>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L53" s="32" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G53,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="G54" s="30" t="str">
-        <x:v>柏瑞</x:v>
-      </x:c>
-      <x:c r="H54" s="40" t="n">
+      <x:c r="G54" s="33" t="str">
+        <x:v>國泰</x:v>
+      </x:c>
+      <x:c r="H54" s="41" t="n">
         <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G54,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I54" s="40" t="n">
+      <x:c r="I54" s="41" t="n">
         <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G54,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J54" s="43" t="n">
-        <x:f>IFERROR(I54/SUM($I$9:$I$58),0)</x:f>
+      <x:c r="J54" s="44" t="n">
+        <x:f>IFERROR(I54/SUM($I$9:$I$54),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K54" s="31" t="n">
-        <x:f>RANK(I54,$I$9:$I$58,0)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L54" s="32" t="n">
+      <x:c r="K54" s="34" t="n">
+        <x:f>RANK(I54,$I$9:$I$54,0)</x:f>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L54" s="35" t="n">
         <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G54,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
-      <x:c r="G55" s="30" t="str">
-        <x:v>安聯</x:v>
-      </x:c>
-      <x:c r="H55" s="40" t="n">
-        <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G55,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I55" s="40" t="n">
-        <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G55,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J55" s="43" t="n">
-        <x:f>IFERROR(I55/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K55" s="31" t="n">
-        <x:f>RANK(I55,$I$9:$I$58,0)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L55" s="32" t="n">
-        <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G55,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="G56" s="30" t="str">
-        <x:v>玉山</x:v>
-      </x:c>
-      <x:c r="H56" s="40" t="n">
-        <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G56,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I56" s="40" t="n">
-        <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G56,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J56" s="43" t="n">
-        <x:f>IFERROR(I56/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K56" s="31" t="n">
-        <x:f>RANK(I56,$I$9:$I$58,0)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L56" s="32" t="n">
-        <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G56,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57">
-      <x:c r="G57" s="30" t="str">
-        <x:v>野村</x:v>
-      </x:c>
-      <x:c r="H57" s="40" t="n">
-        <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G57,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I57" s="40" t="n">
-        <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G57,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J57" s="43" t="n">
-        <x:f>IFERROR(I57/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K57" s="31" t="n">
-        <x:f>RANK(I57,$I$9:$I$58,0)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L57" s="32" t="n">
-        <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G57,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="G58" s="33" t="str">
-        <x:v>國泰</x:v>
-      </x:c>
-      <x:c r="H58" s="41" t="n">
-        <x:f>SUMIFS('國外委外明細'!$G$4:$G$188,'國外委外明細'!$F$4:$F$188,G58,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I58" s="41" t="n">
-        <x:f>SUMIFS('國外委外明細'!$H$4:$H$188,'國外委外明細'!$F$4:$F$188,G58,'國外委外明細'!$A$4:$A$188,$B$4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J58" s="44" t="n">
-        <x:f>IFERROR(I58/SUM($I$9:$I$58),0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K58" s="34" t="n">
-        <x:f>RANK(I58,$I$9:$I$58,0)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L58" s="35" t="n">
-        <x:f>COUNTIFS('國外委外明細'!$F$4:$F$188,G58,'國外委外明細'!$A$4:$A$188,$B$4,'國外委外明細'!$J$4:$J$188,"&lt;&gt;解約")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -32564,7 +30544,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4068634ba3d4894"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45831a0033ca4cbf"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="Rea57131bbd824ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rc7f6dd0ef8624f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R8f610c8024324425"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R503ecde672d34e62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R4ebe21c7b8d64aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R802666f003924e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R9c0fb9a211e949db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Red807b104c3e47b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R435746bd90384b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R4818d5ca136d45d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rc7badedce6024dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R1ee838209b6846ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R386c6cba956148f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R0e1ce79a85344cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rd6ea12b3b34e4f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R20c90765d3ce449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R915d050253f44ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R857a65ef08204e5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,10 +571,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$V$12:$V$15</c:f>
+              <c:f>'儀表板'!$V$12:$V$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -582,7 +618,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$W$12:$W$15</c:f>
+              <c:f>'儀表板'!$W$12:$W$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -673,10 +709,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$AD$12:$AD$15</c:f>
+              <c:f>'儀表板(美元)'!$AD$12:$AD$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -684,7 +756,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AE$12:$AE$15</c:f>
+              <c:f>'儀表板(美元)'!$AE$12:$AE$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1517,10 +1589,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$X$12:$X$15</c:f>
+              <c:f>'儀表板'!$X$12:$X$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1528,7 +1636,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$Y$12:$Y$15</c:f>
+              <c:f>'儀表板'!$Y$12:$Y$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1619,10 +1727,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$Z$12:$Z$15</c:f>
+              <c:f>'儀表板'!$Z$12:$Z$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1630,7 +1774,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AA$12:$AA$15</c:f>
+              <c:f>'儀表板'!$AA$12:$AA$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1721,10 +1865,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$AB$12:$AB$15</c:f>
+              <c:f>'儀表板'!$AB$12:$AB$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1732,7 +1912,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AC$12:$AC$15</c:f>
+              <c:f>'儀表板'!$AC$12:$AC$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1823,10 +2003,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板'!$AD$12:$AD$15</c:f>
+              <c:f>'儀表板'!$AD$12:$AD$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1834,7 +2050,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板'!$AE$12:$AE$15</c:f>
+              <c:f>'儀表板'!$AE$12:$AE$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1925,10 +2141,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$V$12:$V$15</c:f>
+              <c:f>'儀表板(美元)'!$V$12:$V$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1936,7 +2188,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$W$12:$W$15</c:f>
+              <c:f>'儀表板(美元)'!$W$12:$W$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2027,10 +2279,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$X$12:$X$15</c:f>
+              <c:f>'儀表板(美元)'!$X$12:$X$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2038,7 +2326,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$Y$12:$Y$15</c:f>
+              <c:f>'儀表板(美元)'!$Y$12:$Y$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2129,10 +2417,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$Z$12:$Z$15</c:f>
+              <c:f>'儀表板(美元)'!$Z$12:$Z$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2140,7 +2464,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AA$12:$AA$15</c:f>
+              <c:f>'儀表板(美元)'!$AA$12:$AA$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2231,10 +2555,46 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'儀表板(美元)'!$AB$12:$AB$15</c:f>
+              <c:f>'儀表板(美元)'!$AB$12:$AB$19</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -2242,7 +2602,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'儀表板(美元)'!$AC$12:$AC$15</c:f>
+              <c:f>'儀表板(美元)'!$AC$12:$AC$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="0"/>
@@ -2295,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rddc8e118ed474418"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R499b756ae71d4727"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2325,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b65fbf37bde4894"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0e0e4b4a3044b20"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2355,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4a329b0c78c647c2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67a7b50753e84862"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2385,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b4a3c4fd0d84121"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10fe982a9454461a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2415,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R55ef10ffbb394b03"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b77855f2a9843c4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2450,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb2a6c0d367bd46fa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ac6eea6adbd48dd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2480,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56c9937843464ec6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78f0ba3d51114af9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2510,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c39af05f56c4eb8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23039cf788e748e1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2540,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra0ea1935afa845af"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R818fabeb35b946c1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2570,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbe4c7fa4cb2f4027"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0232fed47cc4d50"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2605,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca4d8f8b1ada4398"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f0ef1055a014989"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2635,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R19e78b81399f4313"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R736bb5eb73e54bd4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2665,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4beec4e9e464d05"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra456163f163f4cb0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2695,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfce1f130435241f8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raeff7a0e2b9e498b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3291,39 +3651,39 @@
         <x:v>來源與報價時間已註明</x:v>
       </x:c>
       <x:c r="V12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.22060000000000002</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19999999999999998</x:v>
       </x:c>
       <x:c r="X12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1165</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.4086</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1724</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AB12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1711</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.3965</x:v>
       </x:c>
       <x:c r="AD12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.45747499999999997</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.9830249999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3351,39 +3711,39 @@
         <x:v>2654.12955439</x:v>
       </x:c>
       <x:c r="V13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.4739</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12080000000000002</x:v>
       </x:c>
       <x:c r="X13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.3744</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0248</x:v>
       </x:c>
       <x:c r="Z13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.2375</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1151</x:v>
       </x:c>
       <x:c r="AB13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.3722</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12240000000000001</x:v>
       </x:c>
       <x:c r="AD13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.8622749999999999</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.095775</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3411,39 +3771,39 @@
         <x:v>802.98009492</x:v>
       </x:c>
       <x:c r="V14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1055</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.014100000000000001</x:v>
       </x:c>
       <x:c r="X14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1005</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0184</x:v>
       </x:c>
       <x:c r="Z14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="AA14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.0901</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0604</x:v>
       </x:c>
       <x:c r="AB14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.060200000000000004</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0668</x:v>
       </x:c>
       <x:c r="AD14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.119375</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.039925</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3471,39 +3831,39 @@
         <x:v>15244.879584</x:v>
       </x:c>
       <x:c r="V15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.19999999999999998</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.007700000000000001</x:v>
       </x:c>
       <x:c r="X15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.4086</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.5</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0067</x:v>
       </x:c>
       <x:c r="AB15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.3965</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.026000000000000002</x:v>
       </x:c>
       <x:c r="AD15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.9830249999999999</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.010100000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3530,6 +3890,41 @@
         <x:f>SUM(B16:E16)</x:f>
         <x:v>8443.91807301</x:v>
       </x:c>
+      <x:c r="V16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="W16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19620000000000004</x:v>
+      </x:c>
+      <x:c r="X16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="Y16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.153</x:v>
+      </x:c>
+      <x:c r="Z16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AA16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.041299999999999996</x:v>
+      </x:c>
+      <x:c r="AB16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AC16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.11349999999999999</x:v>
+      </x:c>
+      <x:c r="AD16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AE16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.126</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="30" t="str">
@@ -3555,6 +3950,41 @@
         <x:f>SUM(B17:E17)</x:f>
         <x:v>22133.584103189998</x:v>
       </x:c>
+      <x:c r="V17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="W17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09980000000000001</x:v>
+      </x:c>
+      <x:c r="X17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="Y17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0917</x:v>
+      </x:c>
+      <x:c r="Z17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="AA17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.057300000000000004</x:v>
+      </x:c>
+      <x:c r="AB17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="AC17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0487</x:v>
+      </x:c>
+      <x:c r="AD17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="AE17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.07437500000000001</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="30" t="str">
@@ -3580,6 +4010,41 @@
         <x:f>SUM(B18:E18)</x:f>
         <x:v>8729.960386230001</x:v>
       </x:c>
+      <x:c r="V18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="W18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.26360000000000006</x:v>
+      </x:c>
+      <x:c r="X18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="Y18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.203</x:v>
+      </x:c>
+      <x:c r="Z18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AA18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1358</x:v>
+      </x:c>
+      <x:c r="AB18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AC18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19190000000000002</x:v>
+      </x:c>
+      <x:c r="AD18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AE18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.198575</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="30" t="str">
@@ -3604,6 +4069,41 @@
       <x:c r="F19" s="66" t="n">
         <x:f>SUM(B19:E19)</x:f>
         <x:v>9274.65680763</x:v>
+      </x:c>
+      <x:c r="V19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="W19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09780000000000001</x:v>
+      </x:c>
+      <x:c r="X19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="Y19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1005</x:v>
+      </x:c>
+      <x:c r="Z19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="AA19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0834</x:v>
+      </x:c>
+      <x:c r="AB19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="AC19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0342</x:v>
+      </x:c>
+      <x:c r="AD19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="AE19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.078975</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3837,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e123d448f714b76"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2af10b403a8454d"/>
 </x:worksheet>
 </file>
 
@@ -4158,39 +4658,39 @@
         <x:v>來源與報價時間已註明</x:v>
       </x:c>
       <x:c r="V12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="W12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.22060000000000002</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19999999999999998</x:v>
       </x:c>
       <x:c r="X12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="Y12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1165</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.4086</x:v>
       </x:c>
       <x:c r="Z12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="AA12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1724</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AB12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="AC12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1711</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.3965</x:v>
       </x:c>
       <x:c r="AD12" t="str">
-        <x:v>固定收益</x:v>
+        <x:v>自行運用 - 其他</x:v>
       </x:c>
       <x:c r="AE12" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.45747499999999997</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.9830249999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4218,39 +4718,39 @@
         <x:v>8.30843498009078</x:v>
       </x:c>
       <x:c r="V13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="W13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.4739</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12080000000000002</x:v>
       </x:c>
       <x:c r="X13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="Y13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.3744</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0248</x:v>
       </x:c>
       <x:c r="Z13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="AA13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.2375</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1151</x:v>
       </x:c>
       <x:c r="AB13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="AC13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.3722</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.12240000000000001</x:v>
       </x:c>
       <x:c r="AD13" t="str">
-        <x:v>權益證券</x:v>
+        <x:v>自行運用 - 固定收益</x:v>
       </x:c>
       <x:c r="AE13" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.8622749999999999</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.095775</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4278,39 +4778,39 @@
         <x:v>2.513633103521678</x:v>
       </x:c>
       <x:c r="V14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="W14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1055</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.014100000000000001</x:v>
       </x:c>
       <x:c r="X14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="Y14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.1005</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0184</x:v>
       </x:c>
       <x:c r="Z14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="AA14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.0901</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0604</x:v>
       </x:c>
       <x:c r="AB14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="AC14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.060200000000000004</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0668</x:v>
       </x:c>
       <x:c r="AD14" t="str">
-        <x:v>另類投資</x:v>
+        <x:v>自行運用 - 權益證券</x:v>
       </x:c>
       <x:c r="AE14" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.119375</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.039925</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4338,39 +4838,39 @@
         <x:v>47.7222713538895</x:v>
       </x:c>
       <x:c r="V15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="W15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.19999999999999998</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.007700000000000001</x:v>
       </x:c>
       <x:c r="X15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="Y15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.4086</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="AA15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.5</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0067</x:v>
       </x:c>
       <x:c r="AB15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="AC15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.3965</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.026000000000000002</x:v>
       </x:c>
       <x:c r="AD15" t="str">
-        <x:v>其他</x:v>
+        <x:v>自行運用 - 另類投資</x:v>
       </x:c>
       <x:c r="AE15" s="50" t="n">
-        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")),0)</x:f>
-        <x:v>0.9830249999999999</x:v>
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.010100000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4397,6 +4897,41 @@
         <x:f>SUM(B16:E16)</x:f>
         <x:v>26.432675138550632</x:v>
       </x:c>
+      <x:c r="V16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="W16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19620000000000004</x:v>
+      </x:c>
+      <x:c r="X16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="Y16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.153</x:v>
+      </x:c>
+      <x:c r="Z16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AA16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.041299999999999996</x:v>
+      </x:c>
+      <x:c r="AB16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AC16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.11349999999999999</x:v>
+      </x:c>
+      <x:c r="AD16" t="str">
+        <x:v>國內委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AE16" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.126</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="30" t="str">
@@ -4422,6 +4957,41 @@
         <x:f>SUM(B17:E17)</x:f>
         <x:v>69.28653655717639</x:v>
       </x:c>
+      <x:c r="V17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="W17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09980000000000001</x:v>
+      </x:c>
+      <x:c r="X17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="Y17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0917</x:v>
+      </x:c>
+      <x:c r="Z17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="AA17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.057300000000000004</x:v>
+      </x:c>
+      <x:c r="AB17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="AC17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0487</x:v>
+      </x:c>
+      <x:c r="AD17" t="str">
+        <x:v>國外委託經營 - 固定收益</x:v>
+      </x:c>
+      <x:c r="AE17" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.07437500000000001</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="30" t="str">
@@ -4447,6 +5017,41 @@
         <x:f>SUM(B18:E18)</x:f>
         <x:v>27.32809637260917</x:v>
       </x:c>
+      <x:c r="V18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="W18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.26360000000000006</x:v>
+      </x:c>
+      <x:c r="X18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="Y18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.203</x:v>
+      </x:c>
+      <x:c r="Z18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AA18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1358</x:v>
+      </x:c>
+      <x:c r="AB18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AC18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.19190000000000002</x:v>
+      </x:c>
+      <x:c r="AD18" t="str">
+        <x:v>國外委託經營 - 權益證券</x:v>
+      </x:c>
+      <x:c r="AE18" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.198575</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="30" t="str">
@@ -4471,6 +5076,41 @@
       <x:c r="F19" s="75" t="n">
         <x:f>SUM(B19:E19)</x:f>
         <x:v>29.033203342087965</x:v>
+      </x:c>
+      <x:c r="V19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="W19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"新制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.09780000000000001</x:v>
+      </x:c>
+      <x:c r="X19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="Y19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"舊制",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.1005</x:v>
+      </x:c>
+      <x:c r="Z19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="AA19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"勞工保險",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0834</x:v>
+      </x:c>
+      <x:c r="AB19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="AC19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$C$4:$C$263,"國民年金",'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.0342</x:v>
+      </x:c>
+      <x:c r="AD19" t="str">
+        <x:v>國外委託經營 - 另類投資</x:v>
+      </x:c>
+      <x:c r="AE19" s="50" t="n">
+        <x:f>IFERROR(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")/(SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"轉存金融機構")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政策性貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"短期票券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、公司債、金融債券及特別股")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"公債、金融債券、公司債及證券化商品")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"房屋及土地")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"政府或公營事業貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"被保險人貸款")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"股票及受益憑證投資（含期貨）")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"自行運用-國外-另類投資")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國內-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-固定收益")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-權益證券")+SUMIFS('月度資產配置'!$F$4:$F$263,'月度資產配置'!$A$4:$A$263,$A$6,'月度資產配置'!$D$4:$D$263,"委託經營-國外-另類投資")),0)</x:f>
+        <x:v>0.078975</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4701,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576dfdfedbb3494b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5403afd071214b54"/>
 </x:worksheet>
 </file>
 
@@ -11523,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55ff615b097e473d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebd52607121e48c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16562,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e109314e2a44d04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2456ac98db94528"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24541,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6614b9a4d8354037"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1d5ec689dcb43ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28480,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R234131b6140b42c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R460c4c544131444f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30544,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45831a0033ca4cbf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b9351d7950405e"/>
 </x:worksheet>
 </file>
 

--- a/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
+++ b/outputs/blf-monthly-disclosure/勞工退休基金月度揭露_可持續更新.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R4818d5ca136d45d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Rc7badedce6024dea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R1ee838209b6846ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R386c6cba956148f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R0e1ce79a85344cfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="Rd6ea12b3b34e4f62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="R20c90765d3ce449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="R915d050253f44ea8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R857a65ef08204e5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板" sheetId="1" r:id="R3812a4dc4885464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="儀表板(美元)" sheetId="2" r:id="Ra7b6409e80534c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度資產配置" sheetId="3" r:id="R1df0219790804d1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國內委外明細" sheetId="4" r:id="R0fa5779b336c4701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="國外委外明細" sheetId="5" r:id="R1e85928260b8496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次彙總" sheetId="6" r:id="R8638dd1b2e6c436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業者彙總" sheetId="7" r:id="Rda5d593f2f644463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新說明" sheetId="8" r:id="Rbd590052f5c54440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資料品質檢核" sheetId="9" r:id="R385aba81dc294349"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2655,7 +2655,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R499b756ae71d4727"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1c02425c7763405f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2685,7 +2685,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0e0e4b4a3044b20"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R85b6d07abc184071"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2715,7 +2715,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R67a7b50753e84862"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd685d74b5cdc4258"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2745,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10fe982a9454461a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9932d27bef4f408f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2775,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b77855f2a9843c4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0fec2278ac39463c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2810,7 +2810,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ac6eea6adbd48dd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbec2c5d1eb024a8e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2840,7 +2840,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78f0ba3d51114af9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5535927a18bd425a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2870,7 +2870,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23039cf788e748e1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0354150bd16c4667"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2900,7 +2900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R818fabeb35b946c1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e1d400215d14885"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2930,7 +2930,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0232fed47cc4d50"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d7731605b9c41bc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2965,7 +2965,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f0ef1055a014989"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00ee71bb6a294ea1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2995,7 +2995,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R736bb5eb73e54bd4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50a29c93ec7a4935"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3025,7 +3025,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra456163f163f4cb0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R71c6ae55c236430f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3055,7 +3055,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raeff7a0e2b9e498b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9ed78a9b4a8d44d5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3169,10 +3169,10 @@
         <a:srgbClr val="2F75B5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="F4B183"/>
+        <a:srgbClr val="1F4E79"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="F4B183"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="C55A11"/>
@@ -4337,7 +4337,7 @@
     <x:mergeCell ref="A3:T3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2af10b403a8454d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a4b1262333b466d"/>
 </x:worksheet>
 </file>
 
@@ -5341,7 +5341,7 @@
     <x:mergeCell ref="A22:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5403afd071214b54"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea3ee92266764a2b"/>
 </x:worksheet>
 </file>
 
@@ -12163,7 +12163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebd52607121e48c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reebcba79ece4414b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17202,7 +17202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2456ac98db94528"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R987db0bfe72f496d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1d5ec689dcb43ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b73035b34d6401a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29120,7 +29120,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R460c4c544131444f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e6bf0e5ad12484d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31184,7 +31184,7 @@
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b9351d7950405e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5427ddb105fe434e"/>
 </x:worksheet>
 </file>
 
